--- a/Excel/PetConfig.xlsx
+++ b/Excel/PetConfig.xlsx
@@ -30,6 +30,7 @@
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>admin</author>
+    <author>Administrator</author>
   </authors>
   <commentList>
     <comment ref="C3" authorId="0">
@@ -55,20 +56,57 @@
         </r>
       </text>
     </comment>
+    <comment ref="G3" authorId="1">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+实际生效值/10</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="37">
+  <si>
+    <t>#</t>
+  </si>
   <si>
     <t>_ID</t>
   </si>
   <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Role</t>
+  </si>
+  <si>
     <t>AttrId</t>
   </si>
   <si>
-    <t>AttrValue</t>
+    <t>MinValue</t>
+  </si>
+  <si>
+    <t>MaxValue</t>
+  </si>
+  <si>
+    <t>Percent</t>
   </si>
   <si>
     <t>StartQuality</t>
@@ -77,7 +115,7 @@
     <t>EndQuality</t>
   </si>
   <si>
-    <t>Role</t>
+    <t>MaxCount</t>
   </si>
   <si>
     <t>描述</t>
@@ -92,82 +130,70 @@
     <t>int</t>
   </si>
   <si>
-    <t>double</t>
-  </si>
-  <si>
     <t>string</t>
   </si>
   <si>
-    <t>幸运</t>
-  </si>
-  <si>
-    <t>暴击</t>
-  </si>
-  <si>
-    <t>爆伤</t>
-  </si>
-  <si>
-    <t>增伤</t>
-  </si>
-  <si>
-    <t>减伤</t>
-  </si>
-  <si>
-    <t>物伤加成</t>
-  </si>
-  <si>
-    <t>法伤加成</t>
-  </si>
-  <si>
-    <t>道伤加成</t>
-  </si>
-  <si>
-    <t>经验加成</t>
-  </si>
-  <si>
-    <t>爆率加成</t>
-  </si>
-  <si>
-    <t>金币加成</t>
-  </si>
-  <si>
-    <t>品质加成</t>
-  </si>
-  <si>
-    <t>物攻倍率</t>
-  </si>
-  <si>
-    <t>魔法倍率</t>
-  </si>
-  <si>
-    <t>道术倍率</t>
-  </si>
-  <si>
-    <t>防御倍率</t>
-  </si>
-  <si>
-    <t>生命倍率</t>
-  </si>
-  <si>
-    <t>闪避</t>
-  </si>
-  <si>
-    <t>命中</t>
-  </si>
-  <si>
-    <t>攻击倍率</t>
-  </si>
-  <si>
-    <t>经验增幅</t>
-  </si>
-  <si>
-    <t>金币增幅</t>
-  </si>
-  <si>
-    <t>爆率增幅</t>
-  </si>
-  <si>
-    <t>品质增幅</t>
+    <t>杀敌攻击</t>
+  </si>
+  <si>
+    <t>杀敌血量</t>
+  </si>
+  <si>
+    <t>杀敌防御</t>
+  </si>
+  <si>
+    <t>杀敌物攻</t>
+  </si>
+  <si>
+    <t>杀敌魔攻</t>
+  </si>
+  <si>
+    <t>杀敌道攻</t>
+  </si>
+  <si>
+    <t>十敌加攻</t>
+  </si>
+  <si>
+    <t>十敌加血</t>
+  </si>
+  <si>
+    <t>十敌加防</t>
+  </si>
+  <si>
+    <t>百敌加攻</t>
+  </si>
+  <si>
+    <t>百敌加血</t>
+  </si>
+  <si>
+    <t>百敌加防</t>
+  </si>
+  <si>
+    <t>千敌加攻</t>
+  </si>
+  <si>
+    <t>千敌加血</t>
+  </si>
+  <si>
+    <t>千敌加防</t>
+  </si>
+  <si>
+    <t>万敌攻加</t>
+  </si>
+  <si>
+    <t>万敌血加</t>
+  </si>
+  <si>
+    <t>万敌防加</t>
+  </si>
+  <si>
+    <t>万敌攻增</t>
+  </si>
+  <si>
+    <t>万敌血增</t>
+  </si>
+  <si>
+    <t>万敌防增</t>
   </si>
 </sst>
 </file>
@@ -180,7 +206,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -191,17 +217,11 @@
     <font>
       <sz val="9"/>
       <color theme="1"/>
-      <name val="微软雅黑"/>
+      <name val="等线"/>
       <charset val="134"/>
     </font>
     <font>
       <b/>
-      <sz val="9"/>
-      <color theme="1"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="9"/>
       <color theme="1"/>
       <name val="等线"/>
@@ -687,143 +707,142 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1143,642 +1162,720 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:I55"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13"/>
+  <dimension ref="A1:M26"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
-    <col min="1" max="4" width="9" style="1"/>
-    <col min="5" max="5" width="17.125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="9.625" style="1" customWidth="1"/>
-    <col min="7" max="8" width="13" style="1" customWidth="1"/>
-    <col min="9" max="9" width="17" style="1" customWidth="1"/>
-    <col min="10" max="16384" width="9" style="1"/>
+    <col min="1" max="3" width="9" style="1"/>
+    <col min="4" max="5" width="12.8333333333333" style="1" customWidth="1"/>
+    <col min="6" max="6" width="9" style="1"/>
+    <col min="7" max="8" width="17.125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="13.5" style="1" customWidth="1"/>
+    <col min="10" max="10" width="9.625" style="1" customWidth="1"/>
+    <col min="11" max="12" width="13" style="1" customWidth="1"/>
+    <col min="13" max="13" width="17" style="1" customWidth="1"/>
+    <col min="14" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="3" s="1" customFormat="1" ht="13.5" spans="3:9">
+    <row r="1" customHeight="1" spans="1:13">
+      <c r="M1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" customHeight="1" spans="1:13">
+      <c r="M2" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:13">
       <c r="C3" s="2" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:13">
+      <c r="C4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="F4" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="G4" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="H4" s="2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="4" s="1" customFormat="1" ht="13.5" spans="3:9">
-      <c r="C4" s="2" t="s">
+      <c r="I4" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="I4" s="2" t="s">
+      <c r="J4" s="2" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="5" s="1" customFormat="1" ht="13.5" spans="3:9">
+      <c r="K4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="L4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="M4" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:13">
       <c r="C5" s="2" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="6" s="1" customFormat="1" spans="3:9">
+        <v>14</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="L5" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="M5" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" s="1" customFormat="1" customHeight="1" spans="1:13">
       <c r="C6" s="1">
         <v>1</v>
       </c>
-      <c r="D6" s="1">
-        <v>7</v>
+      <c r="D6" s="1" t="s">
+        <v>16</v>
       </c>
       <c r="E6" s="1">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F6" s="1">
+        <v>3</v>
+      </c>
+      <c r="G6" s="1">
+        <v>5</v>
+      </c>
+      <c r="H6" s="1">
+        <v>15</v>
+      </c>
+      <c r="I6" s="1">
         <v>1</v>
       </c>
-      <c r="G6" s="1">
+      <c r="J6" s="1">
         <v>1</v>
       </c>
-      <c r="H6" s="1">
-        <v>0</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="7" s="1" customFormat="1" spans="3:9">
+      <c r="K6" s="1">
+        <v>9</v>
+      </c>
+      <c r="L6" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" customHeight="1" spans="1:13">
       <c r="C7" s="1">
         <v>2</v>
       </c>
-      <c r="D7" s="3">
-        <v>8</v>
+      <c r="D7" s="1" t="s">
+        <v>17</v>
       </c>
       <c r="E7" s="1">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F7" s="1">
         <v>1</v>
       </c>
       <c r="G7" s="1">
+        <v>50</v>
+      </c>
+      <c r="H7" s="1">
+        <v>300</v>
+      </c>
+      <c r="I7" s="1">
         <v>1</v>
       </c>
-      <c r="H7" s="1">
-        <v>0</v>
-      </c>
-      <c r="I7" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="8" s="1" customFormat="1" spans="3:9">
+      <c r="J7" s="1">
+        <v>1</v>
+      </c>
+      <c r="K7" s="1">
+        <v>9</v>
+      </c>
+      <c r="L7" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" customHeight="1" spans="1:13">
       <c r="C8" s="1">
         <v>3</v>
       </c>
-      <c r="D8" s="1">
-        <v>9</v>
+      <c r="D8" s="1" t="s">
+        <v>18</v>
       </c>
       <c r="E8" s="1">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="F8" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G8" s="1">
         <v>1</v>
       </c>
       <c r="H8" s="1">
-        <v>0</v>
-      </c>
-      <c r="I8" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="9" s="1" customFormat="1" spans="3:9">
+        <v>3</v>
+      </c>
+      <c r="I8" s="1">
+        <v>1</v>
+      </c>
+      <c r="J8" s="1">
+        <v>1</v>
+      </c>
+      <c r="K8" s="1">
+        <v>9</v>
+      </c>
+      <c r="L8" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" s="1" customFormat="1" customHeight="1" spans="1:13">
       <c r="C9" s="1">
         <v>4</v>
       </c>
-      <c r="D9" s="1">
-        <v>12</v>
+      <c r="D9" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="E9" s="1">
-        <v>40</v>
+        <v>1</v>
       </c>
       <c r="F9" s="1">
+        <v>4</v>
+      </c>
+      <c r="G9" s="1">
+        <v>5</v>
+      </c>
+      <c r="H9" s="1">
+        <v>30</v>
+      </c>
+      <c r="I9" s="1">
         <v>1</v>
       </c>
-      <c r="G9" s="1">
+      <c r="J9" s="1">
         <v>1</v>
       </c>
-      <c r="H9" s="1">
-        <v>0</v>
-      </c>
-      <c r="I9" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="10" s="1" customFormat="1" spans="3:9">
+      <c r="K9" s="1">
+        <v>9</v>
+      </c>
+      <c r="L9" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" s="1" customFormat="1" customHeight="1" spans="1:13">
       <c r="C10" s="1">
         <v>5</v>
       </c>
-      <c r="D10" s="1">
-        <v>13</v>
+      <c r="D10" s="1" t="s">
+        <v>20</v>
       </c>
       <c r="E10" s="1">
+        <v>2</v>
+      </c>
+      <c r="F10" s="1">
+        <v>5</v>
+      </c>
+      <c r="G10" s="1">
+        <v>5</v>
+      </c>
+      <c r="H10" s="1">
         <v>30</v>
       </c>
-      <c r="F10" s="1">
+      <c r="I10" s="1">
         <v>1</v>
       </c>
-      <c r="G10" s="1">
+      <c r="J10" s="1">
         <v>1</v>
       </c>
-      <c r="H10" s="1">
-        <v>0</v>
-      </c>
-      <c r="I10" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="11" spans="3:9">
+      <c r="K10" s="1">
+        <v>9</v>
+      </c>
+      <c r="L10" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" s="1" customFormat="1" customHeight="1" spans="1:13">
       <c r="C11" s="1">
         <v>6</v>
       </c>
-      <c r="D11" s="1">
-        <v>33</v>
+      <c r="D11" s="1" t="s">
+        <v>21</v>
       </c>
       <c r="E11" s="1">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="F11" s="1">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G11" s="1">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H11" s="1">
+        <v>30</v>
+      </c>
+      <c r="I11" s="1">
         <v>1</v>
       </c>
-      <c r="I11" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="12" s="1" customFormat="1" spans="3:9">
+      <c r="J11" s="1">
+        <v>1</v>
+      </c>
+      <c r="K11" s="1">
+        <v>9</v>
+      </c>
+      <c r="L11" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" s="1" customFormat="1" customHeight="1" spans="1:13">
+      <c r="A12" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="C12" s="1">
         <v>7</v>
       </c>
-      <c r="D12" s="1">
-        <v>34</v>
-      </c>
-      <c r="E12" s="1">
-        <v>50</v>
-      </c>
-      <c r="F12" s="1">
-        <v>2</v>
-      </c>
-      <c r="G12" s="1">
-        <v>2</v>
-      </c>
-      <c r="H12" s="1">
-        <v>2</v>
-      </c>
-      <c r="I12" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="13" s="1" customFormat="1" spans="3:9">
+      <c r="D12" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="I12" s="1">
+        <v>10</v>
+      </c>
+      <c r="J12" s="1">
+        <v>6</v>
+      </c>
+      <c r="K12" s="1">
+        <v>9</v>
+      </c>
+      <c r="L12" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" s="1" customFormat="1" customHeight="1" spans="1:13">
+      <c r="A13" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="C13" s="1">
         <v>8</v>
       </c>
-      <c r="D13" s="1">
-        <v>35</v>
-      </c>
-      <c r="E13" s="1">
-        <v>50</v>
-      </c>
-      <c r="F13" s="1">
-        <v>2</v>
-      </c>
-      <c r="G13" s="1">
-        <v>2</v>
-      </c>
-      <c r="H13" s="1">
-        <v>3</v>
-      </c>
-      <c r="I13" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="14" s="1" customFormat="1" spans="3:9">
+      <c r="D13" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I13" s="1">
+        <v>10</v>
+      </c>
+      <c r="J13" s="1">
+        <v>6</v>
+      </c>
+      <c r="K13" s="1">
+        <v>9</v>
+      </c>
+      <c r="L13" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" customHeight="1" spans="1:13">
+      <c r="A14" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="C14" s="1">
         <v>9</v>
       </c>
-      <c r="D14" s="1">
-        <v>18</v>
-      </c>
-      <c r="E14" s="1">
-        <v>100</v>
-      </c>
-      <c r="F14" s="1">
-        <v>3</v>
-      </c>
-      <c r="G14" s="1">
-        <v>3</v>
-      </c>
-      <c r="H14" s="1">
-        <v>0</v>
-      </c>
-      <c r="I14" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="15" s="1" customFormat="1" spans="3:9">
+      <c r="D14" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="I14" s="1">
+        <v>10</v>
+      </c>
+      <c r="J14" s="1">
+        <v>6</v>
+      </c>
+      <c r="K14" s="1">
+        <v>9</v>
+      </c>
+      <c r="L14" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" s="1" customFormat="1" customHeight="1" spans="1:13">
+      <c r="A15" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="C15" s="1">
         <v>10</v>
       </c>
-      <c r="D15" s="1">
-        <v>19</v>
-      </c>
-      <c r="E15" s="1">
-        <v>50</v>
-      </c>
-      <c r="F15" s="1">
-        <v>3</v>
-      </c>
-      <c r="G15" s="1">
-        <v>3</v>
-      </c>
-      <c r="H15" s="1">
-        <v>0</v>
-      </c>
-      <c r="I15" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="16" s="1" customFormat="1" spans="3:9">
+      <c r="D15" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="I15" s="1">
+        <v>100</v>
+      </c>
+      <c r="J15" s="1">
+        <v>6</v>
+      </c>
+      <c r="K15" s="1">
+        <v>9</v>
+      </c>
+      <c r="L15" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" s="1" customFormat="1" customHeight="1" spans="1:13">
+      <c r="A16" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="C16" s="1">
         <v>11</v>
       </c>
-      <c r="D16" s="1">
-        <v>20</v>
-      </c>
-      <c r="E16" s="1">
+      <c r="D16" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="I16" s="1">
         <v>100</v>
       </c>
-      <c r="F16" s="1">
-        <v>3</v>
-      </c>
-      <c r="G16" s="1">
-        <v>3</v>
-      </c>
-      <c r="H16" s="1">
-        <v>0</v>
-      </c>
-      <c r="I16" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="17" s="1" customFormat="1" spans="3:9">
+      <c r="J16" s="1">
+        <v>6</v>
+      </c>
+      <c r="K16" s="1">
+        <v>9</v>
+      </c>
+      <c r="L16" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" s="1" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A17" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="C17" s="1">
         <v>12</v>
       </c>
-      <c r="D17" s="1">
-        <v>24</v>
-      </c>
-      <c r="E17" s="1">
-        <v>50</v>
-      </c>
-      <c r="F17" s="1">
-        <v>3</v>
-      </c>
-      <c r="G17" s="1">
-        <v>3</v>
-      </c>
-      <c r="H17" s="1">
-        <v>0</v>
-      </c>
-      <c r="I17" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="18" s="1" customFormat="1" spans="3:9">
+      <c r="D17" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="I17" s="1">
+        <v>100</v>
+      </c>
+      <c r="J17" s="1">
+        <v>6</v>
+      </c>
+      <c r="K17" s="1">
+        <v>9</v>
+      </c>
+      <c r="L17" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" s="1" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A18" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="C18" s="1">
         <v>13</v>
       </c>
-      <c r="D18" s="1">
-        <v>2004</v>
-      </c>
-      <c r="E18" s="1">
-        <v>8</v>
-      </c>
-      <c r="F18" s="1">
-        <v>4</v>
-      </c>
-      <c r="G18" s="1">
-        <v>4</v>
-      </c>
-      <c r="H18" s="1">
-        <v>1</v>
-      </c>
-      <c r="I18" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="19" s="1" customFormat="1" spans="3:9">
+      <c r="D18" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="I18" s="1">
+        <v>1000</v>
+      </c>
+      <c r="J18" s="1">
+        <v>6</v>
+      </c>
+      <c r="K18" s="1">
+        <v>9</v>
+      </c>
+      <c r="L18" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" s="1" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A19" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="C19" s="1">
         <v>14</v>
       </c>
-      <c r="D19" s="1">
-        <v>2005</v>
-      </c>
-      <c r="E19" s="1">
-        <v>8</v>
-      </c>
-      <c r="F19" s="1">
-        <v>4</v>
-      </c>
-      <c r="G19" s="1">
-        <v>4</v>
-      </c>
-      <c r="H19" s="1">
-        <v>2</v>
-      </c>
-      <c r="I19" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="20" s="1" customFormat="1" spans="3:9">
+      <c r="D19" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I19" s="1">
+        <v>1000</v>
+      </c>
+      <c r="J19" s="1">
+        <v>6</v>
+      </c>
+      <c r="K19" s="1">
+        <v>9</v>
+      </c>
+      <c r="L19" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" s="1" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A20" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="C20" s="1">
         <v>15</v>
       </c>
-      <c r="D20" s="1">
-        <v>2006</v>
-      </c>
-      <c r="E20" s="1">
-        <v>8</v>
-      </c>
-      <c r="F20" s="1">
-        <v>4</v>
-      </c>
-      <c r="G20" s="1">
-        <v>4</v>
-      </c>
-      <c r="H20" s="1">
-        <v>3</v>
-      </c>
-      <c r="I20" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="21" s="1" customFormat="1" spans="3:9">
+      <c r="D20" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="I20" s="1">
+        <v>1000</v>
+      </c>
+      <c r="J20" s="1">
+        <v>6</v>
+      </c>
+      <c r="K20" s="1">
+        <v>9</v>
+      </c>
+      <c r="L20" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" s="1" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A21" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="C21" s="1">
         <v>16</v>
       </c>
-      <c r="D21" s="1">
-        <v>2002</v>
-      </c>
-      <c r="E21" s="1">
-        <v>40</v>
-      </c>
-      <c r="F21" s="1">
-        <v>5</v>
-      </c>
-      <c r="G21" s="1">
-        <v>5</v>
-      </c>
-      <c r="H21" s="1">
-        <v>0</v>
-      </c>
-      <c r="I21" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="22" s="1" customFormat="1" spans="3:9">
+      <c r="D21" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="I21" s="1">
+        <v>10000</v>
+      </c>
+      <c r="J21" s="1">
+        <v>6</v>
+      </c>
+      <c r="K21" s="1">
+        <v>9</v>
+      </c>
+      <c r="L21" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" s="1" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A22" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="C22" s="1">
         <v>17</v>
       </c>
-      <c r="D22" s="1">
-        <v>2003</v>
-      </c>
-      <c r="E22" s="1">
-        <v>20</v>
-      </c>
-      <c r="F22" s="1">
-        <v>5</v>
-      </c>
-      <c r="G22" s="1">
-        <v>5</v>
-      </c>
-      <c r="H22" s="1">
-        <v>0</v>
-      </c>
-      <c r="I22" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="23" s="1" customFormat="1" spans="3:9">
+      <c r="D22" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I22" s="1">
+        <v>10000</v>
+      </c>
+      <c r="J22" s="1">
+        <v>6</v>
+      </c>
+      <c r="K22" s="1">
+        <v>9</v>
+      </c>
+      <c r="L22" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" s="1" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A23" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="C23" s="1">
         <v>18</v>
       </c>
-      <c r="D23" s="1">
-        <v>31</v>
-      </c>
-      <c r="E23" s="1">
-        <v>0.4</v>
-      </c>
-      <c r="F23" s="1">
+      <c r="D23" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I23" s="1">
+        <v>10000</v>
+      </c>
+      <c r="J23" s="1">
         <v>6</v>
       </c>
-      <c r="G23" s="1">
-        <v>6</v>
-      </c>
-      <c r="H23" s="1">
-        <v>0</v>
-      </c>
-      <c r="I23" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="24" s="1" customFormat="1" spans="3:9">
+      <c r="K23" s="1">
+        <v>9</v>
+      </c>
+      <c r="L23" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" s="1" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A24" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="C24" s="1">
         <v>19</v>
       </c>
-      <c r="D24" s="1">
-        <v>32</v>
-      </c>
-      <c r="E24" s="1">
-        <v>0.2</v>
-      </c>
-      <c r="F24" s="1">
+      <c r="D24" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="I24" s="1">
+        <v>10000</v>
+      </c>
+      <c r="J24" s="1">
         <v>6</v>
       </c>
-      <c r="G24" s="1">
-        <v>6</v>
-      </c>
-      <c r="H24" s="1">
-        <v>0</v>
-      </c>
-      <c r="I24" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="25" s="1" customFormat="1" spans="3:9">
+      <c r="K24" s="1">
+        <v>9</v>
+      </c>
+      <c r="L24" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" s="1" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A25" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="C25" s="1">
         <v>20</v>
       </c>
-      <c r="D25" s="1">
-        <v>2001</v>
-      </c>
-      <c r="E25" s="1">
-        <v>5</v>
-      </c>
-      <c r="F25" s="1">
+      <c r="D25" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="I25" s="1">
+        <v>10000</v>
+      </c>
+      <c r="J25" s="1">
         <v>6</v>
       </c>
-      <c r="G25" s="1">
-        <v>6</v>
-      </c>
-      <c r="H25" s="1">
-        <v>0</v>
-      </c>
-      <c r="I25" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="26" s="1" customFormat="1" spans="3:9">
+      <c r="K25" s="1">
+        <v>9</v>
+      </c>
+      <c r="L25" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26" s="1" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A26" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="C26" s="1">
         <v>21</v>
       </c>
-      <c r="D26" s="1">
-        <v>50</v>
-      </c>
-      <c r="E26" s="1">
-        <v>0.1</v>
-      </c>
-      <c r="F26" s="1">
-        <v>7</v>
-      </c>
-      <c r="G26" s="1">
-        <v>7</v>
-      </c>
-      <c r="H26" s="1">
-        <v>0</v>
-      </c>
-      <c r="I26" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="27" s="1" customFormat="1" spans="3:9">
-      <c r="C27" s="1">
-        <v>22</v>
-      </c>
-      <c r="D27" s="1">
-        <v>51</v>
-      </c>
-      <c r="E27" s="1">
-        <v>0.1</v>
-      </c>
-      <c r="F27" s="1">
-        <v>7</v>
-      </c>
-      <c r="G27" s="1">
-        <v>7</v>
-      </c>
-      <c r="H27" s="1">
-        <v>0</v>
-      </c>
-      <c r="I27" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="28" s="1" customFormat="1" spans="3:9">
-      <c r="C28" s="1">
-        <v>23</v>
-      </c>
-      <c r="D28" s="1">
-        <v>52</v>
-      </c>
-      <c r="E28" s="1">
-        <v>0.1</v>
-      </c>
-      <c r="F28" s="1">
-        <v>7</v>
-      </c>
-      <c r="G28" s="1">
-        <v>7</v>
-      </c>
-      <c r="H28" s="1">
-        <v>0</v>
-      </c>
-      <c r="I28" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="29" s="1" customFormat="1" spans="3:9">
-      <c r="C29" s="1">
-        <v>24</v>
-      </c>
-      <c r="D29" s="1">
-        <v>53</v>
-      </c>
-      <c r="E29" s="1">
-        <v>0.1</v>
-      </c>
-      <c r="F29" s="1">
-        <v>7</v>
-      </c>
-      <c r="G29" s="1">
-        <v>7</v>
-      </c>
-      <c r="H29" s="1">
-        <v>0</v>
-      </c>
-      <c r="I29" s="1" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="55" s="1" customFormat="1" ht="81" customHeight="1"/>
+      <c r="D26" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="I26" s="1">
+        <v>10000</v>
+      </c>
+      <c r="J26" s="1">
+        <v>6</v>
+      </c>
+      <c r="K26" s="1">
+        <v>9</v>
+      </c>
+      <c r="L26" s="1">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="I3:I5 C3:D5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="M3:M5 C3:F5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/PetConfig.xlsx
+++ b/Excel/PetConfig.xlsx
@@ -1305,10 +1305,10 @@
         <v>3</v>
       </c>
       <c r="G6" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H6" s="1">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="I6" s="1">
         <v>1</v>
@@ -1337,7 +1337,7 @@
         <v>1</v>
       </c>
       <c r="G7" s="1">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="H7" s="1">
         <v>300</v>
@@ -1372,7 +1372,7 @@
         <v>1</v>
       </c>
       <c r="H8" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I8" s="1">
         <v>1</v>
@@ -1401,10 +1401,10 @@
         <v>4</v>
       </c>
       <c r="G9" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H9" s="1">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="I9" s="1">
         <v>1</v>
@@ -1433,10 +1433,10 @@
         <v>5</v>
       </c>
       <c r="G10" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H10" s="1">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="I10" s="1">
         <v>1</v>
@@ -1465,10 +1465,10 @@
         <v>6</v>
       </c>
       <c r="G11" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H11" s="1">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="I11" s="1">
         <v>1</v>

--- a/Excel/PetConfig.xlsx
+++ b/Excel/PetConfig.xlsx
@@ -133,13 +133,13 @@
     <t>string</t>
   </si>
   <si>
-    <t>杀敌攻击</t>
-  </si>
-  <si>
-    <t>杀敌血量</t>
-  </si>
-  <si>
-    <t>杀敌防御</t>
+    <t>十敌攻击</t>
+  </si>
+  <si>
+    <t>一敌生命</t>
+  </si>
+  <si>
+    <t>百敌防御</t>
   </si>
   <si>
     <t>杀敌物攻</t>
@@ -1305,13 +1305,13 @@
         <v>3</v>
       </c>
       <c r="G6" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H6" s="1">
         <v>10</v>
       </c>
       <c r="I6" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="J6" s="1">
         <v>1</v>
@@ -1337,10 +1337,10 @@
         <v>1</v>
       </c>
       <c r="G7" s="1">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="H7" s="1">
-        <v>300</v>
+        <v>20</v>
       </c>
       <c r="I7" s="1">
         <v>1</v>
@@ -1375,7 +1375,7 @@
         <v>5</v>
       </c>
       <c r="I8" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="J8" s="1">
         <v>1</v>

--- a/Excel/PetConfig.xlsx
+++ b/Excel/PetConfig.xlsx
@@ -83,7 +83,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="38">
   <si>
     <t>#</t>
   </si>
@@ -106,6 +106,9 @@
     <t>MaxValue</t>
   </si>
   <si>
+    <t>QualitRise</t>
+  </si>
+  <si>
     <t>Percent</t>
   </si>
   <si>
@@ -133,13 +136,13 @@
     <t>string</t>
   </si>
   <si>
-    <t>十敌攻击</t>
-  </si>
-  <si>
-    <t>一敌生命</t>
-  </si>
-  <si>
-    <t>百敌防御</t>
+    <t>杀敌攻击</t>
+  </si>
+  <si>
+    <t>杀敌生命</t>
+  </si>
+  <si>
+    <t>十敌防御</t>
   </si>
   <si>
     <t>杀敌物攻</t>
@@ -1162,31 +1165,32 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M26"/>
+  <dimension ref="A1:N26"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="1"/>
     <col min="4" max="5" width="12.8333333333333" style="1" customWidth="1"/>
     <col min="6" max="6" width="9" style="1"/>
-    <col min="7" max="8" width="17.125" style="1" customWidth="1"/>
-    <col min="9" max="9" width="13.5" style="1" customWidth="1"/>
-    <col min="10" max="10" width="9.625" style="1" customWidth="1"/>
-    <col min="11" max="12" width="13" style="1" customWidth="1"/>
-    <col min="13" max="13" width="17" style="1" customWidth="1"/>
-    <col min="14" max="16384" width="9" style="1"/>
+    <col min="7" max="7" width="17.125" style="1" customWidth="1"/>
+    <col min="8" max="9" width="14.0833333333333" style="1" customWidth="1"/>
+    <col min="10" max="10" width="13.5" style="1" customWidth="1"/>
+    <col min="11" max="11" width="9.625" style="1" customWidth="1"/>
+    <col min="12" max="13" width="13" style="1" customWidth="1"/>
+    <col min="14" max="14" width="17" style="1" customWidth="1"/>
+    <col min="15" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" customHeight="1" spans="1:13">
-      <c r="M1" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" customHeight="1" spans="1:13">
-      <c r="M2" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:13">
+    <row r="1" customHeight="1" spans="1:14">
+      <c r="N1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" customHeight="1" spans="1:14">
+      <c r="N2" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="C3" s="2" t="s">
         <v>1</v>
       </c>
@@ -1220,10 +1224,13 @@
       <c r="M3" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:13">
+      <c r="N3" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="C4" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>2</v>
@@ -1253,50 +1260,56 @@
         <v>10</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:13">
+        <v>11</v>
+      </c>
+      <c r="N4" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="C5" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D5" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="E5" s="2" t="s">
-        <v>14</v>
-      </c>
       <c r="F5" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M5" s="2" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="6" s="1" customFormat="1" customHeight="1" spans="1:13">
+      <c r="N5" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="C6" s="1">
         <v>1</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E6" s="1">
         <v>0</v>
@@ -1308,59 +1321,65 @@
         <v>1</v>
       </c>
       <c r="H6" s="1">
+        <v>2</v>
+      </c>
+      <c r="I6" s="1">
+        <v>1</v>
+      </c>
+      <c r="J6" s="1">
+        <v>1</v>
+      </c>
+      <c r="K6" s="1">
+        <v>1</v>
+      </c>
+      <c r="L6" s="1">
+        <v>9</v>
+      </c>
+      <c r="M6" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" customHeight="1" spans="1:14">
+      <c r="C7" s="1">
+        <v>2</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E7" s="1">
+        <v>0</v>
+      </c>
+      <c r="F7" s="1">
+        <v>1</v>
+      </c>
+      <c r="G7" s="1">
         <v>10</v>
       </c>
-      <c r="I6" s="1">
-        <v>10</v>
-      </c>
-      <c r="J6" s="1">
-        <v>1</v>
-      </c>
-      <c r="K6" s="1">
-        <v>9</v>
-      </c>
-      <c r="L6" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" s="1" customFormat="1" customHeight="1" spans="1:13">
-      <c r="C7" s="1">
-        <v>2</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E7" s="1">
-        <v>0</v>
-      </c>
-      <c r="F7" s="1">
-        <v>1</v>
-      </c>
-      <c r="G7" s="1">
-        <v>1</v>
-      </c>
       <c r="H7" s="1">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="I7" s="1">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="J7" s="1">
         <v>1</v>
       </c>
       <c r="K7" s="1">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="L7" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" s="1" customFormat="1" customHeight="1" spans="1:13">
+        <v>9</v>
+      </c>
+      <c r="M7" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="C8" s="1">
         <v>3</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E8" s="1">
         <v>0</v>
@@ -1372,27 +1391,30 @@
         <v>1</v>
       </c>
       <c r="H8" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I8" s="1">
+        <v>1</v>
+      </c>
+      <c r="J8" s="1">
         <v>100</v>
       </c>
-      <c r="J8" s="1">
-        <v>1</v>
-      </c>
       <c r="K8" s="1">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="L8" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" s="1" customFormat="1" customHeight="1" spans="1:13">
+        <v>9</v>
+      </c>
+      <c r="M8" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="C9" s="1">
         <v>4</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E9" s="1">
         <v>1</v>
@@ -1401,30 +1423,33 @@
         <v>4</v>
       </c>
       <c r="G9" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H9" s="1">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="I9" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J9" s="1">
         <v>1</v>
       </c>
       <c r="K9" s="1">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="L9" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10" s="1" customFormat="1" customHeight="1" spans="1:13">
+        <v>9</v>
+      </c>
+      <c r="M9" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="C10" s="1">
         <v>5</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E10" s="1">
         <v>2</v>
@@ -1433,30 +1458,33 @@
         <v>5</v>
       </c>
       <c r="G10" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H10" s="1">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="I10" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J10" s="1">
         <v>1</v>
       </c>
       <c r="K10" s="1">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="L10" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="11" s="1" customFormat="1" customHeight="1" spans="1:13">
+        <v>9</v>
+      </c>
+      <c r="M10" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="C11" s="1">
         <v>6</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E11" s="1">
         <v>3</v>
@@ -1465,25 +1493,28 @@
         <v>6</v>
       </c>
       <c r="G11" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H11" s="1">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="I11" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J11" s="1">
         <v>1</v>
       </c>
       <c r="K11" s="1">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="L11" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="12" s="1" customFormat="1" customHeight="1" spans="1:13">
+        <v>9</v>
+      </c>
+      <c r="M11" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="A12" s="1" t="s">
         <v>0</v>
       </c>
@@ -1494,22 +1525,22 @@
         <v>7</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="I12" s="1">
+        <v>23</v>
+      </c>
+      <c r="J12" s="1">
         <v>10</v>
       </c>
-      <c r="J12" s="1">
+      <c r="K12" s="1">
         <v>6</v>
       </c>
-      <c r="K12" s="1">
-        <v>9</v>
-      </c>
       <c r="L12" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13" s="1" customFormat="1" customHeight="1" spans="1:13">
+        <v>9</v>
+      </c>
+      <c r="M12" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="A13" s="1" t="s">
         <v>0</v>
       </c>
@@ -1520,22 +1551,22 @@
         <v>8</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="I13" s="1">
+        <v>24</v>
+      </c>
+      <c r="J13" s="1">
         <v>10</v>
       </c>
-      <c r="J13" s="1">
+      <c r="K13" s="1">
         <v>6</v>
       </c>
-      <c r="K13" s="1">
-        <v>9</v>
-      </c>
       <c r="L13" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="14" customHeight="1" spans="1:13">
+        <v>9</v>
+      </c>
+      <c r="M13" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" customHeight="1" spans="1:14">
       <c r="A14" s="1" t="s">
         <v>0</v>
       </c>
@@ -1546,22 +1577,22 @@
         <v>9</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="I14" s="1">
+        <v>25</v>
+      </c>
+      <c r="J14" s="1">
         <v>10</v>
       </c>
-      <c r="J14" s="1">
+      <c r="K14" s="1">
         <v>6</v>
       </c>
-      <c r="K14" s="1">
-        <v>9</v>
-      </c>
       <c r="L14" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="15" s="1" customFormat="1" customHeight="1" spans="1:13">
+        <v>9</v>
+      </c>
+      <c r="M14" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="A15" s="1" t="s">
         <v>0</v>
       </c>
@@ -1572,22 +1603,22 @@
         <v>10</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="I15" s="1">
+        <v>26</v>
+      </c>
+      <c r="J15" s="1">
         <v>100</v>
       </c>
-      <c r="J15" s="1">
+      <c r="K15" s="1">
         <v>6</v>
       </c>
-      <c r="K15" s="1">
-        <v>9</v>
-      </c>
       <c r="L15" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="16" s="1" customFormat="1" customHeight="1" spans="1:13">
+        <v>9</v>
+      </c>
+      <c r="M15" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="A16" s="1" t="s">
         <v>0</v>
       </c>
@@ -1598,22 +1629,22 @@
         <v>11</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="I16" s="1">
+        <v>27</v>
+      </c>
+      <c r="J16" s="1">
         <v>100</v>
       </c>
-      <c r="J16" s="1">
+      <c r="K16" s="1">
         <v>6</v>
       </c>
-      <c r="K16" s="1">
-        <v>9</v>
-      </c>
       <c r="L16" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="17" s="1" customFormat="1" customHeight="1" spans="1:12">
+        <v>9</v>
+      </c>
+      <c r="M16" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" s="1" customFormat="1" customHeight="1" spans="1:13">
       <c r="A17" s="1" t="s">
         <v>0</v>
       </c>
@@ -1624,22 +1655,22 @@
         <v>12</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="I17" s="1">
+        <v>28</v>
+      </c>
+      <c r="J17" s="1">
         <v>100</v>
       </c>
-      <c r="J17" s="1">
+      <c r="K17" s="1">
         <v>6</v>
       </c>
-      <c r="K17" s="1">
-        <v>9</v>
-      </c>
       <c r="L17" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="18" s="1" customFormat="1" customHeight="1" spans="1:12">
+        <v>9</v>
+      </c>
+      <c r="M17" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" s="1" customFormat="1" customHeight="1" spans="1:13">
       <c r="A18" s="1" t="s">
         <v>0</v>
       </c>
@@ -1650,22 +1681,22 @@
         <v>13</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="I18" s="1">
+        <v>29</v>
+      </c>
+      <c r="J18" s="1">
         <v>1000</v>
       </c>
-      <c r="J18" s="1">
+      <c r="K18" s="1">
         <v>6</v>
       </c>
-      <c r="K18" s="1">
-        <v>9</v>
-      </c>
       <c r="L18" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="19" s="1" customFormat="1" customHeight="1" spans="1:12">
+        <v>9</v>
+      </c>
+      <c r="M18" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" s="1" customFormat="1" customHeight="1" spans="1:13">
       <c r="A19" s="1" t="s">
         <v>0</v>
       </c>
@@ -1676,22 +1707,22 @@
         <v>14</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="I19" s="1">
+        <v>30</v>
+      </c>
+      <c r="J19" s="1">
         <v>1000</v>
       </c>
-      <c r="J19" s="1">
+      <c r="K19" s="1">
         <v>6</v>
       </c>
-      <c r="K19" s="1">
-        <v>9</v>
-      </c>
       <c r="L19" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="20" s="1" customFormat="1" customHeight="1" spans="1:12">
+        <v>9</v>
+      </c>
+      <c r="M19" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" s="1" customFormat="1" customHeight="1" spans="1:13">
       <c r="A20" s="1" t="s">
         <v>0</v>
       </c>
@@ -1702,22 +1733,22 @@
         <v>15</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="I20" s="1">
+        <v>31</v>
+      </c>
+      <c r="J20" s="1">
         <v>1000</v>
       </c>
-      <c r="J20" s="1">
+      <c r="K20" s="1">
         <v>6</v>
       </c>
-      <c r="K20" s="1">
-        <v>9</v>
-      </c>
       <c r="L20" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="21" s="1" customFormat="1" customHeight="1" spans="1:12">
+        <v>9</v>
+      </c>
+      <c r="M20" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" s="1" customFormat="1" customHeight="1" spans="1:13">
       <c r="A21" s="1" t="s">
         <v>0</v>
       </c>
@@ -1728,22 +1759,22 @@
         <v>16</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="I21" s="1">
+        <v>32</v>
+      </c>
+      <c r="J21" s="1">
         <v>10000</v>
       </c>
-      <c r="J21" s="1">
+      <c r="K21" s="1">
         <v>6</v>
       </c>
-      <c r="K21" s="1">
-        <v>9</v>
-      </c>
       <c r="L21" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="22" s="1" customFormat="1" customHeight="1" spans="1:12">
+        <v>9</v>
+      </c>
+      <c r="M21" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" s="1" customFormat="1" customHeight="1" spans="1:13">
       <c r="A22" s="1" t="s">
         <v>0</v>
       </c>
@@ -1754,22 +1785,22 @@
         <v>17</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I22" s="1">
+        <v>33</v>
+      </c>
+      <c r="J22" s="1">
         <v>10000</v>
       </c>
-      <c r="J22" s="1">
+      <c r="K22" s="1">
         <v>6</v>
       </c>
-      <c r="K22" s="1">
-        <v>9</v>
-      </c>
       <c r="L22" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="23" s="1" customFormat="1" customHeight="1" spans="1:12">
+        <v>9</v>
+      </c>
+      <c r="M22" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" s="1" customFormat="1" customHeight="1" spans="1:13">
       <c r="A23" s="1" t="s">
         <v>0</v>
       </c>
@@ -1780,22 +1811,22 @@
         <v>18</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="I23" s="1">
+        <v>34</v>
+      </c>
+      <c r="J23" s="1">
         <v>10000</v>
       </c>
-      <c r="J23" s="1">
+      <c r="K23" s="1">
         <v>6</v>
       </c>
-      <c r="K23" s="1">
-        <v>9</v>
-      </c>
       <c r="L23" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="24" s="1" customFormat="1" customHeight="1" spans="1:12">
+        <v>9</v>
+      </c>
+      <c r="M23" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" s="1" customFormat="1" customHeight="1" spans="1:13">
       <c r="A24" s="1" t="s">
         <v>0</v>
       </c>
@@ -1806,22 +1837,22 @@
         <v>19</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="I24" s="1">
+        <v>35</v>
+      </c>
+      <c r="J24" s="1">
         <v>10000</v>
       </c>
-      <c r="J24" s="1">
+      <c r="K24" s="1">
         <v>6</v>
       </c>
-      <c r="K24" s="1">
-        <v>9</v>
-      </c>
       <c r="L24" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="25" s="1" customFormat="1" customHeight="1" spans="1:12">
+        <v>9</v>
+      </c>
+      <c r="M24" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" s="1" customFormat="1" customHeight="1" spans="1:13">
       <c r="A25" s="1" t="s">
         <v>0</v>
       </c>
@@ -1832,22 +1863,22 @@
         <v>20</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="I25" s="1">
+        <v>36</v>
+      </c>
+      <c r="J25" s="1">
         <v>10000</v>
       </c>
-      <c r="J25" s="1">
+      <c r="K25" s="1">
         <v>6</v>
       </c>
-      <c r="K25" s="1">
-        <v>9</v>
-      </c>
       <c r="L25" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="26" s="1" customFormat="1" customHeight="1" spans="1:12">
+        <v>9</v>
+      </c>
+      <c r="M25" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26" s="1" customFormat="1" customHeight="1" spans="1:13">
       <c r="A26" s="1" t="s">
         <v>0</v>
       </c>
@@ -1858,24 +1889,24 @@
         <v>21</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="I26" s="1">
+        <v>37</v>
+      </c>
+      <c r="J26" s="1">
         <v>10000</v>
       </c>
-      <c r="J26" s="1">
+      <c r="K26" s="1">
         <v>6</v>
       </c>
-      <c r="K26" s="1">
-        <v>9</v>
-      </c>
       <c r="L26" s="1">
+        <v>9</v>
+      </c>
+      <c r="M26" s="1">
         <v>2</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="M3:M5 C3:F5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="N3:N5 C3:F5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/PetConfig.xlsx
+++ b/Excel/PetConfig.xlsx
@@ -30,7 +30,6 @@
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>admin</author>
-    <author>Administrator</author>
   </authors>
   <commentList>
     <comment ref="C3" authorId="0">
@@ -56,37 +55,12 @@
         </r>
       </text>
     </comment>
-    <comment ref="G3" authorId="1">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>Administrator:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-实际生效值/10</t>
-        </r>
-      </text>
-    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="38">
-  <si>
-    <t>#</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="87">
   <si>
     <t>_ID</t>
   </si>
@@ -94,109 +68,259 @@
     <t>Name</t>
   </si>
   <si>
-    <t>Role</t>
-  </si>
-  <si>
-    <t>AttrId</t>
-  </si>
-  <si>
-    <t>MinValue</t>
-  </si>
-  <si>
-    <t>MaxValue</t>
-  </si>
-  <si>
-    <t>QualitRise</t>
-  </si>
-  <si>
-    <t>Percent</t>
-  </si>
-  <si>
-    <t>StartQuality</t>
-  </si>
-  <si>
-    <t>EndQuality</t>
-  </si>
-  <si>
-    <t>MaxCount</t>
-  </si>
-  <si>
-    <t>描述</t>
+    <t>CardGroupId</t>
+  </si>
+  <si>
+    <t>CardQuality</t>
+  </si>
+  <si>
+    <t>CardAtrList</t>
+  </si>
+  <si>
+    <t>CardVueList</t>
   </si>
   <si>
     <t>Id</t>
   </si>
   <si>
-    <t>Desc</t>
-  </si>
-  <si>
     <t>int</t>
   </si>
   <si>
     <t>string</t>
   </si>
   <si>
-    <t>杀敌攻击</t>
-  </si>
-  <si>
-    <t>杀敌生命</t>
-  </si>
-  <si>
-    <t>十敌防御</t>
-  </si>
-  <si>
-    <t>杀敌物攻</t>
-  </si>
-  <si>
-    <t>杀敌魔攻</t>
-  </si>
-  <si>
-    <t>杀敌道攻</t>
-  </si>
-  <si>
-    <t>十敌加攻</t>
-  </si>
-  <si>
-    <t>十敌加血</t>
-  </si>
-  <si>
-    <t>十敌加防</t>
-  </si>
-  <si>
-    <t>百敌加攻</t>
-  </si>
-  <si>
-    <t>百敌加血</t>
-  </si>
-  <si>
-    <t>百敌加防</t>
-  </si>
-  <si>
-    <t>千敌加攻</t>
-  </si>
-  <si>
-    <t>千敌加血</t>
-  </si>
-  <si>
-    <t>千敌加防</t>
-  </si>
-  <si>
-    <t>万敌攻加</t>
-  </si>
-  <si>
-    <t>万敌血加</t>
-  </si>
-  <si>
-    <t>万敌防加</t>
-  </si>
-  <si>
-    <t>万敌攻增</t>
-  </si>
-  <si>
-    <t>万敌血增</t>
-  </si>
-  <si>
-    <t>万敌防增</t>
+    <t>int[]</t>
+  </si>
+  <si>
+    <t>狼宝宝</t>
+  </si>
+  <si>
+    <t>4,3</t>
+  </si>
+  <si>
+    <t>20,10</t>
+  </si>
+  <si>
+    <t>骷髅宝宝</t>
+  </si>
+  <si>
+    <t>4,2</t>
+  </si>
+  <si>
+    <t>20,5</t>
+  </si>
+  <si>
+    <t>兽人宝宝</t>
+  </si>
+  <si>
+    <t>10,5</t>
+  </si>
+  <si>
+    <t>蜘蛛宝宝</t>
+  </si>
+  <si>
+    <t>4,1</t>
+  </si>
+  <si>
+    <t>10,200</t>
+  </si>
+  <si>
+    <t>岩蝎宝宝</t>
+  </si>
+  <si>
+    <t>10,1</t>
+  </si>
+  <si>
+    <t>鬃狮宝宝</t>
+  </si>
+  <si>
+    <t>毒蛆宝宝</t>
+  </si>
+  <si>
+    <t>蜈蚣宝宝</t>
+  </si>
+  <si>
+    <t>双头宝宝</t>
+  </si>
+  <si>
+    <t>蛛王宝宝</t>
+  </si>
+  <si>
+    <t>蛇宝宝</t>
+  </si>
+  <si>
+    <t>巨鳄宝宝</t>
+  </si>
+  <si>
+    <t>乌鸦宝宝</t>
+  </si>
+  <si>
+    <t>行尸宝宝</t>
+  </si>
+  <si>
+    <t>尸鬼宝宝</t>
+  </si>
+  <si>
+    <t>蝙蝠宝宝</t>
+  </si>
+  <si>
+    <t>尸魔宝宝</t>
+  </si>
+  <si>
+    <t>尸卫宝宝</t>
+  </si>
+  <si>
+    <t>花妖宝宝</t>
+  </si>
+  <si>
+    <t>树精宝宝</t>
+  </si>
+  <si>
+    <t>鱼人宝宝</t>
+  </si>
+  <si>
+    <t>狼人宝宝</t>
+  </si>
+  <si>
+    <t>蠕虫宝宝</t>
+  </si>
+  <si>
+    <t>角鹿宝宝</t>
+  </si>
+  <si>
+    <t>恶犬宝宝</t>
+  </si>
+  <si>
+    <t>守卫宝宝</t>
+  </si>
+  <si>
+    <t>射手宝宝</t>
+  </si>
+  <si>
+    <t>幽灵宝宝</t>
+  </si>
+  <si>
+    <t>法师宝宝</t>
+  </si>
+  <si>
+    <t>骸骨宝宝</t>
+  </si>
+  <si>
+    <t>战猪宝宝</t>
+  </si>
+  <si>
+    <t>勇猪宝宝</t>
+  </si>
+  <si>
+    <t>力猪宝宝</t>
+  </si>
+  <si>
+    <t>萨满宝宝</t>
+  </si>
+  <si>
+    <t>战将宝宝</t>
+  </si>
+  <si>
+    <t>亲卫宝宝</t>
+  </si>
+  <si>
+    <t>花宝宝</t>
+  </si>
+  <si>
+    <t>甲虫宝宝</t>
+  </si>
+  <si>
+    <t>火蛇宝宝</t>
+  </si>
+  <si>
+    <t>赤炎宝宝</t>
+  </si>
+  <si>
+    <t>魔姬宝宝</t>
+  </si>
+  <si>
+    <t>炎魔宝宝</t>
+  </si>
+  <si>
+    <t>冰蝎宝宝</t>
+  </si>
+  <si>
+    <t>寒冰宝宝</t>
+  </si>
+  <si>
+    <t>龙龟宝宝</t>
+  </si>
+  <si>
+    <t>霜骑宝宝</t>
+  </si>
+  <si>
+    <t>巨霜宝宝</t>
+  </si>
+  <si>
+    <t>鬼蛛宝宝</t>
+  </si>
+  <si>
+    <t>蛇姬宝宝</t>
+  </si>
+  <si>
+    <t>巨蜥宝宝</t>
+  </si>
+  <si>
+    <t>暗夜宝宝</t>
+  </si>
+  <si>
+    <t>祭司宝宝</t>
+  </si>
+  <si>
+    <t>女骑宝宝</t>
+  </si>
+  <si>
+    <t>人马宝宝</t>
+  </si>
+  <si>
+    <t>巨熊宝宝</t>
+  </si>
+  <si>
+    <t>屠戮宝宝</t>
+  </si>
+  <si>
+    <t>牛头宝宝</t>
+  </si>
+  <si>
+    <t>蛮卫宝宝</t>
+  </si>
+  <si>
+    <t>魔瞳宝宝</t>
+  </si>
+  <si>
+    <t>收割宝宝</t>
+  </si>
+  <si>
+    <t>血魔宝宝</t>
+  </si>
+  <si>
+    <t>恶魔宝宝</t>
+  </si>
+  <si>
+    <t>黑骑宝宝</t>
+  </si>
+  <si>
+    <t>巫师宝宝</t>
+  </si>
+  <si>
+    <t>三头宝宝</t>
+  </si>
+  <si>
+    <t>女巫宝宝</t>
+  </si>
+  <si>
+    <t>魇兽宝宝</t>
+  </si>
+  <si>
+    <t>大魔宝宝</t>
+  </si>
+  <si>
+    <t>领主宝宝</t>
   </si>
 </sst>
 </file>
@@ -209,7 +333,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="26">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -224,8 +348,21 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <b/>
       <sz val="9"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="等线"/>
       <charset val="134"/>
@@ -710,142 +847,157 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1165,749 +1317,1627 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N26"/>
+  <dimension ref="C3:M107"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="1"/>
-    <col min="4" max="5" width="12.8333333333333" style="1" customWidth="1"/>
-    <col min="6" max="6" width="9" style="1"/>
-    <col min="7" max="7" width="17.125" style="1" customWidth="1"/>
-    <col min="8" max="9" width="14.0833333333333" style="1" customWidth="1"/>
-    <col min="10" max="10" width="13.5" style="1" customWidth="1"/>
-    <col min="11" max="11" width="9.625" style="1" customWidth="1"/>
-    <col min="12" max="13" width="13" style="1" customWidth="1"/>
-    <col min="14" max="14" width="17" style="1" customWidth="1"/>
-    <col min="15" max="16384" width="9" style="1"/>
+    <col min="4" max="4" width="12.8333333333333" style="1" customWidth="1"/>
+    <col min="5" max="6" width="13" style="2" customWidth="1"/>
+    <col min="7" max="7" width="14.1666666666667" style="2" customWidth="1"/>
+    <col min="8" max="8" width="13" style="2" customWidth="1"/>
+    <col min="9" max="9" width="13.5" style="1" customWidth="1"/>
+    <col min="10" max="10" width="9.625" style="1" customWidth="1"/>
+    <col min="11" max="12" width="13" style="1" customWidth="1"/>
+    <col min="13" max="13" width="17" style="1" customWidth="1"/>
+    <col min="14" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" customHeight="1" spans="1:14">
-      <c r="N1" s="1" t="s">
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C3" s="3" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" customHeight="1" spans="1:14">
-      <c r="N2" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:14">
-      <c r="C3" s="2" t="s">
+      <c r="D3" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="E3" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="F3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="G3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="H3" s="2" t="s">
+      <c r="H3" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="I3" s="3"/>
+      <c r="J3" s="3"/>
+      <c r="K3" s="3"/>
+      <c r="L3" s="3"/>
+      <c r="M3" s="3"/>
+    </row>
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C4" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="D4" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="I4" s="3"/>
+      <c r="J4" s="3"/>
+      <c r="K4" s="3"/>
+      <c r="L4" s="3"/>
+      <c r="M4" s="3"/>
+    </row>
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C5" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="D5" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K3" s="2" t="s">
+      <c r="E5" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="G5" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="L3" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="M3" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="N3" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:14">
-      <c r="C4" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="K4" s="2" t="s">
+      <c r="H5" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="L4" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="M4" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="N4" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:14">
-      <c r="C5" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="K5" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="L5" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="M5" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="N5" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="6" s="1" customFormat="1" customHeight="1" spans="1:14">
+      <c r="I5" s="3"/>
+      <c r="J5" s="3"/>
+      <c r="K5" s="3"/>
+      <c r="L5" s="3"/>
+      <c r="M5" s="3"/>
+    </row>
+    <row r="6" s="1" customFormat="1" customHeight="1" spans="3:13">
       <c r="C6" s="1">
         <v>1</v>
       </c>
-      <c r="D6" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E6" s="1">
-        <v>0</v>
-      </c>
-      <c r="F6" s="1">
-        <v>3</v>
-      </c>
-      <c r="G6" s="1">
+      <c r="D6" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="E6" s="2">
+        <f t="shared" ref="E6:E69" si="0">INT(C6/6)+1</f>
         <v>1</v>
       </c>
-      <c r="H6" s="1">
-        <v>2</v>
-      </c>
-      <c r="I6" s="1">
-        <v>1</v>
-      </c>
-      <c r="J6" s="1">
-        <v>1</v>
-      </c>
-      <c r="K6" s="1">
-        <v>1</v>
-      </c>
-      <c r="L6" s="1">
-        <v>9</v>
-      </c>
-      <c r="M6" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" s="1" customFormat="1" customHeight="1" spans="1:14">
+      <c r="F6" s="2">
+        <v>5</v>
+      </c>
+      <c r="G6" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H6" s="9" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" customHeight="1" spans="3:13">
       <c r="C7" s="1">
         <v>2</v>
       </c>
-      <c r="D7" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E7" s="1">
-        <v>0</v>
-      </c>
-      <c r="F7" s="1">
+      <c r="D7" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" s="2">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="G7" s="1">
-        <v>10</v>
-      </c>
-      <c r="H7" s="1">
-        <v>100</v>
-      </c>
-      <c r="I7" s="1">
-        <v>50</v>
-      </c>
-      <c r="J7" s="1">
-        <v>1</v>
-      </c>
-      <c r="K7" s="1">
-        <v>1</v>
-      </c>
-      <c r="L7" s="1">
-        <v>9</v>
-      </c>
-      <c r="M7" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" s="1" customFormat="1" customHeight="1" spans="1:14">
+      <c r="F7" s="2">
+        <v>5</v>
+      </c>
+      <c r="G7" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="H7" s="9" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:13">
       <c r="C8" s="1">
         <v>3</v>
       </c>
-      <c r="D8" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E8" s="1">
-        <v>0</v>
-      </c>
-      <c r="F8" s="1">
-        <v>2</v>
-      </c>
-      <c r="G8" s="1">
+      <c r="D8" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="E8" s="2">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="H8" s="1">
-        <v>2</v>
-      </c>
-      <c r="I8" s="1">
-        <v>1</v>
-      </c>
-      <c r="J8" s="1">
-        <v>100</v>
-      </c>
-      <c r="K8" s="1">
-        <v>1</v>
-      </c>
-      <c r="L8" s="1">
-        <v>9</v>
-      </c>
-      <c r="M8" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" s="1" customFormat="1" customHeight="1" spans="1:14">
+      <c r="F8" s="2">
+        <v>5</v>
+      </c>
+      <c r="G8" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H8" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" s="1" customFormat="1" customHeight="1" spans="3:13">
       <c r="C9" s="1">
         <v>4</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="D9" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E9" s="2">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="F9" s="2">
+        <v>5</v>
+      </c>
+      <c r="G9" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="H9" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="E9" s="1">
+    </row>
+    <row r="10" s="1" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C10" s="1">
+        <v>5</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E10" s="2">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="F9" s="1">
-        <v>4</v>
-      </c>
-      <c r="G9" s="1">
-        <v>1</v>
-      </c>
-      <c r="H9" s="1">
-        <v>4</v>
-      </c>
-      <c r="I9" s="1">
-        <v>2</v>
-      </c>
-      <c r="J9" s="1">
-        <v>1</v>
-      </c>
-      <c r="K9" s="1">
-        <v>1</v>
-      </c>
-      <c r="L9" s="1">
-        <v>9</v>
-      </c>
-      <c r="M9" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10" s="1" customFormat="1" customHeight="1" spans="1:14">
-      <c r="C10" s="1">
-        <v>5</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E10" s="1">
-        <v>2</v>
-      </c>
-      <c r="F10" s="1">
-        <v>5</v>
-      </c>
-      <c r="G10" s="1">
-        <v>1</v>
-      </c>
-      <c r="H10" s="1">
-        <v>4</v>
-      </c>
-      <c r="I10" s="1">
-        <v>2</v>
-      </c>
-      <c r="J10" s="1">
-        <v>1</v>
-      </c>
-      <c r="K10" s="1">
-        <v>1</v>
-      </c>
-      <c r="L10" s="1">
-        <v>9</v>
-      </c>
-      <c r="M10" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="11" s="1" customFormat="1" customHeight="1" spans="1:14">
+      <c r="F10" s="2">
+        <v>5</v>
+      </c>
+      <c r="G10" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="H10" s="9" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:13">
       <c r="C11" s="1">
         <v>6</v>
       </c>
-      <c r="D11" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E11" s="1">
-        <v>3</v>
-      </c>
-      <c r="F11" s="1">
-        <v>6</v>
-      </c>
-      <c r="G11" s="1">
-        <v>1</v>
-      </c>
-      <c r="H11" s="1">
-        <v>4</v>
-      </c>
-      <c r="I11" s="1">
+      <c r="D11" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="E11" s="2">
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="J11" s="1">
-        <v>1</v>
-      </c>
-      <c r="K11" s="1">
-        <v>1</v>
-      </c>
-      <c r="L11" s="1">
-        <v>9</v>
-      </c>
-      <c r="M11" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="12" s="1" customFormat="1" customHeight="1" spans="1:14">
-      <c r="A12" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>0</v>
-      </c>
+      <c r="F11" s="2">
+        <v>5</v>
+      </c>
+      <c r="G11" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H11" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="12" s="1" customFormat="1" customHeight="1" spans="3:13">
       <c r="C12" s="1">
         <v>7</v>
       </c>
-      <c r="D12" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="J12" s="1">
-        <v>10</v>
-      </c>
-      <c r="K12" s="1">
-        <v>6</v>
-      </c>
-      <c r="L12" s="1">
-        <v>9</v>
-      </c>
-      <c r="M12" s="1">
+      <c r="D12" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E12" s="2">
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
-    </row>
-    <row r="13" s="1" customFormat="1" customHeight="1" spans="1:14">
-      <c r="A13" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>0</v>
-      </c>
+      <c r="F12" s="2">
+        <v>5</v>
+      </c>
+      <c r="G12" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H12" s="9" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" s="1" customFormat="1" customHeight="1" spans="3:13">
       <c r="C13" s="1">
         <v>8</v>
       </c>
-      <c r="D13" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="J13" s="1">
-        <v>10</v>
-      </c>
-      <c r="K13" s="1">
-        <v>6</v>
-      </c>
-      <c r="L13" s="1">
-        <v>9</v>
-      </c>
-      <c r="M13" s="1">
+      <c r="D13" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="E13" s="2">
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
-    </row>
-    <row r="14" customHeight="1" spans="1:14">
-      <c r="A14" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>0</v>
-      </c>
+      <c r="F13" s="2">
+        <v>5</v>
+      </c>
+      <c r="G13" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="H13" s="9" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14" customHeight="1" spans="3:13">
       <c r="C14" s="1">
         <v>9</v>
       </c>
-      <c r="D14" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="J14" s="1">
-        <v>10</v>
-      </c>
-      <c r="K14" s="1">
-        <v>6</v>
-      </c>
-      <c r="L14" s="1">
-        <v>9</v>
-      </c>
-      <c r="M14" s="1">
+      <c r="D14" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E14" s="2">
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
-    </row>
-    <row r="15" s="1" customFormat="1" customHeight="1" spans="1:14">
-      <c r="A15" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>0</v>
-      </c>
+      <c r="F14" s="2">
+        <v>5</v>
+      </c>
+      <c r="G14" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H14" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="15" s="1" customFormat="1" customHeight="1" spans="3:13">
       <c r="C15" s="1">
         <v>10</v>
       </c>
-      <c r="D15" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="J15" s="1">
-        <v>100</v>
-      </c>
-      <c r="K15" s="1">
-        <v>6</v>
-      </c>
-      <c r="L15" s="1">
-        <v>9</v>
-      </c>
-      <c r="M15" s="1">
+      <c r="D15" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="E15" s="2">
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
-    </row>
-    <row r="16" s="1" customFormat="1" customHeight="1" spans="1:14">
-      <c r="A16" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>0</v>
-      </c>
+      <c r="F15" s="2">
+        <v>5</v>
+      </c>
+      <c r="G15" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="H15" s="9" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="16" s="1" customFormat="1" customHeight="1" spans="3:13">
       <c r="C16" s="1">
         <v>11</v>
       </c>
-      <c r="D16" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="J16" s="1">
-        <v>100</v>
-      </c>
-      <c r="K16" s="1">
-        <v>6</v>
-      </c>
-      <c r="L16" s="1">
-        <v>9</v>
-      </c>
-      <c r="M16" s="1">
+      <c r="D16" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="E16" s="2">
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
-    </row>
-    <row r="17" s="1" customFormat="1" customHeight="1" spans="1:13">
-      <c r="A17" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>0</v>
-      </c>
+      <c r="F16" s="2">
+        <v>5</v>
+      </c>
+      <c r="G16" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="H16" s="9" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="17" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C17" s="1">
         <v>12</v>
       </c>
-      <c r="D17" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="J17" s="1">
-        <v>100</v>
-      </c>
-      <c r="K17" s="1">
-        <v>6</v>
-      </c>
-      <c r="L17" s="1">
-        <v>9</v>
-      </c>
-      <c r="M17" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="18" s="1" customFormat="1" customHeight="1" spans="1:13">
-      <c r="A18" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>0</v>
-      </c>
+      <c r="D17" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="E17" s="2">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="F17" s="2">
+        <v>5</v>
+      </c>
+      <c r="G17" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H17" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="18" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C18" s="1">
         <v>13</v>
       </c>
-      <c r="D18" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="J18" s="1">
-        <v>1000</v>
-      </c>
-      <c r="K18" s="1">
-        <v>6</v>
-      </c>
-      <c r="L18" s="1">
-        <v>9</v>
-      </c>
-      <c r="M18" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="19" s="1" customFormat="1" customHeight="1" spans="1:13">
-      <c r="A19" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>0</v>
-      </c>
+      <c r="D18" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="E18" s="2">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="F18" s="2">
+        <v>5</v>
+      </c>
+      <c r="G18" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H18" s="9" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="19" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C19" s="1">
         <v>14</v>
       </c>
-      <c r="D19" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="J19" s="1">
-        <v>1000</v>
-      </c>
-      <c r="K19" s="1">
-        <v>6</v>
-      </c>
-      <c r="L19" s="1">
-        <v>9</v>
-      </c>
-      <c r="M19" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="20" s="1" customFormat="1" customHeight="1" spans="1:13">
-      <c r="A20" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>0</v>
-      </c>
+      <c r="D19" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="E19" s="2">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="F19" s="2">
+        <v>5</v>
+      </c>
+      <c r="G19" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="H19" s="9" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="20" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C20" s="1">
         <v>15</v>
       </c>
-      <c r="D20" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="J20" s="1">
-        <v>1000</v>
-      </c>
-      <c r="K20" s="1">
-        <v>6</v>
-      </c>
-      <c r="L20" s="1">
-        <v>9</v>
-      </c>
-      <c r="M20" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="21" s="1" customFormat="1" customHeight="1" spans="1:13">
-      <c r="A21" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>0</v>
-      </c>
+      <c r="D20" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E20" s="2">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="F20" s="2">
+        <v>5</v>
+      </c>
+      <c r="G20" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H20" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="21" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C21" s="1">
         <v>16</v>
       </c>
-      <c r="D21" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="J21" s="1">
-        <v>10000</v>
-      </c>
-      <c r="K21" s="1">
-        <v>6</v>
-      </c>
-      <c r="L21" s="1">
-        <v>9</v>
-      </c>
-      <c r="M21" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="22" s="1" customFormat="1" customHeight="1" spans="1:13">
-      <c r="A22" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>0</v>
-      </c>
+      <c r="D21" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="E21" s="2">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="F21" s="2">
+        <v>5</v>
+      </c>
+      <c r="G21" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="H21" s="9" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C22" s="1">
         <v>17</v>
       </c>
-      <c r="D22" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="J22" s="1">
-        <v>10000</v>
-      </c>
-      <c r="K22" s="1">
-        <v>6</v>
-      </c>
-      <c r="L22" s="1">
-        <v>9</v>
-      </c>
-      <c r="M22" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="23" s="1" customFormat="1" customHeight="1" spans="1:13">
-      <c r="A23" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>0</v>
-      </c>
+      <c r="D22" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E22" s="2">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="F22" s="2">
+        <v>5</v>
+      </c>
+      <c r="G22" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="H22" s="9" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="23" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C23" s="1">
         <v>18</v>
       </c>
-      <c r="D23" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="J23" s="1">
-        <v>10000</v>
-      </c>
-      <c r="K23" s="1">
-        <v>6</v>
-      </c>
-      <c r="L23" s="1">
-        <v>9</v>
-      </c>
-      <c r="M23" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="24" s="1" customFormat="1" customHeight="1" spans="1:13">
-      <c r="A24" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>0</v>
-      </c>
+      <c r="D23" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E23" s="2">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="F23" s="2">
+        <v>5</v>
+      </c>
+      <c r="G23" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H23" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="24" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C24" s="1">
         <v>19</v>
       </c>
-      <c r="D24" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="J24" s="1">
-        <v>10000</v>
-      </c>
-      <c r="K24" s="1">
-        <v>6</v>
-      </c>
-      <c r="L24" s="1">
-        <v>9</v>
-      </c>
-      <c r="M24" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="25" s="1" customFormat="1" customHeight="1" spans="1:13">
-      <c r="A25" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>0</v>
-      </c>
+      <c r="D24" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="E24" s="2">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="F24" s="2">
+        <v>5</v>
+      </c>
+      <c r="G24" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H24" s="9" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="25" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C25" s="1">
         <v>20</v>
       </c>
-      <c r="D25" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="J25" s="1">
-        <v>10000</v>
-      </c>
-      <c r="K25" s="1">
-        <v>6</v>
-      </c>
-      <c r="L25" s="1">
-        <v>9</v>
-      </c>
-      <c r="M25" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="26" s="1" customFormat="1" customHeight="1" spans="1:13">
-      <c r="A26" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>0</v>
-      </c>
+      <c r="D25" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="E25" s="2">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="F25" s="2">
+        <v>5</v>
+      </c>
+      <c r="G25" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="H25" s="9" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="26" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C26" s="1">
         <v>21</v>
       </c>
-      <c r="D26" s="1" t="s">
+      <c r="D26" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="E26" s="2">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="F26" s="2">
+        <v>5</v>
+      </c>
+      <c r="G26" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H26" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="27" customHeight="1" spans="3:8">
+      <c r="C27" s="1">
+        <v>22</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E27" s="2">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="F27" s="2">
+        <v>5</v>
+      </c>
+      <c r="G27" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="H27" s="9" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="28" customHeight="1" spans="3:8">
+      <c r="C28" s="1">
+        <v>23</v>
+      </c>
+      <c r="D28" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="E28" s="2">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="F28" s="2">
+        <v>5</v>
+      </c>
+      <c r="G28" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="H28" s="9" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="29" customHeight="1" spans="3:8">
+      <c r="C29" s="1">
+        <v>24</v>
+      </c>
+      <c r="D29" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="E29" s="2">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="F29" s="2">
+        <v>5</v>
+      </c>
+      <c r="G29" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H29" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="30" customHeight="1" spans="3:8">
+      <c r="C30" s="1">
+        <v>25</v>
+      </c>
+      <c r="D30" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="E30" s="2">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="F30" s="2">
+        <v>5</v>
+      </c>
+      <c r="G30" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H30" s="9" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="31" customHeight="1" spans="3:8">
+      <c r="C31" s="1">
+        <v>26</v>
+      </c>
+      <c r="D31" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E31" s="2">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="F31" s="2">
+        <v>5</v>
+      </c>
+      <c r="G31" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="H31" s="9" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="32" customHeight="1" spans="3:8">
+      <c r="C32" s="1">
+        <v>27</v>
+      </c>
+      <c r="D32" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="E32" s="2">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="F32" s="2">
+        <v>5</v>
+      </c>
+      <c r="G32" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H32" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="33" customHeight="1" spans="3:8">
+      <c r="C33" s="1">
+        <v>28</v>
+      </c>
+      <c r="D33" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="E33" s="2">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="F33" s="2">
+        <v>5</v>
+      </c>
+      <c r="G33" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="H33" s="9" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="34" customHeight="1" spans="3:8">
+      <c r="C34" s="1">
+        <v>29</v>
+      </c>
+      <c r="D34" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="E34" s="2">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="F34" s="2">
+        <v>5</v>
+      </c>
+      <c r="G34" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="H34" s="9" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="35" customHeight="1" spans="3:8">
+      <c r="C35" s="1">
+        <v>30</v>
+      </c>
+      <c r="D35" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="E35" s="2">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="F35" s="2">
+        <v>5</v>
+      </c>
+      <c r="G35" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H35" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="36" customHeight="1" spans="3:8">
+      <c r="C36" s="1">
+        <v>31</v>
+      </c>
+      <c r="D36" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="E36" s="2">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="F36" s="2">
+        <v>5</v>
+      </c>
+      <c r="G36" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H36" s="9" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="37" customHeight="1" spans="3:8">
+      <c r="C37" s="1">
+        <v>32</v>
+      </c>
+      <c r="D37" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="E37" s="2">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="F37" s="2">
+        <v>5</v>
+      </c>
+      <c r="G37" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="H37" s="9" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="38" customHeight="1" spans="3:8">
+      <c r="C38" s="1">
+        <v>33</v>
+      </c>
+      <c r="D38" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="E38" s="2">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="F38" s="2">
+        <v>5</v>
+      </c>
+      <c r="G38" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H38" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="39" customHeight="1" spans="3:8">
+      <c r="C39" s="1">
+        <v>34</v>
+      </c>
+      <c r="D39" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="E39" s="2">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="F39" s="2">
+        <v>5</v>
+      </c>
+      <c r="G39" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="H39" s="9" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="40" customHeight="1" spans="3:8">
+      <c r="C40" s="1">
+        <v>35</v>
+      </c>
+      <c r="D40" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="E40" s="2">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="F40" s="2">
+        <v>5</v>
+      </c>
+      <c r="G40" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="H40" s="9" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="41" customHeight="1" spans="3:8">
+      <c r="C41" s="1">
+        <v>36</v>
+      </c>
+      <c r="D41" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="E41" s="2">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="F41" s="2">
+        <v>5</v>
+      </c>
+      <c r="G41" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H41" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="42" customHeight="1" spans="3:8">
+      <c r="C42" s="1">
         <v>37</v>
       </c>
-      <c r="J26" s="1">
-        <v>10000</v>
-      </c>
-      <c r="K26" s="1">
-        <v>6</v>
-      </c>
-      <c r="L26" s="1">
+      <c r="D42" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="E42" s="2">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="F42" s="2">
+        <v>5</v>
+      </c>
+      <c r="G42" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H42" s="9" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="43" customHeight="1" spans="3:8">
+      <c r="C43" s="1">
+        <v>38</v>
+      </c>
+      <c r="D43" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="E43" s="2">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="F43" s="2">
+        <v>5</v>
+      </c>
+      <c r="G43" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="H43" s="9" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="44" customHeight="1" spans="3:8">
+      <c r="C44" s="1">
+        <v>39</v>
+      </c>
+      <c r="D44" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="E44" s="2">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="F44" s="2">
+        <v>5</v>
+      </c>
+      <c r="G44" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H44" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="45" customHeight="1" spans="3:8">
+      <c r="C45" s="1">
+        <v>40</v>
+      </c>
+      <c r="D45" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="E45" s="2">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="F45" s="2">
+        <v>5</v>
+      </c>
+      <c r="G45" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="H45" s="9" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="46" customHeight="1" spans="3:8">
+      <c r="C46" s="1">
+        <v>41</v>
+      </c>
+      <c r="D46" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="E46" s="2">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="F46" s="2">
+        <v>5</v>
+      </c>
+      <c r="G46" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="H46" s="9" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="47" customHeight="1" spans="3:8">
+      <c r="C47" s="1">
+        <v>42</v>
+      </c>
+      <c r="D47" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="E47" s="2">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="F47" s="2">
+        <v>5</v>
+      </c>
+      <c r="G47" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H47" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="48" customHeight="1" spans="3:8">
+      <c r="C48" s="1">
+        <v>43</v>
+      </c>
+      <c r="D48" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="E48" s="2">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="F48" s="2">
+        <v>5</v>
+      </c>
+      <c r="G48" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H48" s="9" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="49" customHeight="1" spans="3:8">
+      <c r="C49" s="1">
+        <v>44</v>
+      </c>
+      <c r="D49" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="E49" s="2">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="F49" s="2">
+        <v>5</v>
+      </c>
+      <c r="G49" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="H49" s="9" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="50" customHeight="1" spans="3:8">
+      <c r="C50" s="1">
+        <v>45</v>
+      </c>
+      <c r="D50" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="E50" s="2">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="F50" s="2">
+        <v>5</v>
+      </c>
+      <c r="G50" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H50" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="51" customHeight="1" spans="3:8">
+      <c r="C51" s="1">
+        <v>46</v>
+      </c>
+      <c r="D51" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="E51" s="2">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="F51" s="2">
+        <v>5</v>
+      </c>
+      <c r="G51" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="H51" s="9" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="52" customHeight="1" spans="3:8">
+      <c r="C52" s="1">
+        <v>47</v>
+      </c>
+      <c r="D52" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="E52" s="2">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="F52" s="2">
+        <v>5</v>
+      </c>
+      <c r="G52" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="H52" s="9" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="53" customHeight="1" spans="3:8">
+      <c r="C53" s="1">
+        <v>48</v>
+      </c>
+      <c r="D53" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="E53" s="2">
+        <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="M26" s="1">
-        <v>2</v>
-      </c>
+      <c r="F53" s="2">
+        <v>5</v>
+      </c>
+      <c r="G53" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H53" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="54" customHeight="1" spans="3:8">
+      <c r="C54" s="1">
+        <v>49</v>
+      </c>
+      <c r="D54" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="E54" s="2">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="F54" s="2">
+        <v>5</v>
+      </c>
+      <c r="G54" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H54" s="9" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="55" customHeight="1" spans="3:8">
+      <c r="C55" s="1">
+        <v>50</v>
+      </c>
+      <c r="D55" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="E55" s="2">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="F55" s="2">
+        <v>5</v>
+      </c>
+      <c r="G55" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="H55" s="9" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="56" customHeight="1" spans="3:8">
+      <c r="C56" s="1">
+        <v>51</v>
+      </c>
+      <c r="D56" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="E56" s="2">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="F56" s="2">
+        <v>5</v>
+      </c>
+      <c r="G56" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H56" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="57" customHeight="1" spans="3:8">
+      <c r="C57" s="1">
+        <v>52</v>
+      </c>
+      <c r="D57" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="E57" s="2">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="F57" s="2">
+        <v>5</v>
+      </c>
+      <c r="G57" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="H57" s="9" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="58" customHeight="1" spans="3:8">
+      <c r="C58" s="1">
+        <v>53</v>
+      </c>
+      <c r="D58" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E58" s="2">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="F58" s="2">
+        <v>5</v>
+      </c>
+      <c r="G58" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="H58" s="9" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="59" customHeight="1" spans="3:8">
+      <c r="C59" s="1">
+        <v>54</v>
+      </c>
+      <c r="D59" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="E59" s="2">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="F59" s="2">
+        <v>5</v>
+      </c>
+      <c r="G59" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H59" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="60" customHeight="1" spans="3:8">
+      <c r="C60" s="1">
+        <v>55</v>
+      </c>
+      <c r="D60" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="E60" s="2">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="F60" s="2">
+        <v>5</v>
+      </c>
+      <c r="G60" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H60" s="9" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="61" customHeight="1" spans="3:8">
+      <c r="C61" s="1">
+        <v>56</v>
+      </c>
+      <c r="D61" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="E61" s="2">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="F61" s="2">
+        <v>5</v>
+      </c>
+      <c r="G61" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="H61" s="9" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="62" customHeight="1" spans="3:8">
+      <c r="C62" s="1">
+        <v>57</v>
+      </c>
+      <c r="D62" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="E62" s="2">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="F62" s="2">
+        <v>5</v>
+      </c>
+      <c r="G62" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H62" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="63" customHeight="1" spans="3:8">
+      <c r="C63" s="1">
+        <v>58</v>
+      </c>
+      <c r="D63" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="E63" s="2">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="F63" s="2">
+        <v>5</v>
+      </c>
+      <c r="G63" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="H63" s="9" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="64" customHeight="1" spans="3:8">
+      <c r="C64" s="1">
+        <v>59</v>
+      </c>
+      <c r="D64" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="E64" s="2">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="F64" s="2">
+        <v>5</v>
+      </c>
+      <c r="G64" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="H64" s="9" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="65" customHeight="1" spans="3:8">
+      <c r="C65" s="1">
+        <v>60</v>
+      </c>
+      <c r="D65" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="E65" s="2">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="F65" s="2">
+        <v>5</v>
+      </c>
+      <c r="G65" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H65" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="66" customHeight="1" spans="3:8">
+      <c r="C66" s="1">
+        <v>61</v>
+      </c>
+      <c r="D66" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="E66" s="2">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="F66" s="2">
+        <v>5</v>
+      </c>
+      <c r="G66" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H66" s="9" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="67" customHeight="1" spans="3:8">
+      <c r="C67" s="1">
+        <v>62</v>
+      </c>
+      <c r="D67" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="E67" s="2">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="F67" s="2">
+        <v>5</v>
+      </c>
+      <c r="G67" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="H67" s="9" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="68" customHeight="1" spans="3:8">
+      <c r="C68" s="1">
+        <v>63</v>
+      </c>
+      <c r="D68" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="E68" s="2">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="F68" s="2">
+        <v>5</v>
+      </c>
+      <c r="G68" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H68" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="69" customHeight="1" spans="3:8">
+      <c r="C69" s="1">
+        <v>64</v>
+      </c>
+      <c r="D69" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="E69" s="2">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="F69" s="2">
+        <v>5</v>
+      </c>
+      <c r="G69" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="H69" s="9" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="70" customHeight="1" spans="3:8">
+      <c r="C70" s="1">
+        <v>65</v>
+      </c>
+      <c r="D70" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="E70" s="2">
+        <f t="shared" ref="E70:E77" si="1">INT(C70/6)+1</f>
+        <v>11</v>
+      </c>
+      <c r="F70" s="2">
+        <v>5</v>
+      </c>
+      <c r="G70" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="H70" s="9" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="71" customHeight="1" spans="3:8">
+      <c r="C71" s="1">
+        <v>66</v>
+      </c>
+      <c r="D71" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="E71" s="2">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="F71" s="2">
+        <v>5</v>
+      </c>
+      <c r="G71" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H71" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="72" customHeight="1" spans="3:8">
+      <c r="C72" s="1">
+        <v>67</v>
+      </c>
+      <c r="D72" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="E72" s="2">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="F72" s="2">
+        <v>5</v>
+      </c>
+      <c r="G72" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H72" s="9" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="73" customHeight="1" spans="3:8">
+      <c r="C73" s="1">
+        <v>68</v>
+      </c>
+      <c r="D73" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="E73" s="2">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="F73" s="2">
+        <v>5</v>
+      </c>
+      <c r="G73" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="H73" s="9" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="74" customHeight="1" spans="3:8">
+      <c r="C74" s="1">
+        <v>69</v>
+      </c>
+      <c r="D74" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="E74" s="2">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="F74" s="2">
+        <v>5</v>
+      </c>
+      <c r="G74" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H74" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="75" customHeight="1" spans="3:8">
+      <c r="C75" s="1">
+        <v>70</v>
+      </c>
+      <c r="D75" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="E75" s="2">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="F75" s="2">
+        <v>5</v>
+      </c>
+      <c r="G75" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="H75" s="9" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="76" customHeight="1" spans="3:8">
+      <c r="C76" s="1">
+        <v>71</v>
+      </c>
+      <c r="D76" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="E76" s="2">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="F76" s="2">
+        <v>5</v>
+      </c>
+      <c r="G76" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="H76" s="9" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="77" customHeight="1" spans="3:8">
+      <c r="C77" s="1">
+        <v>72</v>
+      </c>
+      <c r="D77" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="E77" s="2">
+        <f t="shared" si="1"/>
+        <v>13</v>
+      </c>
+      <c r="F77" s="2">
+        <v>5</v>
+      </c>
+      <c r="G77" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H77" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="106" customHeight="1" spans="5:8">
+      <c r="E106"/>
+      <c r="F106"/>
+      <c r="G106"/>
+      <c r="H106"/>
+    </row>
+    <row r="107" customHeight="1" spans="5:8">
+      <c r="E107"/>
+      <c r="F107"/>
+      <c r="G107"/>
+      <c r="H107"/>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="N3:N5 C3:F5" errorStyle="warning">
+  <dataValidations count="2">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="M3:M5 C3:D5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="E3:H5" errorStyle="warning">
+      <formula1>COUNTIF($A:$A,E3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Excel/PetConfig.xlsx
+++ b/Excel/PetConfig.xlsx
@@ -1415,8 +1415,8 @@
         <v>10</v>
       </c>
       <c r="E6" s="2">
-        <f t="shared" ref="E6:E69" si="0">INT(C6/6)+1</f>
-        <v>1</v>
+        <f t="shared" ref="E6:E69" si="0">INT((C6-1)/6)+1101</f>
+        <v>1101</v>
       </c>
       <c r="F6" s="2">
         <v>5</v>
@@ -1437,7 +1437,7 @@
       </c>
       <c r="E7" s="2">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>1101</v>
       </c>
       <c r="F7" s="2">
         <v>5</v>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="E8" s="2">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>1101</v>
       </c>
       <c r="F8" s="2">
         <v>5</v>
@@ -1479,7 +1479,7 @@
       </c>
       <c r="E9" s="2">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>1101</v>
       </c>
       <c r="F9" s="2">
         <v>5</v>
@@ -1500,7 +1500,7 @@
       </c>
       <c r="E10" s="2">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>1101</v>
       </c>
       <c r="F10" s="2">
         <v>5</v>
@@ -1521,7 +1521,7 @@
       </c>
       <c r="E11" s="2">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>1101</v>
       </c>
       <c r="F11" s="2">
         <v>5</v>
@@ -1542,7 +1542,7 @@
       </c>
       <c r="E12" s="2">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>1102</v>
       </c>
       <c r="F12" s="2">
         <v>5</v>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="E13" s="2">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>1102</v>
       </c>
       <c r="F13" s="2">
         <v>5</v>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="E14" s="2">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>1102</v>
       </c>
       <c r="F14" s="2">
         <v>5</v>
@@ -1605,7 +1605,7 @@
       </c>
       <c r="E15" s="2">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>1102</v>
       </c>
       <c r="F15" s="2">
         <v>5</v>
@@ -1626,7 +1626,7 @@
       </c>
       <c r="E16" s="2">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>1102</v>
       </c>
       <c r="F16" s="2">
         <v>5</v>
@@ -1647,7 +1647,7 @@
       </c>
       <c r="E17" s="2">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>1102</v>
       </c>
       <c r="F17" s="2">
         <v>5</v>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="E18" s="2">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>1103</v>
       </c>
       <c r="F18" s="2">
         <v>5</v>
@@ -1689,7 +1689,7 @@
       </c>
       <c r="E19" s="2">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>1103</v>
       </c>
       <c r="F19" s="2">
         <v>5</v>
@@ -1710,7 +1710,7 @@
       </c>
       <c r="E20" s="2">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>1103</v>
       </c>
       <c r="F20" s="2">
         <v>5</v>
@@ -1731,7 +1731,7 @@
       </c>
       <c r="E21" s="2">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>1103</v>
       </c>
       <c r="F21" s="2">
         <v>5</v>
@@ -1752,7 +1752,7 @@
       </c>
       <c r="E22" s="2">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>1103</v>
       </c>
       <c r="F22" s="2">
         <v>5</v>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="E23" s="2">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>1103</v>
       </c>
       <c r="F23" s="2">
         <v>5</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="E24" s="2">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>1104</v>
       </c>
       <c r="F24" s="2">
         <v>5</v>
@@ -1815,7 +1815,7 @@
       </c>
       <c r="E25" s="2">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>1104</v>
       </c>
       <c r="F25" s="2">
         <v>5</v>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="E26" s="2">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>1104</v>
       </c>
       <c r="F26" s="2">
         <v>5</v>
@@ -1857,7 +1857,7 @@
       </c>
       <c r="E27" s="2">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>1104</v>
       </c>
       <c r="F27" s="2">
         <v>5</v>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="E28" s="2">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>1104</v>
       </c>
       <c r="F28" s="2">
         <v>5</v>
@@ -1899,7 +1899,7 @@
       </c>
       <c r="E29" s="2">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>1104</v>
       </c>
       <c r="F29" s="2">
         <v>5</v>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="E30" s="2">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>1105</v>
       </c>
       <c r="F30" s="2">
         <v>5</v>
@@ -1941,7 +1941,7 @@
       </c>
       <c r="E31" s="2">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>1105</v>
       </c>
       <c r="F31" s="2">
         <v>5</v>
@@ -1962,7 +1962,7 @@
       </c>
       <c r="E32" s="2">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>1105</v>
       </c>
       <c r="F32" s="2">
         <v>5</v>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="E33" s="2">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>1105</v>
       </c>
       <c r="F33" s="2">
         <v>5</v>
@@ -2004,7 +2004,7 @@
       </c>
       <c r="E34" s="2">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>1105</v>
       </c>
       <c r="F34" s="2">
         <v>5</v>
@@ -2025,7 +2025,7 @@
       </c>
       <c r="E35" s="2">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>1105</v>
       </c>
       <c r="F35" s="2">
         <v>5</v>
@@ -2046,7 +2046,7 @@
       </c>
       <c r="E36" s="2">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>1106</v>
       </c>
       <c r="F36" s="2">
         <v>5</v>
@@ -2067,7 +2067,7 @@
       </c>
       <c r="E37" s="2">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>1106</v>
       </c>
       <c r="F37" s="2">
         <v>5</v>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="E38" s="2">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>1106</v>
       </c>
       <c r="F38" s="2">
         <v>5</v>
@@ -2109,7 +2109,7 @@
       </c>
       <c r="E39" s="2">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>1106</v>
       </c>
       <c r="F39" s="2">
         <v>5</v>
@@ -2130,7 +2130,7 @@
       </c>
       <c r="E40" s="2">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>1106</v>
       </c>
       <c r="F40" s="2">
         <v>5</v>
@@ -2151,7 +2151,7 @@
       </c>
       <c r="E41" s="2">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>1106</v>
       </c>
       <c r="F41" s="2">
         <v>5</v>
@@ -2172,7 +2172,7 @@
       </c>
       <c r="E42" s="2">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>1107</v>
       </c>
       <c r="F42" s="2">
         <v>5</v>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="E43" s="2">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>1107</v>
       </c>
       <c r="F43" s="2">
         <v>5</v>
@@ -2214,7 +2214,7 @@
       </c>
       <c r="E44" s="2">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>1107</v>
       </c>
       <c r="F44" s="2">
         <v>5</v>
@@ -2235,7 +2235,7 @@
       </c>
       <c r="E45" s="2">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>1107</v>
       </c>
       <c r="F45" s="2">
         <v>5</v>
@@ -2256,7 +2256,7 @@
       </c>
       <c r="E46" s="2">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>1107</v>
       </c>
       <c r="F46" s="2">
         <v>5</v>
@@ -2277,7 +2277,7 @@
       </c>
       <c r="E47" s="2">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>1107</v>
       </c>
       <c r="F47" s="2">
         <v>5</v>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="E48" s="2">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>1108</v>
       </c>
       <c r="F48" s="2">
         <v>5</v>
@@ -2319,7 +2319,7 @@
       </c>
       <c r="E49" s="2">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>1108</v>
       </c>
       <c r="F49" s="2">
         <v>5</v>
@@ -2340,7 +2340,7 @@
       </c>
       <c r="E50" s="2">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>1108</v>
       </c>
       <c r="F50" s="2">
         <v>5</v>
@@ -2361,7 +2361,7 @@
       </c>
       <c r="E51" s="2">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>1108</v>
       </c>
       <c r="F51" s="2">
         <v>5</v>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="E52" s="2">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>1108</v>
       </c>
       <c r="F52" s="2">
         <v>5</v>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="E53" s="2">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>1108</v>
       </c>
       <c r="F53" s="2">
         <v>5</v>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="E54" s="2">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>1109</v>
       </c>
       <c r="F54" s="2">
         <v>5</v>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="E55" s="2">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>1109</v>
       </c>
       <c r="F55" s="2">
         <v>5</v>
@@ -2466,7 +2466,7 @@
       </c>
       <c r="E56" s="2">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>1109</v>
       </c>
       <c r="F56" s="2">
         <v>5</v>
@@ -2487,7 +2487,7 @@
       </c>
       <c r="E57" s="2">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>1109</v>
       </c>
       <c r="F57" s="2">
         <v>5</v>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="E58" s="2">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>1109</v>
       </c>
       <c r="F58" s="2">
         <v>5</v>
@@ -2529,7 +2529,7 @@
       </c>
       <c r="E59" s="2">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>1109</v>
       </c>
       <c r="F59" s="2">
         <v>5</v>
@@ -2550,7 +2550,7 @@
       </c>
       <c r="E60" s="2">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>1110</v>
       </c>
       <c r="F60" s="2">
         <v>5</v>
@@ -2571,7 +2571,7 @@
       </c>
       <c r="E61" s="2">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>1110</v>
       </c>
       <c r="F61" s="2">
         <v>5</v>
@@ -2592,7 +2592,7 @@
       </c>
       <c r="E62" s="2">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>1110</v>
       </c>
       <c r="F62" s="2">
         <v>5</v>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="E63" s="2">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>1110</v>
       </c>
       <c r="F63" s="2">
         <v>5</v>
@@ -2634,7 +2634,7 @@
       </c>
       <c r="E64" s="2">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>1110</v>
       </c>
       <c r="F64" s="2">
         <v>5</v>
@@ -2655,7 +2655,7 @@
       </c>
       <c r="E65" s="2">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>1110</v>
       </c>
       <c r="F65" s="2">
         <v>5</v>
@@ -2676,7 +2676,7 @@
       </c>
       <c r="E66" s="2">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>1111</v>
       </c>
       <c r="F66" s="2">
         <v>5</v>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="E67" s="2">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>1111</v>
       </c>
       <c r="F67" s="2">
         <v>5</v>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="E68" s="2">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>1111</v>
       </c>
       <c r="F68" s="2">
         <v>5</v>
@@ -2739,7 +2739,7 @@
       </c>
       <c r="E69" s="2">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>1111</v>
       </c>
       <c r="F69" s="2">
         <v>5</v>
@@ -2759,8 +2759,8 @@
         <v>80</v>
       </c>
       <c r="E70" s="2">
-        <f t="shared" ref="E70:E77" si="1">INT(C70/6)+1</f>
-        <v>11</v>
+        <f t="shared" ref="E70:E77" si="1">INT((C70-1)/6)+1101</f>
+        <v>1111</v>
       </c>
       <c r="F70" s="2">
         <v>5</v>
@@ -2781,7 +2781,7 @@
       </c>
       <c r="E71" s="2">
         <f t="shared" si="1"/>
-        <v>12</v>
+        <v>1111</v>
       </c>
       <c r="F71" s="2">
         <v>5</v>
@@ -2802,7 +2802,7 @@
       </c>
       <c r="E72" s="2">
         <f t="shared" si="1"/>
-        <v>12</v>
+        <v>1112</v>
       </c>
       <c r="F72" s="2">
         <v>5</v>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="E73" s="2">
         <f t="shared" si="1"/>
-        <v>12</v>
+        <v>1112</v>
       </c>
       <c r="F73" s="2">
         <v>5</v>
@@ -2844,7 +2844,7 @@
       </c>
       <c r="E74" s="2">
         <f t="shared" si="1"/>
-        <v>12</v>
+        <v>1112</v>
       </c>
       <c r="F74" s="2">
         <v>5</v>
@@ -2865,7 +2865,7 @@
       </c>
       <c r="E75" s="2">
         <f t="shared" si="1"/>
-        <v>12</v>
+        <v>1112</v>
       </c>
       <c r="F75" s="2">
         <v>5</v>
@@ -2886,7 +2886,7 @@
       </c>
       <c r="E76" s="2">
         <f t="shared" si="1"/>
-        <v>12</v>
+        <v>1112</v>
       </c>
       <c r="F76" s="2">
         <v>5</v>
@@ -2907,7 +2907,7 @@
       </c>
       <c r="E77" s="2">
         <f t="shared" si="1"/>
-        <v>13</v>
+        <v>1112</v>
       </c>
       <c r="F77" s="2">
         <v>5</v>

--- a/Excel/PetConfig.xlsx
+++ b/Excel/PetConfig.xlsx
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="94">
   <si>
     <t>_ID</t>
   </si>
@@ -95,40 +95,37 @@
     <t>狼宝宝</t>
   </si>
   <si>
-    <t>4,3</t>
-  </si>
-  <si>
-    <t>20,10</t>
+    <t>1,1001</t>
+  </si>
+  <si>
+    <t>1000,5</t>
   </si>
   <si>
     <t>骷髅宝宝</t>
   </si>
   <si>
-    <t>4,2</t>
-  </si>
-  <si>
-    <t>20,5</t>
+    <t>2,1002</t>
+  </si>
+  <si>
+    <t>100,5</t>
   </si>
   <si>
     <t>兽人宝宝</t>
   </si>
   <si>
-    <t>10,5</t>
+    <t>3,1003</t>
   </si>
   <si>
     <t>蜘蛛宝宝</t>
   </si>
   <si>
-    <t>4,1</t>
-  </si>
-  <si>
-    <t>10,200</t>
+    <t>5000,10</t>
   </si>
   <si>
     <t>岩蝎宝宝</t>
   </si>
   <si>
-    <t>10,1</t>
+    <t>200,10</t>
   </si>
   <si>
     <t>鬃狮宝宝</t>
@@ -137,34 +134,58 @@
     <t>毒蛆宝宝</t>
   </si>
   <si>
+    <t>10000,15</t>
+  </si>
+  <si>
     <t>蜈蚣宝宝</t>
   </si>
   <si>
+    <t>400,15</t>
+  </si>
+  <si>
     <t>双头宝宝</t>
   </si>
   <si>
     <t>蛛王宝宝</t>
   </si>
   <si>
+    <t>50000,20</t>
+  </si>
+  <si>
     <t>蛇宝宝</t>
   </si>
   <si>
+    <t>800,20</t>
+  </si>
+  <si>
     <t>巨鳄宝宝</t>
   </si>
   <si>
     <t>乌鸦宝宝</t>
   </si>
   <si>
+    <t>100000,20</t>
+  </si>
+  <si>
     <t>行尸宝宝</t>
   </si>
   <si>
+    <t>1500,20</t>
+  </si>
+  <si>
     <t>尸鬼宝宝</t>
   </si>
   <si>
     <t>蝙蝠宝宝</t>
   </si>
   <si>
+    <t>200000,25</t>
+  </si>
+  <si>
     <t>尸魔宝宝</t>
+  </si>
+  <si>
+    <t>3000,25</t>
   </si>
   <si>
     <t>尸卫宝宝</t>
@@ -1464,10 +1485,10 @@
         <v>5</v>
       </c>
       <c r="G8" s="9" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="H8" s="9" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="3:13">
@@ -1485,10 +1506,10 @@
         <v>5</v>
       </c>
       <c r="G9" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H9" s="9" t="s">
         <v>19</v>
-      </c>
-      <c r="H9" s="9" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="3:13">
@@ -1496,7 +1517,7 @@
         <v>5</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E10" s="2">
         <f t="shared" si="0"/>
@@ -1509,7 +1530,7 @@
         <v>14</v>
       </c>
       <c r="H10" s="9" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="3:13">
@@ -1517,7 +1538,7 @@
         <v>6</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E11" s="2">
         <f t="shared" si="0"/>
@@ -1527,10 +1548,10 @@
         <v>5</v>
       </c>
       <c r="G11" s="9" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="H11" s="9" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="3:13">
@@ -1538,7 +1559,7 @@
         <v>7</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E12" s="2">
         <f t="shared" si="0"/>
@@ -1551,7 +1572,7 @@
         <v>11</v>
       </c>
       <c r="H12" s="9" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" customHeight="1" spans="3:13">
@@ -1572,7 +1593,7 @@
         <v>14</v>
       </c>
       <c r="H13" s="9" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="3:13">
@@ -1580,20 +1601,20 @@
         <v>9</v>
       </c>
       <c r="D14" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="E14" s="2">
+        <f t="shared" si="0"/>
+        <v>1102</v>
+      </c>
+      <c r="F14" s="2">
+        <v>5</v>
+      </c>
+      <c r="G14" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H14" s="9" t="s">
         <v>26</v>
-      </c>
-      <c r="E14" s="2">
-        <f t="shared" si="0"/>
-        <v>1102</v>
-      </c>
-      <c r="F14" s="2">
-        <v>5</v>
-      </c>
-      <c r="G14" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="H14" s="9" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" customHeight="1" spans="3:13">
@@ -1601,7 +1622,7 @@
         <v>10</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E15" s="2">
         <f t="shared" si="0"/>
@@ -1611,10 +1632,10 @@
         <v>5</v>
       </c>
       <c r="G15" s="9" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="H15" s="9" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" customHeight="1" spans="3:13">
@@ -1622,7 +1643,7 @@
         <v>11</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E16" s="2">
         <f t="shared" si="0"/>
@@ -1635,7 +1656,7 @@
         <v>14</v>
       </c>
       <c r="H16" s="9" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" customHeight="1" spans="3:8">
@@ -1643,7 +1664,7 @@
         <v>12</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E17" s="2">
         <f t="shared" si="0"/>
@@ -1653,10 +1674,10 @@
         <v>5</v>
       </c>
       <c r="G17" s="9" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="H17" s="9" t="s">
-        <v>17</v>
+        <v>31</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" customHeight="1" spans="3:8">
@@ -1664,7 +1685,7 @@
         <v>13</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="E18" s="2">
         <f t="shared" si="0"/>
@@ -1677,7 +1698,7 @@
         <v>11</v>
       </c>
       <c r="H18" s="9" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" customHeight="1" spans="3:8">
@@ -1685,7 +1706,7 @@
         <v>14</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="E19" s="2">
         <f t="shared" si="0"/>
@@ -1698,7 +1719,7 @@
         <v>14</v>
       </c>
       <c r="H19" s="9" t="s">
-        <v>15</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20" s="1" customFormat="1" customHeight="1" spans="3:8">
@@ -1706,7 +1727,7 @@
         <v>15</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="E20" s="2">
         <f t="shared" si="0"/>
@@ -1716,10 +1737,10 @@
         <v>5</v>
       </c>
       <c r="G20" s="9" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="H20" s="9" t="s">
-        <v>17</v>
+        <v>36</v>
       </c>
     </row>
     <row r="21" s="1" customFormat="1" customHeight="1" spans="3:8">
@@ -1727,7 +1748,7 @@
         <v>16</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="E21" s="2">
         <f t="shared" si="0"/>
@@ -1737,10 +1758,10 @@
         <v>5</v>
       </c>
       <c r="G21" s="9" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="H21" s="9" t="s">
-        <v>20</v>
+        <v>39</v>
       </c>
     </row>
     <row r="22" s="1" customFormat="1" customHeight="1" spans="3:8">
@@ -1748,7 +1769,7 @@
         <v>17</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="E22" s="2">
         <f t="shared" si="0"/>
@@ -1761,7 +1782,7 @@
         <v>14</v>
       </c>
       <c r="H22" s="9" t="s">
-        <v>22</v>
+        <v>41</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" customHeight="1" spans="3:8">
@@ -1769,7 +1790,7 @@
         <v>18</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="E23" s="2">
         <f t="shared" si="0"/>
@@ -1779,10 +1800,10 @@
         <v>5</v>
       </c>
       <c r="G23" s="9" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="H23" s="9" t="s">
-        <v>17</v>
+        <v>41</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" customHeight="1" spans="3:8">
@@ -1790,7 +1811,7 @@
         <v>19</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="E24" s="2">
         <f t="shared" si="0"/>
@@ -1811,7 +1832,7 @@
         <v>20</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="E25" s="2">
         <f t="shared" si="0"/>
@@ -1832,7 +1853,7 @@
         <v>21</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="E26" s="2">
         <f t="shared" si="0"/>
@@ -1842,10 +1863,10 @@
         <v>5</v>
       </c>
       <c r="G26" s="9" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="H26" s="9" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="27" customHeight="1" spans="3:8">
@@ -1853,7 +1874,7 @@
         <v>22</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="E27" s="2">
         <f t="shared" si="0"/>
@@ -1863,10 +1884,10 @@
         <v>5</v>
       </c>
       <c r="G27" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H27" s="9" t="s">
         <v>19</v>
-      </c>
-      <c r="H27" s="9" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="28" customHeight="1" spans="3:8">
@@ -1874,7 +1895,7 @@
         <v>23</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="E28" s="2">
         <f t="shared" si="0"/>
@@ -1887,7 +1908,7 @@
         <v>14</v>
       </c>
       <c r="H28" s="9" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="29" customHeight="1" spans="3:8">
@@ -1895,7 +1916,7 @@
         <v>24</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="E29" s="2">
         <f t="shared" si="0"/>
@@ -1905,10 +1926,10 @@
         <v>5</v>
       </c>
       <c r="G29" s="9" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="H29" s="9" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="30" customHeight="1" spans="3:8">
@@ -1916,7 +1937,7 @@
         <v>25</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="E30" s="2">
         <f t="shared" si="0"/>
@@ -1937,7 +1958,7 @@
         <v>26</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="E31" s="2">
         <f t="shared" si="0"/>
@@ -1958,7 +1979,7 @@
         <v>27</v>
       </c>
       <c r="D32" s="8" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="E32" s="2">
         <f t="shared" si="0"/>
@@ -1968,10 +1989,10 @@
         <v>5</v>
       </c>
       <c r="G32" s="9" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="H32" s="9" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="33" customHeight="1" spans="3:8">
@@ -1979,7 +2000,7 @@
         <v>28</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="E33" s="2">
         <f t="shared" si="0"/>
@@ -1989,10 +2010,10 @@
         <v>5</v>
       </c>
       <c r="G33" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H33" s="9" t="s">
         <v>19</v>
-      </c>
-      <c r="H33" s="9" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="34" customHeight="1" spans="3:8">
@@ -2000,7 +2021,7 @@
         <v>29</v>
       </c>
       <c r="D34" s="8" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="E34" s="2">
         <f t="shared" si="0"/>
@@ -2013,7 +2034,7 @@
         <v>14</v>
       </c>
       <c r="H34" s="9" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="35" customHeight="1" spans="3:8">
@@ -2021,7 +2042,7 @@
         <v>30</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="E35" s="2">
         <f t="shared" si="0"/>
@@ -2031,10 +2052,10 @@
         <v>5</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="H35" s="9" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="36" customHeight="1" spans="3:8">
@@ -2042,7 +2063,7 @@
         <v>31</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="E36" s="2">
         <f t="shared" si="0"/>
@@ -2063,7 +2084,7 @@
         <v>32</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="E37" s="2">
         <f t="shared" si="0"/>
@@ -2084,7 +2105,7 @@
         <v>33</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="E38" s="2">
         <f t="shared" si="0"/>
@@ -2094,10 +2115,10 @@
         <v>5</v>
       </c>
       <c r="G38" s="9" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="H38" s="9" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="39" customHeight="1" spans="3:8">
@@ -2105,7 +2126,7 @@
         <v>34</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="E39" s="2">
         <f t="shared" si="0"/>
@@ -2115,10 +2136,10 @@
         <v>5</v>
       </c>
       <c r="G39" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H39" s="9" t="s">
         <v>19</v>
-      </c>
-      <c r="H39" s="9" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="40" customHeight="1" spans="3:8">
@@ -2126,7 +2147,7 @@
         <v>35</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="E40" s="2">
         <f t="shared" si="0"/>
@@ -2139,7 +2160,7 @@
         <v>14</v>
       </c>
       <c r="H40" s="9" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="41" customHeight="1" spans="3:8">
@@ -2147,7 +2168,7 @@
         <v>36</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="E41" s="2">
         <f t="shared" si="0"/>
@@ -2157,10 +2178,10 @@
         <v>5</v>
       </c>
       <c r="G41" s="9" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="H41" s="9" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="42" customHeight="1" spans="3:8">
@@ -2168,7 +2189,7 @@
         <v>37</v>
       </c>
       <c r="D42" s="7" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="E42" s="2">
         <f t="shared" si="0"/>
@@ -2189,7 +2210,7 @@
         <v>38</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="E43" s="2">
         <f t="shared" si="0"/>
@@ -2210,7 +2231,7 @@
         <v>39</v>
       </c>
       <c r="D44" s="7" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="E44" s="2">
         <f t="shared" si="0"/>
@@ -2220,10 +2241,10 @@
         <v>5</v>
       </c>
       <c r="G44" s="9" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="H44" s="9" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="45" customHeight="1" spans="3:8">
@@ -2231,7 +2252,7 @@
         <v>40</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="E45" s="2">
         <f t="shared" si="0"/>
@@ -2241,10 +2262,10 @@
         <v>5</v>
       </c>
       <c r="G45" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H45" s="9" t="s">
         <v>19</v>
-      </c>
-      <c r="H45" s="9" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="46" customHeight="1" spans="3:8">
@@ -2252,7 +2273,7 @@
         <v>41</v>
       </c>
       <c r="D46" s="8" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="E46" s="2">
         <f t="shared" si="0"/>
@@ -2265,7 +2286,7 @@
         <v>14</v>
       </c>
       <c r="H46" s="9" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="47" customHeight="1" spans="3:8">
@@ -2273,7 +2294,7 @@
         <v>42</v>
       </c>
       <c r="D47" s="7" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="E47" s="2">
         <f t="shared" si="0"/>
@@ -2283,10 +2304,10 @@
         <v>5</v>
       </c>
       <c r="G47" s="9" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="H47" s="9" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="48" customHeight="1" spans="3:8">
@@ -2294,7 +2315,7 @@
         <v>43</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="E48" s="2">
         <f t="shared" si="0"/>
@@ -2315,7 +2336,7 @@
         <v>44</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="E49" s="2">
         <f t="shared" si="0"/>
@@ -2336,7 +2357,7 @@
         <v>45</v>
       </c>
       <c r="D50" s="5" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="E50" s="2">
         <f t="shared" si="0"/>
@@ -2346,10 +2367,10 @@
         <v>5</v>
       </c>
       <c r="G50" s="9" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="H50" s="9" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="51" customHeight="1" spans="3:8">
@@ -2357,7 +2378,7 @@
         <v>46</v>
       </c>
       <c r="D51" s="8" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="E51" s="2">
         <f t="shared" si="0"/>
@@ -2367,10 +2388,10 @@
         <v>5</v>
       </c>
       <c r="G51" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H51" s="9" t="s">
         <v>19</v>
-      </c>
-      <c r="H51" s="9" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="52" customHeight="1" spans="3:8">
@@ -2378,7 +2399,7 @@
         <v>47</v>
       </c>
       <c r="D52" s="5" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="E52" s="2">
         <f t="shared" si="0"/>
@@ -2391,7 +2412,7 @@
         <v>14</v>
       </c>
       <c r="H52" s="9" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="53" customHeight="1" spans="3:8">
@@ -2399,7 +2420,7 @@
         <v>48</v>
       </c>
       <c r="D53" s="6" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="E53" s="2">
         <f t="shared" si="0"/>
@@ -2409,10 +2430,10 @@
         <v>5</v>
       </c>
       <c r="G53" s="9" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="H53" s="9" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="54" customHeight="1" spans="3:8">
@@ -2420,7 +2441,7 @@
         <v>49</v>
       </c>
       <c r="D54" s="5" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="E54" s="2">
         <f t="shared" si="0"/>
@@ -2441,7 +2462,7 @@
         <v>50</v>
       </c>
       <c r="D55" s="5" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="E55" s="2">
         <f t="shared" si="0"/>
@@ -2462,7 +2483,7 @@
         <v>51</v>
       </c>
       <c r="D56" s="5" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="E56" s="2">
         <f t="shared" si="0"/>
@@ -2472,10 +2493,10 @@
         <v>5</v>
       </c>
       <c r="G56" s="9" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="H56" s="9" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="57" customHeight="1" spans="3:8">
@@ -2483,7 +2504,7 @@
         <v>52</v>
       </c>
       <c r="D57" s="5" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="E57" s="2">
         <f t="shared" si="0"/>
@@ -2493,10 +2514,10 @@
         <v>5</v>
       </c>
       <c r="G57" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H57" s="9" t="s">
         <v>19</v>
-      </c>
-      <c r="H57" s="9" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="58" customHeight="1" spans="3:8">
@@ -2504,7 +2525,7 @@
         <v>53</v>
       </c>
       <c r="D58" s="5" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="E58" s="2">
         <f t="shared" si="0"/>
@@ -2517,7 +2538,7 @@
         <v>14</v>
       </c>
       <c r="H58" s="9" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="59" customHeight="1" spans="3:8">
@@ -2525,7 +2546,7 @@
         <v>54</v>
       </c>
       <c r="D59" s="6" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="E59" s="2">
         <f t="shared" si="0"/>
@@ -2535,10 +2556,10 @@
         <v>5</v>
       </c>
       <c r="G59" s="9" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="H59" s="9" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="60" customHeight="1" spans="3:8">
@@ -2546,7 +2567,7 @@
         <v>55</v>
       </c>
       <c r="D60" s="5" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="E60" s="2">
         <f t="shared" si="0"/>
@@ -2567,7 +2588,7 @@
         <v>56</v>
       </c>
       <c r="D61" s="5" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="E61" s="2">
         <f t="shared" si="0"/>
@@ -2588,7 +2609,7 @@
         <v>57</v>
       </c>
       <c r="D62" s="5" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="E62" s="2">
         <f t="shared" si="0"/>
@@ -2598,10 +2619,10 @@
         <v>5</v>
       </c>
       <c r="G62" s="9" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="H62" s="9" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="63" customHeight="1" spans="3:8">
@@ -2609,7 +2630,7 @@
         <v>58</v>
       </c>
       <c r="D63" s="7" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="E63" s="2">
         <f t="shared" si="0"/>
@@ -2619,10 +2640,10 @@
         <v>5</v>
       </c>
       <c r="G63" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H63" s="9" t="s">
         <v>19</v>
-      </c>
-      <c r="H63" s="9" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="64" customHeight="1" spans="3:8">
@@ -2630,7 +2651,7 @@
         <v>59</v>
       </c>
       <c r="D64" s="5" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="E64" s="2">
         <f t="shared" si="0"/>
@@ -2643,7 +2664,7 @@
         <v>14</v>
       </c>
       <c r="H64" s="9" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="65" customHeight="1" spans="3:8">
@@ -2651,7 +2672,7 @@
         <v>60</v>
       </c>
       <c r="D65" s="6" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="E65" s="2">
         <f t="shared" si="0"/>
@@ -2661,10 +2682,10 @@
         <v>5</v>
       </c>
       <c r="G65" s="9" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="H65" s="9" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="66" customHeight="1" spans="3:8">
@@ -2672,7 +2693,7 @@
         <v>61</v>
       </c>
       <c r="D66" s="5" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="E66" s="2">
         <f t="shared" si="0"/>
@@ -2693,7 +2714,7 @@
         <v>62</v>
       </c>
       <c r="D67" s="8" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="E67" s="2">
         <f t="shared" si="0"/>
@@ -2714,7 +2735,7 @@
         <v>63</v>
       </c>
       <c r="D68" s="5" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="E68" s="2">
         <f t="shared" si="0"/>
@@ -2724,10 +2745,10 @@
         <v>5</v>
       </c>
       <c r="G68" s="9" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="H68" s="9" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="69" customHeight="1" spans="3:8">
@@ -2735,7 +2756,7 @@
         <v>64</v>
       </c>
       <c r="D69" s="5" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="E69" s="2">
         <f t="shared" si="0"/>
@@ -2745,10 +2766,10 @@
         <v>5</v>
       </c>
       <c r="G69" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H69" s="9" t="s">
         <v>19</v>
-      </c>
-      <c r="H69" s="9" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="70" customHeight="1" spans="3:8">
@@ -2756,7 +2777,7 @@
         <v>65</v>
       </c>
       <c r="D70" s="5" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="E70" s="2">
         <f t="shared" ref="E70:E77" si="1">INT((C70-1)/6)+1101</f>
@@ -2769,7 +2790,7 @@
         <v>14</v>
       </c>
       <c r="H70" s="9" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="71" customHeight="1" spans="3:8">
@@ -2777,7 +2798,7 @@
         <v>66</v>
       </c>
       <c r="D71" s="6" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="E71" s="2">
         <f t="shared" si="1"/>
@@ -2787,10 +2808,10 @@
         <v>5</v>
       </c>
       <c r="G71" s="9" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="H71" s="9" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="72" customHeight="1" spans="3:8">
@@ -2798,7 +2819,7 @@
         <v>67</v>
       </c>
       <c r="D72" s="5" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="E72" s="2">
         <f t="shared" si="1"/>
@@ -2819,7 +2840,7 @@
         <v>68</v>
       </c>
       <c r="D73" s="5" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="E73" s="2">
         <f t="shared" si="1"/>
@@ -2840,7 +2861,7 @@
         <v>69</v>
       </c>
       <c r="D74" s="5" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="E74" s="2">
         <f t="shared" si="1"/>
@@ -2850,10 +2871,10 @@
         <v>5</v>
       </c>
       <c r="G74" s="9" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="H74" s="9" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="75" customHeight="1" spans="3:8">
@@ -2861,7 +2882,7 @@
         <v>70</v>
       </c>
       <c r="D75" s="5" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="E75" s="2">
         <f t="shared" si="1"/>
@@ -2871,10 +2892,10 @@
         <v>5</v>
       </c>
       <c r="G75" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H75" s="9" t="s">
         <v>19</v>
-      </c>
-      <c r="H75" s="9" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="76" customHeight="1" spans="3:8">
@@ -2882,7 +2903,7 @@
         <v>71</v>
       </c>
       <c r="D76" s="7" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="E76" s="2">
         <f t="shared" si="1"/>
@@ -2895,7 +2916,7 @@
         <v>14</v>
       </c>
       <c r="H76" s="9" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="77" customHeight="1" spans="3:8">
@@ -2903,7 +2924,7 @@
         <v>72</v>
       </c>
       <c r="D77" s="6" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="E77" s="2">
         <f t="shared" si="1"/>
@@ -2913,10 +2934,10 @@
         <v>5</v>
       </c>
       <c r="G77" s="9" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="H77" s="9" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="106" customHeight="1" spans="5:8">

--- a/Excel/PetConfig.xlsx
+++ b/Excel/PetConfig.xlsx
@@ -60,7 +60,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="107">
+  <si>
+    <t>#</t>
+  </si>
   <si>
     <t>_ID</t>
   </si>
@@ -80,6 +83,70 @@
     <t>CardVueList</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Perk</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>‌</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+      </rPr>
+      <t>AtrIdList</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Perk</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>‌</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+      </rPr>
+      <t>AtrVueList</t>
+    </r>
+  </si>
+  <si>
     <t>Id</t>
   </si>
   <si>
@@ -92,6 +159,9 @@
     <t>int[]</t>
   </si>
   <si>
+    <t>double[]</t>
+  </si>
+  <si>
     <t>狼宝宝</t>
   </si>
   <si>
@@ -167,13 +237,40 @@
     <t>100000,20</t>
   </si>
   <si>
+    <t>1003,15</t>
+  </si>
+  <si>
+    <t>20,20</t>
+  </si>
+  <si>
+    <t>生命，回复加成</t>
+  </si>
+  <si>
     <t>行尸宝宝</t>
   </si>
   <si>
     <t>1500,20</t>
   </si>
   <si>
+    <t>1002,28</t>
+  </si>
+  <si>
+    <t>20,10</t>
+  </si>
+  <si>
+    <t>防御，免伤</t>
+  </si>
+  <si>
     <t>尸鬼宝宝</t>
+  </si>
+  <si>
+    <t>1001,11</t>
+  </si>
+  <si>
+    <t>20,5</t>
+  </si>
+  <si>
+    <t>攻击，攻速</t>
   </si>
   <si>
     <t>蝙蝠宝宝</t>
@@ -369,12 +466,6 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <b/>
       <sz val="9"/>
       <color theme="1"/>
@@ -382,11 +473,11 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
-      <sz val="10"/>
+      <sz val="9"/>
       <color theme="1"/>
       <name val="等线"/>
       <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -535,6 +626,13 @@
     <font>
       <b/>
       <sz val="9"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -868,144 +966,140 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1018,7 +1112,8 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1338,1619 +1433,1740 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:M107"/>
+  <dimension ref="C1:M107"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="1"/>
     <col min="4" max="4" width="12.8333333333333" style="1" customWidth="1"/>
-    <col min="5" max="6" width="13" style="2" customWidth="1"/>
-    <col min="7" max="7" width="14.1666666666667" style="2" customWidth="1"/>
-    <col min="8" max="8" width="13" style="2" customWidth="1"/>
-    <col min="9" max="9" width="13.5" style="1" customWidth="1"/>
-    <col min="10" max="10" width="9.625" style="1" customWidth="1"/>
+    <col min="5" max="6" width="13" style="1" customWidth="1"/>
+    <col min="7" max="7" width="14.1666666666667" style="1" customWidth="1"/>
+    <col min="8" max="8" width="13" style="1" customWidth="1"/>
+    <col min="9" max="9" width="14.8333333333333" style="1" customWidth="1"/>
+    <col min="10" max="10" width="14.25" style="1" customWidth="1"/>
     <col min="11" max="12" width="13" style="1" customWidth="1"/>
     <col min="13" max="13" width="17" style="1" customWidth="1"/>
     <col min="14" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
+    <row r="1" customHeight="1" spans="3:13">
+      <c r="K1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" customHeight="1" spans="3:13">
+      <c r="K2" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
     <row r="3" s="1" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C3" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="D3" s="3" t="s">
+      <c r="C3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="D3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="E3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="F3" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="H3" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="I3" s="3"/>
-      <c r="J3" s="3"/>
-      <c r="K3" s="3"/>
-      <c r="L3" s="3"/>
-      <c r="M3" s="3"/>
+      <c r="G3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K3" s="2"/>
+      <c r="L3" s="2"/>
+      <c r="M3" s="2"/>
     </row>
     <row r="4" s="1" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H4" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D4" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="I4" s="3"/>
-      <c r="J4" s="3"/>
-      <c r="K4" s="3"/>
-      <c r="L4" s="3"/>
-      <c r="M4" s="3"/>
+      <c r="I4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K4" s="2"/>
+      <c r="L4" s="2"/>
+      <c r="M4" s="2"/>
     </row>
     <row r="5" s="1" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C5" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="I5" s="3"/>
-      <c r="J5" s="3"/>
-      <c r="K5" s="3"/>
-      <c r="L5" s="3"/>
-      <c r="M5" s="3"/>
+      <c r="C5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="K5" s="2"/>
+      <c r="L5" s="2"/>
+      <c r="M5" s="2"/>
     </row>
     <row r="6" s="1" customFormat="1" customHeight="1" spans="3:13">
       <c r="C6" s="1">
         <v>1</v>
       </c>
-      <c r="D6" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="E6" s="2">
+      <c r="D6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6" s="1">
         <f t="shared" ref="E6:E69" si="0">INT((C6-1)/6)+1101</f>
         <v>1101</v>
       </c>
-      <c r="F6" s="2">
-        <v>5</v>
-      </c>
-      <c r="G6" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="H6" s="9" t="s">
-        <v>12</v>
+      <c r="F6" s="1">
+        <v>5</v>
+      </c>
+      <c r="G6" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="H6" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="I6" s="1">
+        <v>1003</v>
+      </c>
+      <c r="J6" s="1">
+        <v>5</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="3:13">
       <c r="C7" s="1">
         <v>2</v>
       </c>
-      <c r="D7" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="E7" s="2">
+      <c r="D7" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E7" s="1">
         <f t="shared" si="0"/>
         <v>1101</v>
       </c>
-      <c r="F7" s="2">
-        <v>5</v>
-      </c>
-      <c r="G7" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="H7" s="9" t="s">
-        <v>15</v>
+      <c r="F7" s="1">
+        <v>5</v>
+      </c>
+      <c r="G7" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I7" s="1">
+        <v>1002</v>
+      </c>
+      <c r="J7" s="1">
+        <v>5</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="3:13">
       <c r="C8" s="1">
         <v>3</v>
       </c>
-      <c r="D8" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="E8" s="2">
+      <c r="D8" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E8" s="1">
         <f t="shared" si="0"/>
         <v>1101</v>
       </c>
-      <c r="F8" s="2">
-        <v>5</v>
-      </c>
-      <c r="G8" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="H8" s="9" t="s">
-        <v>15</v>
+      <c r="F8" s="1">
+        <v>5</v>
+      </c>
+      <c r="G8" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="H8" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I8" s="1">
+        <v>1001</v>
+      </c>
+      <c r="J8" s="1">
+        <v>5</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="3:13">
       <c r="C9" s="1">
         <v>4</v>
       </c>
-      <c r="D9" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="E9" s="2">
+      <c r="D9" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E9" s="1">
         <f t="shared" si="0"/>
         <v>1101</v>
       </c>
-      <c r="F9" s="2">
-        <v>5</v>
-      </c>
-      <c r="G9" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="H9" s="9" t="s">
-        <v>19</v>
+      <c r="F9" s="1">
+        <v>5</v>
+      </c>
+      <c r="G9" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="H9" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="I9" s="1">
+        <v>1003</v>
+      </c>
+      <c r="J9" s="1">
+        <v>10</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="3:13">
       <c r="C10" s="1">
         <v>5</v>
       </c>
-      <c r="D10" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="E10" s="2">
+      <c r="D10" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E10" s="1">
         <f t="shared" si="0"/>
         <v>1101</v>
       </c>
-      <c r="F10" s="2">
-        <v>5</v>
-      </c>
-      <c r="G10" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="H10" s="9" t="s">
-        <v>21</v>
+      <c r="F10" s="1">
+        <v>5</v>
+      </c>
+      <c r="G10" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H10" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I10" s="1">
+        <v>1002</v>
+      </c>
+      <c r="J10" s="1">
+        <v>10</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="3:13">
       <c r="C11" s="1">
         <v>6</v>
       </c>
-      <c r="D11" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="E11" s="2">
+      <c r="D11" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E11" s="1">
         <f t="shared" si="0"/>
         <v>1101</v>
       </c>
-      <c r="F11" s="2">
-        <v>5</v>
-      </c>
-      <c r="G11" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="H11" s="9" t="s">
+      <c r="F11" s="1">
+        <v>5</v>
+      </c>
+      <c r="G11" s="8" t="s">
         <v>21</v>
+      </c>
+      <c r="H11" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I11" s="1">
+        <v>1001</v>
+      </c>
+      <c r="J11" s="1">
+        <v>10</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="3:13">
       <c r="C12" s="1">
         <v>7</v>
       </c>
-      <c r="D12" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="E12" s="2">
+      <c r="D12" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E12" s="1">
         <f t="shared" si="0"/>
         <v>1102</v>
       </c>
-      <c r="F12" s="2">
-        <v>5</v>
-      </c>
-      <c r="G12" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="H12" s="9" t="s">
-        <v>24</v>
+      <c r="F12" s="1">
+        <v>5</v>
+      </c>
+      <c r="G12" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="H12" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="I12" s="1">
+        <v>1003</v>
+      </c>
+      <c r="J12" s="1">
+        <v>15</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" customHeight="1" spans="3:13">
       <c r="C13" s="1">
         <v>8</v>
       </c>
-      <c r="D13" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="E13" s="2">
+      <c r="D13" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="E13" s="1">
         <f t="shared" si="0"/>
         <v>1102</v>
       </c>
-      <c r="F13" s="2">
-        <v>5</v>
-      </c>
-      <c r="G13" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="H13" s="9" t="s">
-        <v>26</v>
+      <c r="F13" s="1">
+        <v>5</v>
+      </c>
+      <c r="G13" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H13" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="I13" s="1">
+        <v>1002</v>
+      </c>
+      <c r="J13" s="1">
+        <v>15</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="3:13">
       <c r="C14" s="1">
         <v>9</v>
       </c>
-      <c r="D14" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="E14" s="2">
+      <c r="D14" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="E14" s="1">
         <f t="shared" si="0"/>
         <v>1102</v>
       </c>
-      <c r="F14" s="2">
-        <v>5</v>
-      </c>
-      <c r="G14" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="H14" s="9" t="s">
-        <v>26</v>
+      <c r="F14" s="1">
+        <v>5</v>
+      </c>
+      <c r="G14" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="H14" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="I14" s="1">
+        <v>1001</v>
+      </c>
+      <c r="J14" s="1">
+        <v>15</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" customHeight="1" spans="3:13">
       <c r="C15" s="1">
         <v>10</v>
       </c>
-      <c r="D15" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="E15" s="2">
+      <c r="D15" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E15" s="1">
         <f t="shared" si="0"/>
         <v>1102</v>
       </c>
-      <c r="F15" s="2">
-        <v>5</v>
-      </c>
-      <c r="G15" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="H15" s="9" t="s">
-        <v>29</v>
+      <c r="F15" s="1">
+        <v>5</v>
+      </c>
+      <c r="G15" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="H15" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="I15" s="1">
+        <v>1003</v>
+      </c>
+      <c r="J15" s="1">
+        <v>20</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" customHeight="1" spans="3:13">
       <c r="C16" s="1">
         <v>11</v>
       </c>
-      <c r="D16" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="E16" s="2">
+      <c r="D16" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E16" s="1">
         <f t="shared" si="0"/>
         <v>1102</v>
       </c>
-      <c r="F16" s="2">
-        <v>5</v>
-      </c>
-      <c r="G16" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="H16" s="9" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="17" s="1" customFormat="1" customHeight="1" spans="3:8">
+      <c r="F16" s="1">
+        <v>5</v>
+      </c>
+      <c r="G16" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H16" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="I16" s="1">
+        <v>1002</v>
+      </c>
+      <c r="J16" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="17" s="1" customFormat="1" customHeight="1" spans="3:11">
       <c r="C17" s="1">
         <v>12</v>
       </c>
-      <c r="D17" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="E17" s="2">
+      <c r="D17" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="E17" s="1">
         <f t="shared" si="0"/>
         <v>1102</v>
       </c>
-      <c r="F17" s="2">
-        <v>5</v>
-      </c>
-      <c r="G17" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="H17" s="9" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="18" s="1" customFormat="1" customHeight="1" spans="3:8">
+      <c r="F17" s="1">
+        <v>5</v>
+      </c>
+      <c r="G17" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="H17" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="I17" s="1">
+        <v>1001</v>
+      </c>
+      <c r="J17" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="18" s="1" customFormat="1" customHeight="1" spans="3:11">
       <c r="C18" s="1">
         <v>13</v>
       </c>
-      <c r="D18" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="E18" s="2">
+      <c r="D18" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="E18" s="1">
         <f t="shared" si="0"/>
         <v>1103</v>
       </c>
-      <c r="F18" s="2">
-        <v>5</v>
-      </c>
-      <c r="G18" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="H18" s="9" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="19" s="1" customFormat="1" customHeight="1" spans="3:8">
+      <c r="F18" s="1">
+        <v>5</v>
+      </c>
+      <c r="G18" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="H18" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="I18" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="J18" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="K18" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="19" s="1" customFormat="1" customHeight="1" spans="3:11">
       <c r="C19" s="1">
         <v>14</v>
       </c>
-      <c r="D19" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="E19" s="2">
+      <c r="D19" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="E19" s="1">
         <f t="shared" si="0"/>
         <v>1103</v>
       </c>
-      <c r="F19" s="2">
-        <v>5</v>
-      </c>
-      <c r="G19" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="H19" s="9" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="20" s="1" customFormat="1" customHeight="1" spans="3:8">
+      <c r="F19" s="1">
+        <v>5</v>
+      </c>
+      <c r="G19" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H19" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="I19" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="J19" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="K19" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="20" s="1" customFormat="1" customHeight="1" spans="3:11">
       <c r="C20" s="1">
         <v>15</v>
       </c>
-      <c r="D20" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="E20" s="2">
+      <c r="D20" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E20" s="1">
         <f t="shared" si="0"/>
         <v>1103</v>
       </c>
-      <c r="F20" s="2">
-        <v>5</v>
-      </c>
-      <c r="G20" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="H20" s="9" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="21" s="1" customFormat="1" customHeight="1" spans="3:8">
+      <c r="F20" s="1">
+        <v>5</v>
+      </c>
+      <c r="G20" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="H20" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="I20" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="J20" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="K20" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="21" s="1" customFormat="1" customHeight="1" spans="3:11">
       <c r="C21" s="1">
         <v>16</v>
       </c>
-      <c r="D21" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="E21" s="2">
+      <c r="D21" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E21" s="1">
         <f t="shared" si="0"/>
         <v>1103</v>
       </c>
-      <c r="F21" s="2">
-        <v>5</v>
-      </c>
-      <c r="G21" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="H21" s="9" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="22" s="1" customFormat="1" customHeight="1" spans="3:8">
+      <c r="F21" s="1">
+        <v>5</v>
+      </c>
+      <c r="G21" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="H21" s="8" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="22" s="1" customFormat="1" customHeight="1" spans="3:11">
       <c r="C22" s="1">
         <v>17</v>
       </c>
-      <c r="D22" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="E22" s="2">
+      <c r="D22" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E22" s="1">
         <f t="shared" si="0"/>
         <v>1103</v>
       </c>
-      <c r="F22" s="2">
-        <v>5</v>
-      </c>
-      <c r="G22" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="H22" s="9" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="23" s="1" customFormat="1" customHeight="1" spans="3:8">
+      <c r="F22" s="1">
+        <v>5</v>
+      </c>
+      <c r="G22" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H22" s="8" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="23" s="1" customFormat="1" customHeight="1" spans="3:11">
       <c r="C23" s="1">
         <v>18</v>
       </c>
-      <c r="D23" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="E23" s="2">
+      <c r="D23" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="E23" s="1">
         <f t="shared" si="0"/>
         <v>1103</v>
       </c>
-      <c r="F23" s="2">
-        <v>5</v>
-      </c>
-      <c r="G23" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="H23" s="9" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="24" s="1" customFormat="1" customHeight="1" spans="3:8">
+      <c r="F23" s="1">
+        <v>5</v>
+      </c>
+      <c r="G23" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="H23" s="8" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="24" s="1" customFormat="1" customHeight="1" spans="3:11">
       <c r="C24" s="1">
         <v>19</v>
       </c>
-      <c r="D24" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="E24" s="2">
+      <c r="D24" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="E24" s="1">
         <f t="shared" si="0"/>
         <v>1104</v>
       </c>
-      <c r="F24" s="2">
-        <v>5</v>
-      </c>
-      <c r="G24" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="H24" s="9" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="25" s="1" customFormat="1" customHeight="1" spans="3:8">
+      <c r="F24" s="1">
+        <v>5</v>
+      </c>
+      <c r="G24" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="H24" s="8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="25" s="1" customFormat="1" customHeight="1" spans="3:11">
       <c r="C25" s="1">
         <v>20</v>
       </c>
-      <c r="D25" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="E25" s="2">
+      <c r="D25" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E25" s="1">
         <f t="shared" si="0"/>
         <v>1104</v>
       </c>
-      <c r="F25" s="2">
-        <v>5</v>
-      </c>
-      <c r="G25" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="H25" s="9" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="26" s="1" customFormat="1" customHeight="1" spans="3:8">
+      <c r="F25" s="1">
+        <v>5</v>
+      </c>
+      <c r="G25" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H25" s="8" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="26" s="1" customFormat="1" customHeight="1" spans="3:11">
       <c r="C26" s="1">
         <v>21</v>
       </c>
-      <c r="D26" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="E26" s="2">
+      <c r="D26" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E26" s="1">
         <f t="shared" si="0"/>
         <v>1104</v>
       </c>
-      <c r="F26" s="2">
-        <v>5</v>
-      </c>
-      <c r="G26" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="H26" s="9" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="27" customHeight="1" spans="3:8">
+      <c r="F26" s="1">
+        <v>5</v>
+      </c>
+      <c r="G26" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="H26" s="8" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="27" customHeight="1" spans="3:11">
       <c r="C27" s="1">
         <v>22</v>
       </c>
-      <c r="D27" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="E27" s="2">
+      <c r="D27" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E27" s="1">
         <f t="shared" si="0"/>
         <v>1104</v>
       </c>
-      <c r="F27" s="2">
-        <v>5</v>
-      </c>
-      <c r="G27" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="H27" s="9" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="28" customHeight="1" spans="3:8">
+      <c r="F27" s="1">
+        <v>5</v>
+      </c>
+      <c r="G27" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="H27" s="8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="28" customHeight="1" spans="3:11">
       <c r="C28" s="1">
         <v>23</v>
       </c>
-      <c r="D28" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="E28" s="2">
+      <c r="D28" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="E28" s="1">
         <f t="shared" si="0"/>
         <v>1104</v>
       </c>
-      <c r="F28" s="2">
-        <v>5</v>
-      </c>
-      <c r="G28" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="H28" s="9" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="29" customHeight="1" spans="3:8">
+      <c r="F28" s="1">
+        <v>5</v>
+      </c>
+      <c r="G28" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H28" s="8" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="29" customHeight="1" spans="3:11">
       <c r="C29" s="1">
         <v>24</v>
       </c>
-      <c r="D29" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="E29" s="2">
+      <c r="D29" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="E29" s="1">
         <f t="shared" si="0"/>
         <v>1104</v>
       </c>
-      <c r="F29" s="2">
-        <v>5</v>
-      </c>
-      <c r="G29" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="H29" s="9" t="s">
+      <c r="F29" s="1">
+        <v>5</v>
+      </c>
+      <c r="G29" s="8" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="30" customHeight="1" spans="3:8">
+      <c r="H29" s="8" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="30" customHeight="1" spans="3:11">
       <c r="C30" s="1">
         <v>25</v>
       </c>
-      <c r="D30" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="E30" s="2">
+      <c r="D30" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="E30" s="1">
         <f t="shared" si="0"/>
         <v>1105</v>
       </c>
-      <c r="F30" s="2">
-        <v>5</v>
-      </c>
-      <c r="G30" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="H30" s="9" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="31" customHeight="1" spans="3:8">
+      <c r="F30" s="1">
+        <v>5</v>
+      </c>
+      <c r="G30" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="H30" s="8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="31" customHeight="1" spans="3:11">
       <c r="C31" s="1">
         <v>26</v>
       </c>
-      <c r="D31" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="E31" s="2">
+      <c r="D31" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="E31" s="1">
         <f t="shared" si="0"/>
         <v>1105</v>
       </c>
-      <c r="F31" s="2">
-        <v>5</v>
-      </c>
-      <c r="G31" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="H31" s="9" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="32" customHeight="1" spans="3:8">
+      <c r="F31" s="1">
+        <v>5</v>
+      </c>
+      <c r="G31" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H31" s="8" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="32" customHeight="1" spans="3:11">
       <c r="C32" s="1">
         <v>27</v>
       </c>
-      <c r="D32" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="E32" s="2">
+      <c r="D32" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="E32" s="1">
         <f t="shared" si="0"/>
         <v>1105</v>
       </c>
-      <c r="F32" s="2">
-        <v>5</v>
-      </c>
-      <c r="G32" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="H32" s="9" t="s">
-        <v>15</v>
+      <c r="F32" s="1">
+        <v>5</v>
+      </c>
+      <c r="G32" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="H32" s="8" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="33" customHeight="1" spans="3:8">
       <c r="C33" s="1">
         <v>28</v>
       </c>
-      <c r="D33" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="E33" s="2">
+      <c r="D33" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="E33" s="1">
         <f t="shared" si="0"/>
         <v>1105</v>
       </c>
-      <c r="F33" s="2">
-        <v>5</v>
-      </c>
-      <c r="G33" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="H33" s="9" t="s">
-        <v>19</v>
+      <c r="F33" s="1">
+        <v>5</v>
+      </c>
+      <c r="G33" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="H33" s="8" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="34" customHeight="1" spans="3:8">
       <c r="C34" s="1">
         <v>29</v>
       </c>
-      <c r="D34" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="E34" s="2">
+      <c r="D34" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="E34" s="1">
         <f t="shared" si="0"/>
         <v>1105</v>
       </c>
-      <c r="F34" s="2">
-        <v>5</v>
-      </c>
-      <c r="G34" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="H34" s="9" t="s">
-        <v>21</v>
+      <c r="F34" s="1">
+        <v>5</v>
+      </c>
+      <c r="G34" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H34" s="8" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="35" customHeight="1" spans="3:8">
       <c r="C35" s="1">
         <v>30</v>
       </c>
-      <c r="D35" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="E35" s="2">
+      <c r="D35" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="E35" s="1">
         <f t="shared" si="0"/>
         <v>1105</v>
       </c>
-      <c r="F35" s="2">
-        <v>5</v>
-      </c>
-      <c r="G35" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="H35" s="9" t="s">
+      <c r="F35" s="1">
+        <v>5</v>
+      </c>
+      <c r="G35" s="8" t="s">
         <v>21</v>
+      </c>
+      <c r="H35" s="8" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="36" customHeight="1" spans="3:8">
       <c r="C36" s="1">
         <v>31</v>
       </c>
-      <c r="D36" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="E36" s="2">
+      <c r="D36" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="E36" s="1">
         <f t="shared" si="0"/>
         <v>1106</v>
       </c>
-      <c r="F36" s="2">
-        <v>5</v>
-      </c>
-      <c r="G36" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="H36" s="9" t="s">
-        <v>12</v>
+      <c r="F36" s="1">
+        <v>5</v>
+      </c>
+      <c r="G36" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="H36" s="8" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="37" customHeight="1" spans="3:8">
       <c r="C37" s="1">
         <v>32</v>
       </c>
-      <c r="D37" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="E37" s="2">
+      <c r="D37" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="E37" s="1">
         <f t="shared" si="0"/>
         <v>1106</v>
       </c>
-      <c r="F37" s="2">
-        <v>5</v>
-      </c>
-      <c r="G37" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="H37" s="9" t="s">
-        <v>15</v>
+      <c r="F37" s="1">
+        <v>5</v>
+      </c>
+      <c r="G37" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H37" s="8" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="38" customHeight="1" spans="3:8">
       <c r="C38" s="1">
         <v>33</v>
       </c>
-      <c r="D38" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="E38" s="2">
+      <c r="D38" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="E38" s="1">
         <f t="shared" si="0"/>
         <v>1106</v>
       </c>
-      <c r="F38" s="2">
-        <v>5</v>
-      </c>
-      <c r="G38" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="H38" s="9" t="s">
-        <v>15</v>
+      <c r="F38" s="1">
+        <v>5</v>
+      </c>
+      <c r="G38" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="H38" s="8" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="39" customHeight="1" spans="3:8">
       <c r="C39" s="1">
         <v>34</v>
       </c>
-      <c r="D39" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="E39" s="2">
+      <c r="D39" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="E39" s="1">
         <f t="shared" si="0"/>
         <v>1106</v>
       </c>
-      <c r="F39" s="2">
-        <v>5</v>
-      </c>
-      <c r="G39" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="H39" s="9" t="s">
-        <v>19</v>
+      <c r="F39" s="1">
+        <v>5</v>
+      </c>
+      <c r="G39" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="H39" s="8" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="40" customHeight="1" spans="3:8">
       <c r="C40" s="1">
         <v>35</v>
       </c>
-      <c r="D40" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="E40" s="2">
+      <c r="D40" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="E40" s="1">
         <f t="shared" si="0"/>
         <v>1106</v>
       </c>
-      <c r="F40" s="2">
-        <v>5</v>
-      </c>
-      <c r="G40" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="H40" s="9" t="s">
-        <v>21</v>
+      <c r="F40" s="1">
+        <v>5</v>
+      </c>
+      <c r="G40" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H40" s="8" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="41" customHeight="1" spans="3:8">
       <c r="C41" s="1">
         <v>36</v>
       </c>
-      <c r="D41" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="E41" s="2">
+      <c r="D41" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="E41" s="1">
         <f t="shared" si="0"/>
         <v>1106</v>
       </c>
-      <c r="F41" s="2">
-        <v>5</v>
-      </c>
-      <c r="G41" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="H41" s="9" t="s">
+      <c r="F41" s="1">
+        <v>5</v>
+      </c>
+      <c r="G41" s="8" t="s">
         <v>21</v>
+      </c>
+      <c r="H41" s="8" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="42" customHeight="1" spans="3:8">
       <c r="C42" s="1">
         <v>37</v>
       </c>
-      <c r="D42" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="E42" s="2">
+      <c r="D42" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="E42" s="1">
         <f t="shared" si="0"/>
         <v>1107</v>
       </c>
-      <c r="F42" s="2">
-        <v>5</v>
-      </c>
-      <c r="G42" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="H42" s="9" t="s">
-        <v>12</v>
+      <c r="F42" s="1">
+        <v>5</v>
+      </c>
+      <c r="G42" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="H42" s="8" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="43" customHeight="1" spans="3:8">
       <c r="C43" s="1">
         <v>38</v>
       </c>
-      <c r="D43" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="E43" s="2">
+      <c r="D43" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="E43" s="1">
         <f t="shared" si="0"/>
         <v>1107</v>
       </c>
-      <c r="F43" s="2">
-        <v>5</v>
-      </c>
-      <c r="G43" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="H43" s="9" t="s">
-        <v>15</v>
+      <c r="F43" s="1">
+        <v>5</v>
+      </c>
+      <c r="G43" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H43" s="8" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="44" customHeight="1" spans="3:8">
       <c r="C44" s="1">
         <v>39</v>
       </c>
-      <c r="D44" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="E44" s="2">
+      <c r="D44" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="E44" s="1">
         <f t="shared" si="0"/>
         <v>1107</v>
       </c>
-      <c r="F44" s="2">
-        <v>5</v>
-      </c>
-      <c r="G44" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="H44" s="9" t="s">
-        <v>15</v>
+      <c r="F44" s="1">
+        <v>5</v>
+      </c>
+      <c r="G44" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="H44" s="8" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="45" customHeight="1" spans="3:8">
       <c r="C45" s="1">
         <v>40</v>
       </c>
-      <c r="D45" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="E45" s="2">
+      <c r="D45" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="E45" s="1">
         <f t="shared" si="0"/>
         <v>1107</v>
       </c>
-      <c r="F45" s="2">
-        <v>5</v>
-      </c>
-      <c r="G45" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="H45" s="9" t="s">
-        <v>19</v>
+      <c r="F45" s="1">
+        <v>5</v>
+      </c>
+      <c r="G45" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="H45" s="8" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="46" customHeight="1" spans="3:8">
       <c r="C46" s="1">
         <v>41</v>
       </c>
-      <c r="D46" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="E46" s="2">
+      <c r="D46" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="E46" s="1">
         <f t="shared" si="0"/>
         <v>1107</v>
       </c>
-      <c r="F46" s="2">
-        <v>5</v>
-      </c>
-      <c r="G46" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="H46" s="9" t="s">
-        <v>21</v>
+      <c r="F46" s="1">
+        <v>5</v>
+      </c>
+      <c r="G46" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H46" s="8" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="47" customHeight="1" spans="3:8">
       <c r="C47" s="1">
         <v>42</v>
       </c>
-      <c r="D47" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="E47" s="2">
+      <c r="D47" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="E47" s="1">
         <f t="shared" si="0"/>
         <v>1107</v>
       </c>
-      <c r="F47" s="2">
-        <v>5</v>
-      </c>
-      <c r="G47" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="H47" s="9" t="s">
+      <c r="F47" s="1">
+        <v>5</v>
+      </c>
+      <c r="G47" s="8" t="s">
         <v>21</v>
+      </c>
+      <c r="H47" s="8" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="48" customHeight="1" spans="3:8">
       <c r="C48" s="1">
         <v>43</v>
       </c>
-      <c r="D48" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="E48" s="2">
+      <c r="D48" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="E48" s="1">
         <f t="shared" si="0"/>
         <v>1108</v>
       </c>
-      <c r="F48" s="2">
-        <v>5</v>
-      </c>
-      <c r="G48" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="H48" s="9" t="s">
-        <v>12</v>
+      <c r="F48" s="1">
+        <v>5</v>
+      </c>
+      <c r="G48" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="H48" s="8" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="49" customHeight="1" spans="3:8">
       <c r="C49" s="1">
         <v>44</v>
       </c>
-      <c r="D49" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="E49" s="2">
+      <c r="D49" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="E49" s="1">
         <f t="shared" si="0"/>
         <v>1108</v>
       </c>
-      <c r="F49" s="2">
-        <v>5</v>
-      </c>
-      <c r="G49" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="H49" s="9" t="s">
-        <v>15</v>
+      <c r="F49" s="1">
+        <v>5</v>
+      </c>
+      <c r="G49" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H49" s="8" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="50" customHeight="1" spans="3:8">
       <c r="C50" s="1">
         <v>45</v>
       </c>
-      <c r="D50" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="E50" s="2">
+      <c r="D50" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="E50" s="1">
         <f t="shared" si="0"/>
         <v>1108</v>
       </c>
-      <c r="F50" s="2">
-        <v>5</v>
-      </c>
-      <c r="G50" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="H50" s="9" t="s">
-        <v>15</v>
+      <c r="F50" s="1">
+        <v>5</v>
+      </c>
+      <c r="G50" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="H50" s="8" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="51" customHeight="1" spans="3:8">
       <c r="C51" s="1">
         <v>46</v>
       </c>
-      <c r="D51" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="E51" s="2">
+      <c r="D51" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="E51" s="1">
         <f t="shared" si="0"/>
         <v>1108</v>
       </c>
-      <c r="F51" s="2">
-        <v>5</v>
-      </c>
-      <c r="G51" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="H51" s="9" t="s">
-        <v>19</v>
+      <c r="F51" s="1">
+        <v>5</v>
+      </c>
+      <c r="G51" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="H51" s="8" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="52" customHeight="1" spans="3:8">
       <c r="C52" s="1">
         <v>47</v>
       </c>
-      <c r="D52" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="E52" s="2">
+      <c r="D52" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="E52" s="1">
         <f t="shared" si="0"/>
         <v>1108</v>
       </c>
-      <c r="F52" s="2">
-        <v>5</v>
-      </c>
-      <c r="G52" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="H52" s="9" t="s">
-        <v>21</v>
+      <c r="F52" s="1">
+        <v>5</v>
+      </c>
+      <c r="G52" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H52" s="8" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="53" customHeight="1" spans="3:8">
       <c r="C53" s="1">
         <v>48</v>
       </c>
-      <c r="D53" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="E53" s="2">
+      <c r="D53" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="E53" s="1">
         <f t="shared" si="0"/>
         <v>1108</v>
       </c>
-      <c r="F53" s="2">
-        <v>5</v>
-      </c>
-      <c r="G53" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="H53" s="9" t="s">
+      <c r="F53" s="1">
+        <v>5</v>
+      </c>
+      <c r="G53" s="8" t="s">
         <v>21</v>
+      </c>
+      <c r="H53" s="8" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="54" customHeight="1" spans="3:8">
       <c r="C54" s="1">
         <v>49</v>
       </c>
-      <c r="D54" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="E54" s="2">
+      <c r="D54" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="E54" s="1">
         <f t="shared" si="0"/>
         <v>1109</v>
       </c>
-      <c r="F54" s="2">
-        <v>5</v>
-      </c>
-      <c r="G54" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="H54" s="9" t="s">
-        <v>12</v>
+      <c r="F54" s="1">
+        <v>5</v>
+      </c>
+      <c r="G54" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="H54" s="8" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="55" customHeight="1" spans="3:8">
       <c r="C55" s="1">
         <v>50</v>
       </c>
-      <c r="D55" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="E55" s="2">
+      <c r="D55" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="E55" s="1">
         <f t="shared" si="0"/>
         <v>1109</v>
       </c>
-      <c r="F55" s="2">
-        <v>5</v>
-      </c>
-      <c r="G55" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="H55" s="9" t="s">
-        <v>15</v>
+      <c r="F55" s="1">
+        <v>5</v>
+      </c>
+      <c r="G55" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H55" s="8" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="56" customHeight="1" spans="3:8">
       <c r="C56" s="1">
         <v>51</v>
       </c>
-      <c r="D56" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="E56" s="2">
+      <c r="D56" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="E56" s="1">
         <f t="shared" si="0"/>
         <v>1109</v>
       </c>
-      <c r="F56" s="2">
-        <v>5</v>
-      </c>
-      <c r="G56" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="H56" s="9" t="s">
-        <v>15</v>
+      <c r="F56" s="1">
+        <v>5</v>
+      </c>
+      <c r="G56" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="H56" s="8" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="57" customHeight="1" spans="3:8">
       <c r="C57" s="1">
         <v>52</v>
       </c>
-      <c r="D57" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="E57" s="2">
+      <c r="D57" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="E57" s="1">
         <f t="shared" si="0"/>
         <v>1109</v>
       </c>
-      <c r="F57" s="2">
-        <v>5</v>
-      </c>
-      <c r="G57" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="H57" s="9" t="s">
-        <v>19</v>
+      <c r="F57" s="1">
+        <v>5</v>
+      </c>
+      <c r="G57" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="H57" s="8" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="58" customHeight="1" spans="3:8">
       <c r="C58" s="1">
         <v>53</v>
       </c>
-      <c r="D58" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="E58" s="2">
+      <c r="D58" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="E58" s="1">
         <f t="shared" si="0"/>
         <v>1109</v>
       </c>
-      <c r="F58" s="2">
-        <v>5</v>
-      </c>
-      <c r="G58" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="H58" s="9" t="s">
-        <v>21</v>
+      <c r="F58" s="1">
+        <v>5</v>
+      </c>
+      <c r="G58" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H58" s="8" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="59" customHeight="1" spans="3:8">
       <c r="C59" s="1">
         <v>54</v>
       </c>
-      <c r="D59" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="E59" s="2">
+      <c r="D59" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="E59" s="1">
         <f t="shared" si="0"/>
         <v>1109</v>
       </c>
-      <c r="F59" s="2">
-        <v>5</v>
-      </c>
-      <c r="G59" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="H59" s="9" t="s">
+      <c r="F59" s="1">
+        <v>5</v>
+      </c>
+      <c r="G59" s="8" t="s">
         <v>21</v>
+      </c>
+      <c r="H59" s="8" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="60" customHeight="1" spans="3:8">
       <c r="C60" s="1">
         <v>55</v>
       </c>
-      <c r="D60" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="E60" s="2">
+      <c r="D60" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E60" s="1">
         <f t="shared" si="0"/>
         <v>1110</v>
       </c>
-      <c r="F60" s="2">
-        <v>5</v>
-      </c>
-      <c r="G60" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="H60" s="9" t="s">
-        <v>12</v>
+      <c r="F60" s="1">
+        <v>5</v>
+      </c>
+      <c r="G60" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="H60" s="8" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="61" customHeight="1" spans="3:8">
       <c r="C61" s="1">
         <v>56</v>
       </c>
-      <c r="D61" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="E61" s="2">
+      <c r="D61" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="E61" s="1">
         <f t="shared" si="0"/>
         <v>1110</v>
       </c>
-      <c r="F61" s="2">
-        <v>5</v>
-      </c>
-      <c r="G61" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="H61" s="9" t="s">
-        <v>15</v>
+      <c r="F61" s="1">
+        <v>5</v>
+      </c>
+      <c r="G61" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H61" s="8" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="62" customHeight="1" spans="3:8">
       <c r="C62" s="1">
         <v>57</v>
       </c>
-      <c r="D62" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="E62" s="2">
+      <c r="D62" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="E62" s="1">
         <f t="shared" si="0"/>
         <v>1110</v>
       </c>
-      <c r="F62" s="2">
-        <v>5</v>
-      </c>
-      <c r="G62" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="H62" s="9" t="s">
-        <v>15</v>
+      <c r="F62" s="1">
+        <v>5</v>
+      </c>
+      <c r="G62" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="H62" s="8" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="63" customHeight="1" spans="3:8">
       <c r="C63" s="1">
         <v>58</v>
       </c>
-      <c r="D63" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="E63" s="2">
+      <c r="D63" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="E63" s="1">
         <f t="shared" si="0"/>
         <v>1110</v>
       </c>
-      <c r="F63" s="2">
-        <v>5</v>
-      </c>
-      <c r="G63" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="H63" s="9" t="s">
-        <v>19</v>
+      <c r="F63" s="1">
+        <v>5</v>
+      </c>
+      <c r="G63" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="H63" s="8" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="64" customHeight="1" spans="3:8">
       <c r="C64" s="1">
         <v>59</v>
       </c>
-      <c r="D64" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="E64" s="2">
+      <c r="D64" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="E64" s="1">
         <f t="shared" si="0"/>
         <v>1110</v>
       </c>
-      <c r="F64" s="2">
-        <v>5</v>
-      </c>
-      <c r="G64" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="H64" s="9" t="s">
-        <v>21</v>
+      <c r="F64" s="1">
+        <v>5</v>
+      </c>
+      <c r="G64" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H64" s="8" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="65" customHeight="1" spans="3:8">
       <c r="C65" s="1">
         <v>60</v>
       </c>
-      <c r="D65" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="E65" s="2">
+      <c r="D65" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="E65" s="1">
         <f t="shared" si="0"/>
         <v>1110</v>
       </c>
-      <c r="F65" s="2">
-        <v>5</v>
-      </c>
-      <c r="G65" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="H65" s="9" t="s">
+      <c r="F65" s="1">
+        <v>5</v>
+      </c>
+      <c r="G65" s="8" t="s">
         <v>21</v>
+      </c>
+      <c r="H65" s="8" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="66" customHeight="1" spans="3:8">
       <c r="C66" s="1">
         <v>61</v>
       </c>
-      <c r="D66" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="E66" s="2">
+      <c r="D66" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="E66" s="1">
         <f t="shared" si="0"/>
         <v>1111</v>
       </c>
-      <c r="F66" s="2">
-        <v>5</v>
-      </c>
-      <c r="G66" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="H66" s="9" t="s">
-        <v>12</v>
+      <c r="F66" s="1">
+        <v>5</v>
+      </c>
+      <c r="G66" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="H66" s="8" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="67" customHeight="1" spans="3:8">
       <c r="C67" s="1">
         <v>62</v>
       </c>
-      <c r="D67" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="E67" s="2">
+      <c r="D67" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="E67" s="1">
         <f t="shared" si="0"/>
         <v>1111</v>
       </c>
-      <c r="F67" s="2">
-        <v>5</v>
-      </c>
-      <c r="G67" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="H67" s="9" t="s">
-        <v>15</v>
+      <c r="F67" s="1">
+        <v>5</v>
+      </c>
+      <c r="G67" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H67" s="8" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="68" customHeight="1" spans="3:8">
       <c r="C68" s="1">
         <v>63</v>
       </c>
-      <c r="D68" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="E68" s="2">
+      <c r="D68" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="E68" s="1">
         <f t="shared" si="0"/>
         <v>1111</v>
       </c>
-      <c r="F68" s="2">
-        <v>5</v>
-      </c>
-      <c r="G68" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="H68" s="9" t="s">
-        <v>15</v>
+      <c r="F68" s="1">
+        <v>5</v>
+      </c>
+      <c r="G68" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="H68" s="8" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="69" customHeight="1" spans="3:8">
       <c r="C69" s="1">
         <v>64</v>
       </c>
-      <c r="D69" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="E69" s="2">
+      <c r="D69" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="E69" s="1">
         <f t="shared" si="0"/>
         <v>1111</v>
       </c>
-      <c r="F69" s="2">
-        <v>5</v>
-      </c>
-      <c r="G69" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="H69" s="9" t="s">
-        <v>19</v>
+      <c r="F69" s="1">
+        <v>5</v>
+      </c>
+      <c r="G69" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="H69" s="8" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="70" customHeight="1" spans="3:8">
       <c r="C70" s="1">
         <v>65</v>
       </c>
-      <c r="D70" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="E70" s="2">
+      <c r="D70" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="E70" s="1">
         <f t="shared" ref="E70:E77" si="1">INT((C70-1)/6)+1101</f>
         <v>1111</v>
       </c>
-      <c r="F70" s="2">
-        <v>5</v>
-      </c>
-      <c r="G70" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="H70" s="9" t="s">
-        <v>21</v>
+      <c r="F70" s="1">
+        <v>5</v>
+      </c>
+      <c r="G70" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H70" s="8" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="71" customHeight="1" spans="3:8">
       <c r="C71" s="1">
         <v>66</v>
       </c>
-      <c r="D71" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="E71" s="2">
+      <c r="D71" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="E71" s="1">
         <f t="shared" si="1"/>
         <v>1111</v>
       </c>
-      <c r="F71" s="2">
-        <v>5</v>
-      </c>
-      <c r="G71" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="H71" s="9" t="s">
+      <c r="F71" s="1">
+        <v>5</v>
+      </c>
+      <c r="G71" s="8" t="s">
         <v>21</v>
+      </c>
+      <c r="H71" s="8" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="72" customHeight="1" spans="3:8">
       <c r="C72" s="1">
         <v>67</v>
       </c>
-      <c r="D72" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="E72" s="2">
+      <c r="D72" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="E72" s="1">
         <f t="shared" si="1"/>
         <v>1112</v>
       </c>
-      <c r="F72" s="2">
-        <v>5</v>
-      </c>
-      <c r="G72" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="H72" s="9" t="s">
-        <v>12</v>
+      <c r="F72" s="1">
+        <v>5</v>
+      </c>
+      <c r="G72" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="H72" s="8" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="73" customHeight="1" spans="3:8">
       <c r="C73" s="1">
         <v>68</v>
       </c>
-      <c r="D73" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="E73" s="2">
+      <c r="D73" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="E73" s="1">
         <f t="shared" si="1"/>
         <v>1112</v>
       </c>
-      <c r="F73" s="2">
-        <v>5</v>
-      </c>
-      <c r="G73" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="H73" s="9" t="s">
-        <v>15</v>
+      <c r="F73" s="1">
+        <v>5</v>
+      </c>
+      <c r="G73" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H73" s="8" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="74" customHeight="1" spans="3:8">
       <c r="C74" s="1">
         <v>69</v>
       </c>
-      <c r="D74" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="E74" s="2">
+      <c r="D74" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="E74" s="1">
         <f t="shared" si="1"/>
         <v>1112</v>
       </c>
-      <c r="F74" s="2">
-        <v>5</v>
-      </c>
-      <c r="G74" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="H74" s="9" t="s">
-        <v>15</v>
+      <c r="F74" s="1">
+        <v>5</v>
+      </c>
+      <c r="G74" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="H74" s="8" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="75" customHeight="1" spans="3:8">
       <c r="C75" s="1">
         <v>70</v>
       </c>
-      <c r="D75" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="E75" s="2">
+      <c r="D75" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="E75" s="1">
         <f t="shared" si="1"/>
         <v>1112</v>
       </c>
-      <c r="F75" s="2">
-        <v>5</v>
-      </c>
-      <c r="G75" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="H75" s="9" t="s">
-        <v>19</v>
+      <c r="F75" s="1">
+        <v>5</v>
+      </c>
+      <c r="G75" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="H75" s="8" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="76" customHeight="1" spans="3:8">
       <c r="C76" s="1">
         <v>71</v>
       </c>
-      <c r="D76" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="E76" s="2">
+      <c r="D76" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="E76" s="1">
         <f t="shared" si="1"/>
         <v>1112</v>
       </c>
-      <c r="F76" s="2">
-        <v>5</v>
-      </c>
-      <c r="G76" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="H76" s="9" t="s">
-        <v>21</v>
+      <c r="F76" s="1">
+        <v>5</v>
+      </c>
+      <c r="G76" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H76" s="8" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="77" customHeight="1" spans="3:8">
       <c r="C77" s="1">
         <v>72</v>
       </c>
-      <c r="D77" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="E77" s="2">
+      <c r="D77" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="E77" s="1">
         <f t="shared" si="1"/>
         <v>1112</v>
       </c>
-      <c r="F77" s="2">
-        <v>5</v>
-      </c>
-      <c r="G77" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="H77" s="9" t="s">
+      <c r="F77" s="1">
+        <v>5</v>
+      </c>
+      <c r="G77" s="8" t="s">
         <v>21</v>
       </c>
+      <c r="H77" s="8" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="106" customHeight="1" spans="5:8">
-      <c r="E106"/>
-      <c r="F106"/>
-      <c r="G106"/>
-      <c r="H106"/>
+      <c r="E106" s="7"/>
+      <c r="F106" s="7"/>
+      <c r="G106" s="7"/>
+      <c r="H106" s="7"/>
     </row>
     <row r="107" customHeight="1" spans="5:8">
-      <c r="E107"/>
-      <c r="F107"/>
-      <c r="G107"/>
-      <c r="H107"/>
+      <c r="E107" s="7"/>
+      <c r="F107" s="7"/>
+      <c r="G107" s="7"/>
+      <c r="H107" s="7"/>
     </row>
   </sheetData>
   <dataValidations count="2">

--- a/Excel/PetConfig.xlsx
+++ b/Excel/PetConfig.xlsx
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="115">
   <si>
     <t>#</t>
   </si>
@@ -83,68 +83,10 @@
     <t>CardVueList</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
-      </rPr>
-      <t>Perk</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>‌</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
-      </rPr>
-      <t>AtrIdList</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
-      </rPr>
-      <t>Perk</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>‌</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
-      </rPr>
-      <t>AtrVueList</t>
-    </r>
+    <t>TraitId</t>
+  </si>
+  <si>
+    <t>TraitLevel</t>
   </si>
   <si>
     <t>Id</t>
@@ -159,9 +101,6 @@
     <t>int[]</t>
   </si>
   <si>
-    <t>double[]</t>
-  </si>
-  <si>
     <t>狼宝宝</t>
   </si>
   <si>
@@ -171,6 +110,9 @@
     <t>1000,5</t>
   </si>
   <si>
+    <t>基础生命</t>
+  </si>
+  <si>
     <t>骷髅宝宝</t>
   </si>
   <si>
@@ -180,70 +122,97 @@
     <t>100,5</t>
   </si>
   <si>
+    <t>基础防御</t>
+  </si>
+  <si>
     <t>兽人宝宝</t>
   </si>
   <si>
     <t>3,1003</t>
   </si>
   <si>
+    <t>基础攻击</t>
+  </si>
+  <si>
     <t>蜘蛛宝宝</t>
   </si>
   <si>
     <t>5000,10</t>
   </si>
   <si>
+    <t>基础物攻</t>
+  </si>
+  <si>
     <t>岩蝎宝宝</t>
   </si>
   <si>
     <t>200,10</t>
   </si>
   <si>
+    <t>基础魔法</t>
+  </si>
+  <si>
     <t>鬃狮宝宝</t>
   </si>
   <si>
+    <t>基础道术</t>
+  </si>
+  <si>
     <t>毒蛆宝宝</t>
   </si>
   <si>
     <t>10000,15</t>
   </si>
   <si>
+    <t>金币加成</t>
+  </si>
+  <si>
     <t>蜈蚣宝宝</t>
   </si>
   <si>
     <t>400,15</t>
   </si>
   <si>
+    <t>经验加成</t>
+  </si>
+  <si>
     <t>双头宝宝</t>
   </si>
   <si>
+    <t>品质加成</t>
+  </si>
+  <si>
     <t>蛛王宝宝</t>
   </si>
   <si>
     <t>50000,20</t>
   </si>
   <si>
+    <t>掉率加成</t>
+  </si>
+  <si>
     <t>蛇宝宝</t>
   </si>
   <si>
     <t>800,20</t>
   </si>
   <si>
+    <t>杀敌金币</t>
+  </si>
+  <si>
     <t>巨鳄宝宝</t>
   </si>
   <si>
+    <t>杀敌经验</t>
+  </si>
+  <si>
     <t>乌鸦宝宝</t>
   </si>
   <si>
     <t>100000,20</t>
   </si>
   <si>
-    <t>1003,15</t>
-  </si>
-  <si>
-    <t>20,20</t>
-  </si>
-  <si>
-    <t>生命，回复加成</t>
+    <t>命中</t>
   </si>
   <si>
     <t>行尸宝宝</t>
@@ -252,25 +221,13 @@
     <t>1500,20</t>
   </si>
   <si>
-    <t>1002,28</t>
-  </si>
-  <si>
-    <t>20,10</t>
-  </si>
-  <si>
-    <t>防御，免伤</t>
+    <t>闪避</t>
   </si>
   <si>
     <t>尸鬼宝宝</t>
   </si>
   <si>
-    <t>1001,11</t>
-  </si>
-  <si>
-    <t>20,5</t>
-  </si>
-  <si>
-    <t>攻击，攻速</t>
+    <t>爆伤</t>
   </si>
   <si>
     <t>蝙蝠宝宝</t>
@@ -279,13 +236,22 @@
     <t>200000,25</t>
   </si>
   <si>
+    <t>移动速度</t>
+  </si>
+  <si>
     <t>尸魔宝宝</t>
   </si>
   <si>
     <t>3000,25</t>
   </si>
   <si>
+    <t>技能冷却</t>
+  </si>
+  <si>
     <t>尸卫宝宝</t>
+  </si>
+  <si>
+    <t>攻速</t>
   </si>
   <si>
     <t>花妖宝宝</t>
@@ -451,7 +417,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="26">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -622,13 +588,6 @@
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color theme="1"/>
-      <name val="Times New Roman"/>
-      <charset val="134"/>
     </font>
     <font>
       <b/>
@@ -1433,7 +1392,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:M107"/>
+  <dimension ref="C1:K107"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="1"/>
@@ -1442,23 +1401,22 @@
     <col min="7" max="7" width="14.1666666666667" style="1" customWidth="1"/>
     <col min="8" max="8" width="13" style="1" customWidth="1"/>
     <col min="9" max="9" width="14.8333333333333" style="1" customWidth="1"/>
-    <col min="10" max="10" width="14.25" style="1" customWidth="1"/>
-    <col min="11" max="12" width="13" style="1" customWidth="1"/>
-    <col min="13" max="13" width="17" style="1" customWidth="1"/>
-    <col min="14" max="16384" width="9" style="1"/>
+    <col min="10" max="10" width="13" style="1" customWidth="1"/>
+    <col min="11" max="11" width="17" style="1" customWidth="1"/>
+    <col min="12" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" customHeight="1" spans="3:13">
+    <row r="1" customHeight="1" spans="3:11">
       <c r="K1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" customHeight="1" spans="3:13">
+    <row r="2" customHeight="1" spans="3:11">
       <c r="K2" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:13">
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:11">
       <c r="C3" s="2" t="s">
         <v>1</v>
       </c>
@@ -1483,11 +1441,11 @@
       <c r="J3" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="K3" s="2"/>
-      <c r="L3" s="2"/>
-      <c r="M3" s="2"/>
-    </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:13">
+      <c r="K3" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:11">
       <c r="C4" s="2" t="s">
         <v>9</v>
       </c>
@@ -1512,11 +1470,11 @@
       <c r="J4" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="K4" s="2"/>
-      <c r="L4" s="2"/>
-      <c r="M4" s="2"/>
-    </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:13">
+      <c r="K4" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:11">
       <c r="C5" s="2" t="s">
         <v>10</v>
       </c>
@@ -1536,21 +1494,21 @@
         <v>12</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="K5" s="2"/>
-      <c r="L5" s="2"/>
-      <c r="M5" s="2"/>
-    </row>
-    <row r="6" s="1" customFormat="1" customHeight="1" spans="3:13">
+        <v>10</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" s="1" customFormat="1" customHeight="1" spans="3:11">
       <c r="C6" s="1">
         <v>1</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E6" s="1">
         <f t="shared" ref="E6:E69" si="0">INT((C6-1)/6)+1101</f>
@@ -1560,19 +1518,22 @@
         <v>5</v>
       </c>
       <c r="G6" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="H6" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="H6" s="8" t="s">
+      <c r="I6" s="1">
+        <v>1</v>
+      </c>
+      <c r="J6" s="1">
+        <v>1</v>
+      </c>
+      <c r="K6" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="I6" s="1">
-        <v>1003</v>
-      </c>
-      <c r="J6" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" s="1" customFormat="1" customHeight="1" spans="3:13">
+    </row>
+    <row r="7" s="1" customFormat="1" customHeight="1" spans="3:11">
       <c r="C7" s="1">
         <v>2</v>
       </c>
@@ -1593,18 +1554,21 @@
         <v>19</v>
       </c>
       <c r="I7" s="1">
-        <v>1002</v>
+        <v>2</v>
       </c>
       <c r="J7" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:13">
+        <v>1</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:11">
       <c r="C8" s="1">
         <v>3</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E8" s="1">
         <f t="shared" si="0"/>
@@ -1614,24 +1578,27 @@
         <v>5</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H8" s="8" t="s">
         <v>19</v>
       </c>
       <c r="I8" s="1">
-        <v>1001</v>
+        <v>3</v>
       </c>
       <c r="J8" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" s="1" customFormat="1" customHeight="1" spans="3:13">
+        <v>1</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="9" s="1" customFormat="1" customHeight="1" spans="3:11">
       <c r="C9" s="1">
         <v>4</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E9" s="1">
         <f t="shared" si="0"/>
@@ -1641,24 +1608,27 @@
         <v>5</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H9" s="8" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I9" s="1">
-        <v>1003</v>
+        <v>4</v>
       </c>
       <c r="J9" s="1">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" s="1" customFormat="1" customHeight="1" spans="3:13">
+        <v>1</v>
+      </c>
+      <c r="K9" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="10" s="1" customFormat="1" customHeight="1" spans="3:11">
       <c r="C10" s="1">
         <v>5</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="E10" s="1">
         <f t="shared" si="0"/>
@@ -1671,21 +1641,24 @@
         <v>18</v>
       </c>
       <c r="H10" s="8" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="I10" s="1">
-        <v>1002</v>
+        <v>5</v>
       </c>
       <c r="J10" s="1">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:13">
+        <v>1</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:11">
       <c r="C11" s="1">
         <v>6</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E11" s="1">
         <f t="shared" si="0"/>
@@ -1695,24 +1668,27 @@
         <v>5</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H11" s="8" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="I11" s="1">
-        <v>1001</v>
+        <v>6</v>
       </c>
       <c r="J11" s="1">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12" s="1" customFormat="1" customHeight="1" spans="3:13">
+        <v>1</v>
+      </c>
+      <c r="K11" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="12" s="1" customFormat="1" customHeight="1" spans="3:11">
       <c r="C12" s="1">
         <v>7</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="E12" s="1">
         <f t="shared" si="0"/>
@@ -1722,24 +1698,27 @@
         <v>5</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H12" s="8" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="I12" s="1">
-        <v>1003</v>
+        <v>81</v>
       </c>
       <c r="J12" s="1">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="13" s="1" customFormat="1" customHeight="1" spans="3:13">
+        <v>1</v>
+      </c>
+      <c r="K12" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="13" s="1" customFormat="1" customHeight="1" spans="3:11">
       <c r="C13" s="1">
         <v>8</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="E13" s="1">
         <f t="shared" si="0"/>
@@ -1752,21 +1731,24 @@
         <v>18</v>
       </c>
       <c r="H13" s="8" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I13" s="1">
-        <v>1002</v>
+        <v>82</v>
       </c>
       <c r="J13" s="1">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="14" customHeight="1" spans="3:13">
+        <v>1</v>
+      </c>
+      <c r="K13" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="14" customHeight="1" spans="3:11">
       <c r="C14" s="1">
         <v>9</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="E14" s="1">
         <f t="shared" si="0"/>
@@ -1776,24 +1758,27 @@
         <v>5</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H14" s="8" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I14" s="1">
-        <v>1001</v>
+        <v>83</v>
       </c>
       <c r="J14" s="1">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="15" s="1" customFormat="1" customHeight="1" spans="3:13">
+        <v>1</v>
+      </c>
+      <c r="K14" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="15" s="1" customFormat="1" customHeight="1" spans="3:11">
       <c r="C15" s="1">
         <v>10</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="E15" s="1">
         <f t="shared" si="0"/>
@@ -1803,24 +1788,27 @@
         <v>5</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H15" s="8" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="I15" s="1">
-        <v>1003</v>
+        <v>84</v>
       </c>
       <c r="J15" s="1">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="16" s="1" customFormat="1" customHeight="1" spans="3:13">
+        <v>1</v>
+      </c>
+      <c r="K15" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="16" s="1" customFormat="1" customHeight="1" spans="3:11">
       <c r="C16" s="1">
         <v>11</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="E16" s="1">
         <f t="shared" si="0"/>
@@ -1833,13 +1821,16 @@
         <v>18</v>
       </c>
       <c r="H16" s="8" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="I16" s="1">
-        <v>1002</v>
+        <v>85</v>
       </c>
       <c r="J16" s="1">
-        <v>20</v>
+        <v>1</v>
+      </c>
+      <c r="K16" s="1" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -1847,7 +1838,7 @@
         <v>12</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="E17" s="1">
         <f t="shared" si="0"/>
@@ -1857,16 +1848,19 @@
         <v>5</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H17" s="8" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="I17" s="1">
-        <v>1001</v>
+        <v>86</v>
       </c>
       <c r="J17" s="1">
-        <v>20</v>
+        <v>1</v>
+      </c>
+      <c r="K17" s="1" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -1874,7 +1868,7 @@
         <v>13</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="E18" s="1">
         <f t="shared" si="0"/>
@@ -1884,19 +1878,19 @@
         <v>5</v>
       </c>
       <c r="G18" s="8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H18" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="I18" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="J18" s="8" t="s">
-        <v>40</v>
+        <v>49</v>
+      </c>
+      <c r="I18" s="1">
+        <v>13</v>
+      </c>
+      <c r="J18" s="1">
+        <v>1</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -1904,7 +1898,7 @@
         <v>14</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="E19" s="1">
         <f t="shared" si="0"/>
@@ -1917,16 +1911,16 @@
         <v>18</v>
       </c>
       <c r="H19" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="I19" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="J19" s="8" t="s">
-        <v>45</v>
+        <v>52</v>
+      </c>
+      <c r="I19" s="1">
+        <v>14</v>
+      </c>
+      <c r="J19" s="1">
+        <v>1</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
     </row>
     <row r="20" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -1934,7 +1928,7 @@
         <v>15</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="E20" s="1">
         <f t="shared" si="0"/>
@@ -1944,19 +1938,19 @@
         <v>5</v>
       </c>
       <c r="G20" s="8" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H20" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="I20" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="J20" s="8" t="s">
-        <v>49</v>
+        <v>52</v>
+      </c>
+      <c r="I20" s="1">
+        <v>22</v>
+      </c>
+      <c r="J20" s="1">
+        <v>1</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
     </row>
     <row r="21" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -1964,7 +1958,7 @@
         <v>16</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="E21" s="1">
         <f t="shared" si="0"/>
@@ -1974,10 +1968,19 @@
         <v>5</v>
       </c>
       <c r="G21" s="8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H21" s="8" t="s">
-        <v>52</v>
+        <v>57</v>
+      </c>
+      <c r="I21" s="1">
+        <v>12</v>
+      </c>
+      <c r="J21" s="1">
+        <v>1</v>
+      </c>
+      <c r="K21" s="1" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="22" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -1985,7 +1988,7 @@
         <v>17</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="E22" s="1">
         <f t="shared" si="0"/>
@@ -1998,7 +2001,16 @@
         <v>18</v>
       </c>
       <c r="H22" s="8" t="s">
-        <v>54</v>
+        <v>60</v>
+      </c>
+      <c r="I22" s="1">
+        <v>10</v>
+      </c>
+      <c r="J22" s="1">
+        <v>1</v>
+      </c>
+      <c r="K22" s="1" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -2006,7 +2018,7 @@
         <v>18</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="E23" s="1">
         <f t="shared" si="0"/>
@@ -2016,10 +2028,19 @@
         <v>5</v>
       </c>
       <c r="G23" s="8" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H23" s="8" t="s">
-        <v>54</v>
+        <v>60</v>
+      </c>
+      <c r="I23" s="1">
+        <v>11</v>
+      </c>
+      <c r="J23" s="1">
+        <v>1</v>
+      </c>
+      <c r="K23" s="1" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -2027,7 +2048,7 @@
         <v>19</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="E24" s="1">
         <f t="shared" si="0"/>
@@ -2037,9 +2058,18 @@
         <v>5</v>
       </c>
       <c r="G24" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="H24" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="H24" s="8" t="s">
+      <c r="I24" s="1">
+        <v>1</v>
+      </c>
+      <c r="J24" s="1">
+        <v>2</v>
+      </c>
+      <c r="K24" s="1" t="s">
         <v>16</v>
       </c>
     </row>
@@ -2048,7 +2078,7 @@
         <v>20</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="E25" s="1">
         <f t="shared" si="0"/>
@@ -2062,6 +2092,15 @@
       </c>
       <c r="H25" s="8" t="s">
         <v>19</v>
+      </c>
+      <c r="I25" s="1">
+        <v>2</v>
+      </c>
+      <c r="J25" s="1">
+        <v>2</v>
+      </c>
+      <c r="K25" s="1" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="26" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -2069,7 +2108,7 @@
         <v>21</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="E26" s="1">
         <f t="shared" si="0"/>
@@ -2079,10 +2118,19 @@
         <v>5</v>
       </c>
       <c r="G26" s="8" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H26" s="8" t="s">
         <v>19</v>
+      </c>
+      <c r="I26" s="1">
+        <v>3</v>
+      </c>
+      <c r="J26" s="1">
+        <v>2</v>
+      </c>
+      <c r="K26" s="1" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="27" customHeight="1" spans="3:11">
@@ -2090,7 +2138,7 @@
         <v>22</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="E27" s="1">
         <f t="shared" si="0"/>
@@ -2100,10 +2148,19 @@
         <v>5</v>
       </c>
       <c r="G27" s="8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H27" s="8" t="s">
-        <v>23</v>
+        <v>25</v>
+      </c>
+      <c r="I27" s="1">
+        <v>4</v>
+      </c>
+      <c r="J27" s="1">
+        <v>2</v>
+      </c>
+      <c r="K27" s="1" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="28" customHeight="1" spans="3:11">
@@ -2111,7 +2168,7 @@
         <v>23</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="E28" s="1">
         <f t="shared" si="0"/>
@@ -2124,7 +2181,16 @@
         <v>18</v>
       </c>
       <c r="H28" s="8" t="s">
-        <v>25</v>
+        <v>28</v>
+      </c>
+      <c r="I28" s="1">
+        <v>5</v>
+      </c>
+      <c r="J28" s="1">
+        <v>2</v>
+      </c>
+      <c r="K28" s="1" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="29" customHeight="1" spans="3:11">
@@ -2132,7 +2198,7 @@
         <v>24</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="E29" s="1">
         <f t="shared" si="0"/>
@@ -2142,10 +2208,19 @@
         <v>5</v>
       </c>
       <c r="G29" s="8" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H29" s="8" t="s">
-        <v>25</v>
+        <v>28</v>
+      </c>
+      <c r="I29" s="1">
+        <v>6</v>
+      </c>
+      <c r="J29" s="1">
+        <v>2</v>
+      </c>
+      <c r="K29" s="1" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="30" customHeight="1" spans="3:11">
@@ -2153,7 +2228,7 @@
         <v>25</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="E30" s="1">
         <f t="shared" si="0"/>
@@ -2163,10 +2238,19 @@
         <v>5</v>
       </c>
       <c r="G30" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="H30" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="H30" s="8" t="s">
-        <v>16</v>
+      <c r="I30" s="1">
+        <v>81</v>
+      </c>
+      <c r="J30" s="1">
+        <v>2</v>
+      </c>
+      <c r="K30" s="1" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="31" customHeight="1" spans="3:11">
@@ -2174,7 +2258,7 @@
         <v>26</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="E31" s="1">
         <f t="shared" si="0"/>
@@ -2188,6 +2272,15 @@
       </c>
       <c r="H31" s="8" t="s">
         <v>19</v>
+      </c>
+      <c r="I31" s="1">
+        <v>82</v>
+      </c>
+      <c r="J31" s="1">
+        <v>2</v>
+      </c>
+      <c r="K31" s="1" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="32" customHeight="1" spans="3:11">
@@ -2195,7 +2288,7 @@
         <v>27</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="E32" s="1">
         <f t="shared" si="0"/>
@@ -2205,18 +2298,27 @@
         <v>5</v>
       </c>
       <c r="G32" s="8" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H32" s="8" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="33" customHeight="1" spans="3:8">
+      <c r="I32" s="1">
+        <v>83</v>
+      </c>
+      <c r="J32" s="1">
+        <v>2</v>
+      </c>
+      <c r="K32" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="33" customHeight="1" spans="3:11">
       <c r="C33" s="1">
         <v>28</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="E33" s="1">
         <f t="shared" si="0"/>
@@ -2226,18 +2328,27 @@
         <v>5</v>
       </c>
       <c r="G33" s="8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H33" s="8" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="34" customHeight="1" spans="3:8">
+        <v>25</v>
+      </c>
+      <c r="I33" s="1">
+        <v>84</v>
+      </c>
+      <c r="J33" s="1">
+        <v>2</v>
+      </c>
+      <c r="K33" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="34" customHeight="1" spans="3:11">
       <c r="C34" s="1">
         <v>29</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="E34" s="1">
         <f t="shared" si="0"/>
@@ -2250,15 +2361,24 @@
         <v>18</v>
       </c>
       <c r="H34" s="8" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="35" customHeight="1" spans="3:8">
+        <v>28</v>
+      </c>
+      <c r="I34" s="1">
+        <v>85</v>
+      </c>
+      <c r="J34" s="1">
+        <v>2</v>
+      </c>
+      <c r="K34" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="35" customHeight="1" spans="3:11">
       <c r="C35" s="1">
         <v>30</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="E35" s="1">
         <f t="shared" si="0"/>
@@ -2268,18 +2388,27 @@
         <v>5</v>
       </c>
       <c r="G35" s="8" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H35" s="8" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="36" customHeight="1" spans="3:8">
+        <v>28</v>
+      </c>
+      <c r="I35" s="1">
+        <v>86</v>
+      </c>
+      <c r="J35" s="1">
+        <v>2</v>
+      </c>
+      <c r="K35" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="36" customHeight="1" spans="3:11">
       <c r="C36" s="1">
         <v>31</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="E36" s="1">
         <f t="shared" si="0"/>
@@ -2289,18 +2418,27 @@
         <v>5</v>
       </c>
       <c r="G36" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="H36" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="H36" s="8" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="37" customHeight="1" spans="3:8">
+      <c r="I36" s="1">
+        <v>13</v>
+      </c>
+      <c r="J36" s="1">
+        <v>2</v>
+      </c>
+      <c r="K36" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="37" customHeight="1" spans="3:11">
       <c r="C37" s="1">
         <v>32</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="E37" s="1">
         <f t="shared" si="0"/>
@@ -2315,13 +2453,22 @@
       <c r="H37" s="8" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="38" customHeight="1" spans="3:8">
+      <c r="I37" s="1">
+        <v>14</v>
+      </c>
+      <c r="J37" s="1">
+        <v>2</v>
+      </c>
+      <c r="K37" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="38" customHeight="1" spans="3:11">
       <c r="C38" s="1">
         <v>33</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="E38" s="1">
         <f t="shared" si="0"/>
@@ -2331,18 +2478,27 @@
         <v>5</v>
       </c>
       <c r="G38" s="8" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H38" s="8" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="39" customHeight="1" spans="3:8">
+      <c r="I38" s="1">
+        <v>22</v>
+      </c>
+      <c r="J38" s="1">
+        <v>2</v>
+      </c>
+      <c r="K38" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="39" customHeight="1" spans="3:11">
       <c r="C39" s="1">
         <v>34</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="E39" s="1">
         <f t="shared" si="0"/>
@@ -2352,18 +2508,27 @@
         <v>5</v>
       </c>
       <c r="G39" s="8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H39" s="8" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="40" customHeight="1" spans="3:8">
+        <v>25</v>
+      </c>
+      <c r="I39" s="1">
+        <v>12</v>
+      </c>
+      <c r="J39" s="1">
+        <v>2</v>
+      </c>
+      <c r="K39" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="40" customHeight="1" spans="3:11">
       <c r="C40" s="1">
         <v>35</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="E40" s="1">
         <f t="shared" si="0"/>
@@ -2376,15 +2541,24 @@
         <v>18</v>
       </c>
       <c r="H40" s="8" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="41" customHeight="1" spans="3:8">
+        <v>28</v>
+      </c>
+      <c r="I40" s="1">
+        <v>10</v>
+      </c>
+      <c r="J40" s="1">
+        <v>2</v>
+      </c>
+      <c r="K40" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="41" customHeight="1" spans="3:11">
       <c r="C41" s="1">
         <v>36</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="E41" s="1">
         <f t="shared" si="0"/>
@@ -2394,18 +2568,27 @@
         <v>5</v>
       </c>
       <c r="G41" s="8" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H41" s="8" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="42" customHeight="1" spans="3:8">
+        <v>28</v>
+      </c>
+      <c r="I41" s="1">
+        <v>11</v>
+      </c>
+      <c r="J41" s="1">
+        <v>2</v>
+      </c>
+      <c r="K41" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="42" customHeight="1" spans="3:11">
       <c r="C42" s="1">
         <v>37</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="E42" s="1">
         <f t="shared" si="0"/>
@@ -2415,18 +2598,27 @@
         <v>5</v>
       </c>
       <c r="G42" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="H42" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="H42" s="8" t="s">
+      <c r="I42" s="1">
+        <v>1</v>
+      </c>
+      <c r="J42" s="1">
+        <v>3</v>
+      </c>
+      <c r="K42" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="43" customHeight="1" spans="3:8">
+    <row r="43" customHeight="1" spans="3:11">
       <c r="C43" s="1">
         <v>38</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="E43" s="1">
         <f t="shared" si="0"/>
@@ -2441,13 +2633,22 @@
       <c r="H43" s="8" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="44" customHeight="1" spans="3:8">
+      <c r="I43" s="1">
+        <v>2</v>
+      </c>
+      <c r="J43" s="1">
+        <v>3</v>
+      </c>
+      <c r="K43" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="44" customHeight="1" spans="3:11">
       <c r="C44" s="1">
         <v>39</v>
       </c>
       <c r="D44" s="5" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="E44" s="1">
         <f t="shared" si="0"/>
@@ -2457,18 +2658,27 @@
         <v>5</v>
       </c>
       <c r="G44" s="8" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H44" s="8" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="45" customHeight="1" spans="3:8">
+      <c r="I44" s="1">
+        <v>3</v>
+      </c>
+      <c r="J44" s="1">
+        <v>3</v>
+      </c>
+      <c r="K44" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="45" customHeight="1" spans="3:11">
       <c r="C45" s="1">
         <v>40</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="E45" s="1">
         <f t="shared" si="0"/>
@@ -2478,18 +2688,27 @@
         <v>5</v>
       </c>
       <c r="G45" s="8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H45" s="8" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="46" customHeight="1" spans="3:8">
+        <v>25</v>
+      </c>
+      <c r="I45" s="1">
+        <v>4</v>
+      </c>
+      <c r="J45" s="1">
+        <v>3</v>
+      </c>
+      <c r="K45" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="46" customHeight="1" spans="3:11">
       <c r="C46" s="1">
         <v>41</v>
       </c>
       <c r="D46" s="6" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="E46" s="1">
         <f t="shared" si="0"/>
@@ -2502,15 +2721,24 @@
         <v>18</v>
       </c>
       <c r="H46" s="8" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="47" customHeight="1" spans="3:8">
+        <v>28</v>
+      </c>
+      <c r="I46" s="1">
+        <v>5</v>
+      </c>
+      <c r="J46" s="1">
+        <v>3</v>
+      </c>
+      <c r="K46" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="47" customHeight="1" spans="3:11">
       <c r="C47" s="1">
         <v>42</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="E47" s="1">
         <f t="shared" si="0"/>
@@ -2520,18 +2748,27 @@
         <v>5</v>
       </c>
       <c r="G47" s="8" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H47" s="8" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="48" customHeight="1" spans="3:8">
+        <v>28</v>
+      </c>
+      <c r="I47" s="1">
+        <v>6</v>
+      </c>
+      <c r="J47" s="1">
+        <v>3</v>
+      </c>
+      <c r="K47" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="48" customHeight="1" spans="3:11">
       <c r="C48" s="1">
         <v>43</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="E48" s="1">
         <f t="shared" si="0"/>
@@ -2541,18 +2778,27 @@
         <v>5</v>
       </c>
       <c r="G48" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="H48" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="H48" s="8" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="49" customHeight="1" spans="3:8">
+      <c r="I48" s="1">
+        <v>81</v>
+      </c>
+      <c r="J48" s="1">
+        <v>3</v>
+      </c>
+      <c r="K48" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="49" customHeight="1" spans="3:11">
       <c r="C49" s="1">
         <v>44</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="E49" s="1">
         <f t="shared" si="0"/>
@@ -2567,13 +2813,22 @@
       <c r="H49" s="8" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="50" customHeight="1" spans="3:8">
+      <c r="I49" s="1">
+        <v>82</v>
+      </c>
+      <c r="J49" s="1">
+        <v>3</v>
+      </c>
+      <c r="K49" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="50" customHeight="1" spans="3:11">
       <c r="C50" s="1">
         <v>45</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="E50" s="1">
         <f t="shared" si="0"/>
@@ -2583,18 +2838,27 @@
         <v>5</v>
       </c>
       <c r="G50" s="8" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H50" s="8" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="51" customHeight="1" spans="3:8">
+      <c r="I50" s="1">
+        <v>83</v>
+      </c>
+      <c r="J50" s="1">
+        <v>3</v>
+      </c>
+      <c r="K50" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="51" customHeight="1" spans="3:11">
       <c r="C51" s="1">
         <v>46</v>
       </c>
       <c r="D51" s="6" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="E51" s="1">
         <f t="shared" si="0"/>
@@ -2604,18 +2868,27 @@
         <v>5</v>
       </c>
       <c r="G51" s="8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H51" s="8" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="52" customHeight="1" spans="3:8">
+        <v>25</v>
+      </c>
+      <c r="I51" s="1">
+        <v>84</v>
+      </c>
+      <c r="J51" s="1">
+        <v>3</v>
+      </c>
+      <c r="K51" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="52" customHeight="1" spans="3:11">
       <c r="C52" s="1">
         <v>47</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="E52" s="1">
         <f t="shared" si="0"/>
@@ -2628,15 +2901,24 @@
         <v>18</v>
       </c>
       <c r="H52" s="8" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="53" customHeight="1" spans="3:8">
+        <v>28</v>
+      </c>
+      <c r="I52" s="1">
+        <v>85</v>
+      </c>
+      <c r="J52" s="1">
+        <v>3</v>
+      </c>
+      <c r="K52" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="53" customHeight="1" spans="3:11">
       <c r="C53" s="1">
         <v>48</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="E53" s="1">
         <f t="shared" si="0"/>
@@ -2646,18 +2928,27 @@
         <v>5</v>
       </c>
       <c r="G53" s="8" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H53" s="8" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="54" customHeight="1" spans="3:8">
+        <v>28</v>
+      </c>
+      <c r="I53" s="1">
+        <v>86</v>
+      </c>
+      <c r="J53" s="1">
+        <v>3</v>
+      </c>
+      <c r="K53" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="54" customHeight="1" spans="3:11">
       <c r="C54" s="1">
         <v>49</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="E54" s="1">
         <f t="shared" si="0"/>
@@ -2667,18 +2958,27 @@
         <v>5</v>
       </c>
       <c r="G54" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="H54" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="H54" s="8" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="55" customHeight="1" spans="3:8">
+      <c r="I54" s="1">
+        <v>13</v>
+      </c>
+      <c r="J54" s="1">
+        <v>3</v>
+      </c>
+      <c r="K54" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="55" customHeight="1" spans="3:11">
       <c r="C55" s="1">
         <v>50</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="E55" s="1">
         <f t="shared" si="0"/>
@@ -2693,13 +2993,22 @@
       <c r="H55" s="8" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="56" customHeight="1" spans="3:8">
+      <c r="I55" s="1">
+        <v>14</v>
+      </c>
+      <c r="J55" s="1">
+        <v>3</v>
+      </c>
+      <c r="K55" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="56" customHeight="1" spans="3:11">
       <c r="C56" s="1">
         <v>51</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="E56" s="1">
         <f t="shared" si="0"/>
@@ -2709,18 +3018,27 @@
         <v>5</v>
       </c>
       <c r="G56" s="8" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H56" s="8" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="57" customHeight="1" spans="3:8">
+      <c r="I56" s="1">
+        <v>22</v>
+      </c>
+      <c r="J56" s="1">
+        <v>3</v>
+      </c>
+      <c r="K56" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="57" customHeight="1" spans="3:11">
       <c r="C57" s="1">
         <v>52</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="E57" s="1">
         <f t="shared" si="0"/>
@@ -2730,18 +3048,27 @@
         <v>5</v>
       </c>
       <c r="G57" s="8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H57" s="8" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="58" customHeight="1" spans="3:8">
+        <v>25</v>
+      </c>
+      <c r="I57" s="1">
+        <v>12</v>
+      </c>
+      <c r="J57" s="1">
+        <v>3</v>
+      </c>
+      <c r="K57" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="58" customHeight="1" spans="3:11">
       <c r="C58" s="1">
         <v>53</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="E58" s="1">
         <f t="shared" si="0"/>
@@ -2754,15 +3081,24 @@
         <v>18</v>
       </c>
       <c r="H58" s="8" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="59" customHeight="1" spans="3:8">
+        <v>28</v>
+      </c>
+      <c r="I58" s="1">
+        <v>10</v>
+      </c>
+      <c r="J58" s="1">
+        <v>3</v>
+      </c>
+      <c r="K58" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="59" customHeight="1" spans="3:11">
       <c r="C59" s="1">
         <v>54</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="E59" s="1">
         <f t="shared" si="0"/>
@@ -2772,18 +3108,27 @@
         <v>5</v>
       </c>
       <c r="G59" s="8" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H59" s="8" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="60" customHeight="1" spans="3:8">
+        <v>28</v>
+      </c>
+      <c r="I59" s="1">
+        <v>11</v>
+      </c>
+      <c r="J59" s="1">
+        <v>3</v>
+      </c>
+      <c r="K59" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="60" customHeight="1" spans="3:11">
       <c r="C60" s="1">
         <v>55</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="E60" s="1">
         <f t="shared" si="0"/>
@@ -2793,18 +3138,27 @@
         <v>5</v>
       </c>
       <c r="G60" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="H60" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="H60" s="8" t="s">
+      <c r="I60" s="1">
+        <v>1</v>
+      </c>
+      <c r="J60" s="1">
+        <v>4</v>
+      </c>
+      <c r="K60" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="61" customHeight="1" spans="3:8">
+    <row r="61" customHeight="1" spans="3:11">
       <c r="C61" s="1">
         <v>56</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="E61" s="1">
         <f t="shared" si="0"/>
@@ -2819,13 +3173,22 @@
       <c r="H61" s="8" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="62" customHeight="1" spans="3:8">
+      <c r="I61" s="1">
+        <v>2</v>
+      </c>
+      <c r="J61" s="1">
+        <v>4</v>
+      </c>
+      <c r="K61" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="62" customHeight="1" spans="3:11">
       <c r="C62" s="1">
         <v>57</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="E62" s="1">
         <f t="shared" si="0"/>
@@ -2835,18 +3198,27 @@
         <v>5</v>
       </c>
       <c r="G62" s="8" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H62" s="8" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="63" customHeight="1" spans="3:8">
+      <c r="I62" s="1">
+        <v>3</v>
+      </c>
+      <c r="J62" s="1">
+        <v>4</v>
+      </c>
+      <c r="K62" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="63" customHeight="1" spans="3:11">
       <c r="C63" s="1">
         <v>58</v>
       </c>
       <c r="D63" s="5" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="E63" s="1">
         <f t="shared" si="0"/>
@@ -2856,18 +3228,27 @@
         <v>5</v>
       </c>
       <c r="G63" s="8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H63" s="8" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="64" customHeight="1" spans="3:8">
+        <v>25</v>
+      </c>
+      <c r="I63" s="1">
+        <v>4</v>
+      </c>
+      <c r="J63" s="1">
+        <v>4</v>
+      </c>
+      <c r="K63" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="64" customHeight="1" spans="3:11">
       <c r="C64" s="1">
         <v>59</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="E64" s="1">
         <f t="shared" si="0"/>
@@ -2880,15 +3261,24 @@
         <v>18</v>
       </c>
       <c r="H64" s="8" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="65" customHeight="1" spans="3:8">
+        <v>28</v>
+      </c>
+      <c r="I64" s="1">
+        <v>5</v>
+      </c>
+      <c r="J64" s="1">
+        <v>4</v>
+      </c>
+      <c r="K64" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="65" customHeight="1" spans="3:11">
       <c r="C65" s="1">
         <v>60</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="E65" s="1">
         <f t="shared" si="0"/>
@@ -2898,18 +3288,27 @@
         <v>5</v>
       </c>
       <c r="G65" s="8" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H65" s="8" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="66" customHeight="1" spans="3:8">
+        <v>28</v>
+      </c>
+      <c r="I65" s="1">
+        <v>6</v>
+      </c>
+      <c r="J65" s="1">
+        <v>4</v>
+      </c>
+      <c r="K65" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="66" customHeight="1" spans="3:11">
       <c r="C66" s="1">
         <v>61</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="E66" s="1">
         <f t="shared" si="0"/>
@@ -2919,18 +3318,27 @@
         <v>5</v>
       </c>
       <c r="G66" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="H66" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="H66" s="8" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="67" customHeight="1" spans="3:8">
+      <c r="I66" s="1">
+        <v>81</v>
+      </c>
+      <c r="J66" s="1">
+        <v>4</v>
+      </c>
+      <c r="K66" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="67" customHeight="1" spans="3:11">
       <c r="C67" s="1">
         <v>62</v>
       </c>
       <c r="D67" s="6" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="E67" s="1">
         <f t="shared" si="0"/>
@@ -2945,13 +3353,22 @@
       <c r="H67" s="8" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="68" customHeight="1" spans="3:8">
+      <c r="I67" s="1">
+        <v>82</v>
+      </c>
+      <c r="J67" s="1">
+        <v>4</v>
+      </c>
+      <c r="K67" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="68" customHeight="1" spans="3:11">
       <c r="C68" s="1">
         <v>63</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="E68" s="1">
         <f t="shared" si="0"/>
@@ -2961,18 +3378,27 @@
         <v>5</v>
       </c>
       <c r="G68" s="8" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H68" s="8" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="69" customHeight="1" spans="3:8">
+      <c r="I68" s="1">
+        <v>83</v>
+      </c>
+      <c r="J68" s="1">
+        <v>4</v>
+      </c>
+      <c r="K68" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="69" customHeight="1" spans="3:11">
       <c r="C69" s="1">
         <v>64</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="E69" s="1">
         <f t="shared" si="0"/>
@@ -2982,18 +3408,27 @@
         <v>5</v>
       </c>
       <c r="G69" s="8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H69" s="8" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="70" customHeight="1" spans="3:8">
+        <v>25</v>
+      </c>
+      <c r="I69" s="1">
+        <v>84</v>
+      </c>
+      <c r="J69" s="1">
+        <v>4</v>
+      </c>
+      <c r="K69" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="70" customHeight="1" spans="3:11">
       <c r="C70" s="1">
         <v>65</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="E70" s="1">
         <f t="shared" ref="E70:E77" si="1">INT((C70-1)/6)+1101</f>
@@ -3006,15 +3441,24 @@
         <v>18</v>
       </c>
       <c r="H70" s="8" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="71" customHeight="1" spans="3:8">
+        <v>28</v>
+      </c>
+      <c r="I70" s="1">
+        <v>85</v>
+      </c>
+      <c r="J70" s="1">
+        <v>4</v>
+      </c>
+      <c r="K70" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="71" customHeight="1" spans="3:11">
       <c r="C71" s="1">
         <v>66</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="E71" s="1">
         <f t="shared" si="1"/>
@@ -3024,18 +3468,27 @@
         <v>5</v>
       </c>
       <c r="G71" s="8" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H71" s="8" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="72" customHeight="1" spans="3:8">
+        <v>28</v>
+      </c>
+      <c r="I71" s="1">
+        <v>86</v>
+      </c>
+      <c r="J71" s="1">
+        <v>4</v>
+      </c>
+      <c r="K71" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="72" customHeight="1" spans="3:11">
       <c r="C72" s="1">
         <v>67</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="E72" s="1">
         <f t="shared" si="1"/>
@@ -3045,18 +3498,27 @@
         <v>5</v>
       </c>
       <c r="G72" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="H72" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="H72" s="8" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="73" customHeight="1" spans="3:8">
+      <c r="I72" s="1">
+        <v>13</v>
+      </c>
+      <c r="J72" s="1">
+        <v>4</v>
+      </c>
+      <c r="K72" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="73" customHeight="1" spans="3:11">
       <c r="C73" s="1">
         <v>68</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="E73" s="1">
         <f t="shared" si="1"/>
@@ -3071,13 +3533,22 @@
       <c r="H73" s="8" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="74" customHeight="1" spans="3:8">
+      <c r="I73" s="1">
+        <v>14</v>
+      </c>
+      <c r="J73" s="1">
+        <v>4</v>
+      </c>
+      <c r="K73" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="74" customHeight="1" spans="3:11">
       <c r="C74" s="1">
         <v>69</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="E74" s="1">
         <f t="shared" si="1"/>
@@ -3087,18 +3558,27 @@
         <v>5</v>
       </c>
       <c r="G74" s="8" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H74" s="8" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="75" customHeight="1" spans="3:8">
+      <c r="I74" s="1">
+        <v>22</v>
+      </c>
+      <c r="J74" s="1">
+        <v>4</v>
+      </c>
+      <c r="K74" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="75" customHeight="1" spans="3:11">
       <c r="C75" s="1">
         <v>70</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="E75" s="1">
         <f t="shared" si="1"/>
@@ -3108,18 +3588,27 @@
         <v>5</v>
       </c>
       <c r="G75" s="8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H75" s="8" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="76" customHeight="1" spans="3:8">
+        <v>25</v>
+      </c>
+      <c r="I75" s="1">
+        <v>12</v>
+      </c>
+      <c r="J75" s="1">
+        <v>4</v>
+      </c>
+      <c r="K75" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="76" customHeight="1" spans="3:11">
       <c r="C76" s="1">
         <v>71</v>
       </c>
       <c r="D76" s="5" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="E76" s="1">
         <f t="shared" si="1"/>
@@ -3132,15 +3621,24 @@
         <v>18</v>
       </c>
       <c r="H76" s="8" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="77" customHeight="1" spans="3:8">
+        <v>28</v>
+      </c>
+      <c r="I76" s="1">
+        <v>10</v>
+      </c>
+      <c r="J76" s="1">
+        <v>4</v>
+      </c>
+      <c r="K76" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="77" customHeight="1" spans="3:11">
       <c r="C77" s="1">
         <v>72</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="E77" s="1">
         <f t="shared" si="1"/>
@@ -3150,10 +3648,19 @@
         <v>5</v>
       </c>
       <c r="G77" s="8" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H77" s="8" t="s">
-        <v>25</v>
+        <v>28</v>
+      </c>
+      <c r="I77" s="1">
+        <v>11</v>
+      </c>
+      <c r="J77" s="1">
+        <v>4</v>
+      </c>
+      <c r="K77" s="1" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="106" customHeight="1" spans="5:8">
@@ -3170,7 +3677,7 @@
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="M3:M5 C3:D5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="K3:K5 C3:D5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
     <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="E3:H5" errorStyle="warning">

--- a/Excel/PetConfig.xlsx
+++ b/Excel/PetConfig.xlsx
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="141">
   <si>
     <t>#</t>
   </si>
@@ -137,7 +137,7 @@
     <t>蜘蛛宝宝</t>
   </si>
   <si>
-    <t>5000,10</t>
+    <t>2000,10</t>
   </si>
   <si>
     <t>基础物攻</t>
@@ -161,156 +161,201 @@
     <t>毒蛆宝宝</t>
   </si>
   <si>
-    <t>10000,15</t>
+    <t>4000,15</t>
+  </si>
+  <si>
+    <t>杀敌经验</t>
+  </si>
+  <si>
+    <t>蜈蚣宝宝</t>
+  </si>
+  <si>
+    <t>400,15</t>
+  </si>
+  <si>
+    <t>经验加成</t>
+  </si>
+  <si>
+    <t>双头宝宝</t>
+  </si>
+  <si>
+    <t>品质加成</t>
+  </si>
+  <si>
+    <t>蛛王宝宝</t>
+  </si>
+  <si>
+    <t>7000,20</t>
+  </si>
+  <si>
+    <t>蛇宝宝</t>
+  </si>
+  <si>
+    <t>700,20</t>
+  </si>
+  <si>
+    <t>巨鳄宝宝</t>
+  </si>
+  <si>
+    <t>乌鸦宝宝</t>
+  </si>
+  <si>
+    <t>10000,25</t>
+  </si>
+  <si>
+    <t>行尸宝宝</t>
+  </si>
+  <si>
+    <t>1000,25</t>
+  </si>
+  <si>
+    <t>尸鬼宝宝</t>
+  </si>
+  <si>
+    <t>蝙蝠宝宝</t>
+  </si>
+  <si>
+    <t>20000,30</t>
+  </si>
+  <si>
+    <t>杀敌金币</t>
+  </si>
+  <si>
+    <t>尸魔宝宝</t>
+  </si>
+  <si>
+    <t>2000,30</t>
   </si>
   <si>
     <t>金币加成</t>
   </si>
   <si>
-    <t>蜈蚣宝宝</t>
-  </si>
-  <si>
-    <t>400,15</t>
-  </si>
-  <si>
-    <t>经验加成</t>
-  </si>
-  <si>
-    <t>双头宝宝</t>
-  </si>
-  <si>
-    <t>品质加成</t>
-  </si>
-  <si>
-    <t>蛛王宝宝</t>
-  </si>
-  <si>
-    <t>50000,20</t>
+    <t>尸卫宝宝</t>
   </si>
   <si>
     <t>掉率加成</t>
   </si>
   <si>
-    <t>蛇宝宝</t>
-  </si>
-  <si>
-    <t>800,20</t>
-  </si>
-  <si>
-    <t>杀敌金币</t>
-  </si>
-  <si>
-    <t>巨鳄宝宝</t>
-  </si>
-  <si>
-    <t>杀敌经验</t>
-  </si>
-  <si>
-    <t>乌鸦宝宝</t>
-  </si>
-  <si>
-    <t>100000,20</t>
+    <t>花妖宝宝</t>
+  </si>
+  <si>
+    <t>30000,35</t>
+  </si>
+  <si>
+    <t>树精宝宝</t>
+  </si>
+  <si>
+    <t>3000,35</t>
+  </si>
+  <si>
+    <t>鱼人宝宝</t>
+  </si>
+  <si>
+    <t>狼人宝宝</t>
+  </si>
+  <si>
+    <t>40000,40</t>
+  </si>
+  <si>
+    <t>蠕虫宝宝</t>
+  </si>
+  <si>
+    <t>4000,40</t>
+  </si>
+  <si>
+    <t>角鹿宝宝</t>
+  </si>
+  <si>
+    <t>恶犬宝宝</t>
+  </si>
+  <si>
+    <t>50000,45</t>
   </si>
   <si>
     <t>命中</t>
   </si>
   <si>
-    <t>行尸宝宝</t>
-  </si>
-  <si>
-    <t>1500,20</t>
+    <t>守卫宝宝</t>
+  </si>
+  <si>
+    <t>5000,45</t>
   </si>
   <si>
     <t>闪避</t>
   </si>
   <si>
-    <t>尸鬼宝宝</t>
+    <t>射手宝宝</t>
   </si>
   <si>
     <t>爆伤</t>
   </si>
   <si>
-    <t>蝙蝠宝宝</t>
-  </si>
-  <si>
-    <t>200000,25</t>
+    <t>幽灵宝宝</t>
+  </si>
+  <si>
+    <t>60000,50</t>
+  </si>
+  <si>
+    <t>法师宝宝</t>
+  </si>
+  <si>
+    <t>6000,50</t>
+  </si>
+  <si>
+    <t>骸骨宝宝</t>
+  </si>
+  <si>
+    <t>战猪宝宝</t>
+  </si>
+  <si>
+    <t>70000,55</t>
+  </si>
+  <si>
+    <t>勇猪宝宝</t>
+  </si>
+  <si>
+    <t>7000,55</t>
+  </si>
+  <si>
+    <t>力猪宝宝</t>
+  </si>
+  <si>
+    <t>萨满宝宝</t>
+  </si>
+  <si>
+    <t>1001,2001</t>
+  </si>
+  <si>
+    <t>60,5</t>
   </si>
   <si>
     <t>移动速度</t>
   </si>
   <si>
-    <t>尸魔宝宝</t>
-  </si>
-  <si>
-    <t>3000,25</t>
+    <t>战将宝宝</t>
+  </si>
+  <si>
+    <t>1002,2002</t>
   </si>
   <si>
     <t>技能冷却</t>
   </si>
   <si>
-    <t>尸卫宝宝</t>
+    <t>亲卫宝宝</t>
+  </si>
+  <si>
+    <t>1003,2003</t>
   </si>
   <si>
     <t>攻速</t>
   </si>
   <si>
-    <t>花妖宝宝</t>
-  </si>
-  <si>
-    <t>树精宝宝</t>
-  </si>
-  <si>
-    <t>鱼人宝宝</t>
-  </si>
-  <si>
-    <t>狼人宝宝</t>
-  </si>
-  <si>
-    <t>蠕虫宝宝</t>
-  </si>
-  <si>
-    <t>角鹿宝宝</t>
-  </si>
-  <si>
-    <t>恶犬宝宝</t>
-  </si>
-  <si>
-    <t>守卫宝宝</t>
-  </si>
-  <si>
-    <t>射手宝宝</t>
-  </si>
-  <si>
-    <t>幽灵宝宝</t>
-  </si>
-  <si>
-    <t>法师宝宝</t>
-  </si>
-  <si>
-    <t>骸骨宝宝</t>
-  </si>
-  <si>
-    <t>战猪宝宝</t>
-  </si>
-  <si>
-    <t>勇猪宝宝</t>
-  </si>
-  <si>
-    <t>力猪宝宝</t>
-  </si>
-  <si>
-    <t>萨满宝宝</t>
-  </si>
-  <si>
-    <t>战将宝宝</t>
-  </si>
-  <si>
-    <t>亲卫宝宝</t>
-  </si>
-  <si>
     <t>花宝宝</t>
   </si>
   <si>
+    <t>70,10</t>
+  </si>
+  <si>
     <t>甲虫宝宝</t>
   </si>
   <si>
@@ -320,6 +365,9 @@
     <t>赤炎宝宝</t>
   </si>
   <si>
+    <t>80,15</t>
+  </si>
+  <si>
     <t>魔姬宝宝</t>
   </si>
   <si>
@@ -329,6 +377,9 @@
     <t>冰蝎宝宝</t>
   </si>
   <si>
+    <t>90,20</t>
+  </si>
+  <si>
     <t>寒冰宝宝</t>
   </si>
   <si>
@@ -338,12 +389,18 @@
     <t>霜骑宝宝</t>
   </si>
   <si>
+    <t>100,25</t>
+  </si>
+  <si>
     <t>巨霜宝宝</t>
   </si>
   <si>
     <t>鬼蛛宝宝</t>
   </si>
   <si>
+    <t>110,30</t>
+  </si>
+  <si>
     <t>蛇姬宝宝</t>
   </si>
   <si>
@@ -353,6 +410,9 @@
     <t>暗夜宝宝</t>
   </si>
   <si>
+    <t>120,35</t>
+  </si>
+  <si>
     <t>祭司宝宝</t>
   </si>
   <si>
@@ -362,12 +422,18 @@
     <t>人马宝宝</t>
   </si>
   <si>
+    <t>130,40</t>
+  </si>
+  <si>
     <t>巨熊宝宝</t>
   </si>
   <si>
     <t>屠戮宝宝</t>
   </si>
   <si>
+    <t>140,45</t>
+  </si>
+  <si>
     <t>牛头宝宝</t>
   </si>
   <si>
@@ -377,6 +443,9 @@
     <t>魔瞳宝宝</t>
   </si>
   <si>
+    <t>150,50</t>
+  </si>
+  <si>
     <t>收割宝宝</t>
   </si>
   <si>
@@ -386,12 +455,18 @@
     <t>恶魔宝宝</t>
   </si>
   <si>
+    <t>160,55</t>
+  </si>
+  <si>
     <t>黑骑宝宝</t>
   </si>
   <si>
     <t>巫师宝宝</t>
   </si>
   <si>
+    <t>170,60</t>
+  </si>
+  <si>
     <t>三头宝宝</t>
   </si>
   <si>
@@ -399,6 +474,9 @@
   </si>
   <si>
     <t>魇兽宝宝</t>
+  </si>
+  <si>
+    <t>175,65</t>
   </si>
   <si>
     <t>大魔宝宝</t>
@@ -1399,7 +1477,7 @@
     <col min="4" max="4" width="12.8333333333333" style="1" customWidth="1"/>
     <col min="5" max="6" width="13" style="1" customWidth="1"/>
     <col min="7" max="7" width="14.1666666666667" style="1" customWidth="1"/>
-    <col min="8" max="8" width="13" style="1" customWidth="1"/>
+    <col min="8" max="8" width="16.25" style="1" customWidth="1"/>
     <col min="9" max="9" width="14.8333333333333" style="1" customWidth="1"/>
     <col min="10" max="10" width="13" style="1" customWidth="1"/>
     <col min="11" max="11" width="17" style="1" customWidth="1"/>
@@ -1704,7 +1782,7 @@
         <v>33</v>
       </c>
       <c r="I12" s="1">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="J12" s="1">
         <v>1</v>
@@ -1794,13 +1872,13 @@
         <v>41</v>
       </c>
       <c r="I15" s="1">
-        <v>84</v>
+        <v>1</v>
       </c>
       <c r="J15" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>42</v>
+        <v>16</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -1808,7 +1886,7 @@
         <v>11</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E16" s="1">
         <f t="shared" si="0"/>
@@ -1821,16 +1899,16 @@
         <v>18</v>
       </c>
       <c r="H16" s="8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I16" s="1">
-        <v>85</v>
+        <v>2</v>
       </c>
       <c r="J16" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>45</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -1838,7 +1916,7 @@
         <v>12</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E17" s="1">
         <f t="shared" si="0"/>
@@ -1851,16 +1929,16 @@
         <v>22</v>
       </c>
       <c r="H17" s="8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I17" s="1">
-        <v>86</v>
+        <v>3</v>
       </c>
       <c r="J17" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -1868,7 +1946,7 @@
         <v>13</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E18" s="1">
         <f t="shared" si="0"/>
@@ -1881,16 +1959,16 @@
         <v>14</v>
       </c>
       <c r="H18" s="8" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="I18" s="1">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="J18" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>50</v>
+        <v>26</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -1898,7 +1976,7 @@
         <v>14</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="E19" s="1">
         <f t="shared" si="0"/>
@@ -1911,16 +1989,16 @@
         <v>18</v>
       </c>
       <c r="H19" s="8" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="I19" s="1">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="J19" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>53</v>
+        <v>29</v>
       </c>
     </row>
     <row r="20" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -1928,7 +2006,7 @@
         <v>15</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="E20" s="1">
         <f t="shared" si="0"/>
@@ -1941,16 +2019,16 @@
         <v>22</v>
       </c>
       <c r="H20" s="8" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="I20" s="1">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="J20" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>55</v>
+        <v>31</v>
       </c>
     </row>
     <row r="21" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -1958,7 +2036,7 @@
         <v>16</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="E21" s="1">
         <f t="shared" si="0"/>
@@ -1971,16 +2049,16 @@
         <v>14</v>
       </c>
       <c r="H21" s="8" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="I21" s="1">
-        <v>12</v>
+        <v>85</v>
       </c>
       <c r="J21" s="1">
         <v>1</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
     </row>
     <row r="22" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -1988,7 +2066,7 @@
         <v>17</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="E22" s="1">
         <f t="shared" si="0"/>
@@ -2001,16 +2079,16 @@
         <v>18</v>
       </c>
       <c r="H22" s="8" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="I22" s="1">
-        <v>10</v>
+        <v>81</v>
       </c>
       <c r="J22" s="1">
         <v>1</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -2018,7 +2096,7 @@
         <v>18</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="E23" s="1">
         <f t="shared" si="0"/>
@@ -2031,16 +2109,16 @@
         <v>22</v>
       </c>
       <c r="H23" s="8" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="I23" s="1">
-        <v>11</v>
+        <v>84</v>
       </c>
       <c r="J23" s="1">
         <v>1</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -2048,7 +2126,7 @@
         <v>19</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="E24" s="1">
         <f t="shared" si="0"/>
@@ -2061,13 +2139,13 @@
         <v>14</v>
       </c>
       <c r="H24" s="8" t="s">
-        <v>15</v>
+        <v>59</v>
       </c>
       <c r="I24" s="1">
         <v>1</v>
       </c>
       <c r="J24" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K24" s="1" t="s">
         <v>16</v>
@@ -2078,7 +2156,7 @@
         <v>20</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="E25" s="1">
         <f t="shared" si="0"/>
@@ -2091,13 +2169,13 @@
         <v>18</v>
       </c>
       <c r="H25" s="8" t="s">
-        <v>19</v>
+        <v>61</v>
       </c>
       <c r="I25" s="1">
         <v>2</v>
       </c>
       <c r="J25" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K25" s="1" t="s">
         <v>20</v>
@@ -2108,7 +2186,7 @@
         <v>21</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="E26" s="1">
         <f t="shared" si="0"/>
@@ -2121,13 +2199,13 @@
         <v>22</v>
       </c>
       <c r="H26" s="8" t="s">
-        <v>19</v>
+        <v>61</v>
       </c>
       <c r="I26" s="1">
         <v>3</v>
       </c>
       <c r="J26" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K26" s="1" t="s">
         <v>23</v>
@@ -2138,7 +2216,7 @@
         <v>22</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="E27" s="1">
         <f t="shared" si="0"/>
@@ -2151,13 +2229,13 @@
         <v>14</v>
       </c>
       <c r="H27" s="8" t="s">
-        <v>25</v>
+        <v>64</v>
       </c>
       <c r="I27" s="1">
         <v>4</v>
       </c>
       <c r="J27" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K27" s="1" t="s">
         <v>26</v>
@@ -2168,7 +2246,7 @@
         <v>23</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="E28" s="1">
         <f t="shared" si="0"/>
@@ -2181,13 +2259,13 @@
         <v>18</v>
       </c>
       <c r="H28" s="8" t="s">
-        <v>28</v>
+        <v>66</v>
       </c>
       <c r="I28" s="1">
         <v>5</v>
       </c>
       <c r="J28" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K28" s="1" t="s">
         <v>29</v>
@@ -2198,7 +2276,7 @@
         <v>24</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E29" s="1">
         <f t="shared" si="0"/>
@@ -2211,13 +2289,13 @@
         <v>22</v>
       </c>
       <c r="H29" s="8" t="s">
-        <v>28</v>
+        <v>66</v>
       </c>
       <c r="I29" s="1">
         <v>6</v>
       </c>
       <c r="J29" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K29" s="1" t="s">
         <v>31</v>
@@ -2228,7 +2306,7 @@
         <v>25</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E30" s="1">
         <f t="shared" si="0"/>
@@ -2241,16 +2319,16 @@
         <v>14</v>
       </c>
       <c r="H30" s="8" t="s">
-        <v>15</v>
+        <v>69</v>
       </c>
       <c r="I30" s="1">
-        <v>81</v>
+        <v>13</v>
       </c>
       <c r="J30" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
     </row>
     <row r="31" customHeight="1" spans="3:11">
@@ -2271,16 +2349,16 @@
         <v>18</v>
       </c>
       <c r="H31" s="8" t="s">
-        <v>19</v>
+        <v>72</v>
       </c>
       <c r="I31" s="1">
-        <v>82</v>
+        <v>14</v>
       </c>
       <c r="J31" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K31" s="1" t="s">
-        <v>37</v>
+        <v>73</v>
       </c>
     </row>
     <row r="32" customHeight="1" spans="3:11">
@@ -2288,7 +2366,7 @@
         <v>27</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E32" s="1">
         <f t="shared" si="0"/>
@@ -2301,16 +2379,16 @@
         <v>22</v>
       </c>
       <c r="H32" s="8" t="s">
-        <v>19</v>
+        <v>72</v>
       </c>
       <c r="I32" s="1">
-        <v>83</v>
+        <v>22</v>
       </c>
       <c r="J32" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K32" s="1" t="s">
-        <v>39</v>
+        <v>75</v>
       </c>
     </row>
     <row r="33" customHeight="1" spans="3:11">
@@ -2318,7 +2396,7 @@
         <v>28</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="E33" s="1">
         <f t="shared" si="0"/>
@@ -2331,16 +2409,16 @@
         <v>14</v>
       </c>
       <c r="H33" s="8" t="s">
-        <v>25</v>
+        <v>77</v>
       </c>
       <c r="I33" s="1">
-        <v>84</v>
+        <v>1</v>
       </c>
       <c r="J33" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K33" s="1" t="s">
-        <v>42</v>
+        <v>16</v>
       </c>
     </row>
     <row r="34" customHeight="1" spans="3:11">
@@ -2348,7 +2426,7 @@
         <v>29</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="E34" s="1">
         <f t="shared" si="0"/>
@@ -2361,16 +2439,16 @@
         <v>18</v>
       </c>
       <c r="H34" s="8" t="s">
-        <v>28</v>
+        <v>79</v>
       </c>
       <c r="I34" s="1">
-        <v>85</v>
+        <v>2</v>
       </c>
       <c r="J34" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K34" s="1" t="s">
-        <v>45</v>
+        <v>20</v>
       </c>
     </row>
     <row r="35" customHeight="1" spans="3:11">
@@ -2378,7 +2456,7 @@
         <v>30</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="E35" s="1">
         <f t="shared" si="0"/>
@@ -2391,16 +2469,16 @@
         <v>22</v>
       </c>
       <c r="H35" s="8" t="s">
-        <v>28</v>
+        <v>79</v>
       </c>
       <c r="I35" s="1">
-        <v>86</v>
+        <v>3</v>
       </c>
       <c r="J35" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K35" s="1" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
     </row>
     <row r="36" customHeight="1" spans="3:11">
@@ -2408,7 +2486,7 @@
         <v>31</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="E36" s="1">
         <f t="shared" si="0"/>
@@ -2421,16 +2499,16 @@
         <v>14</v>
       </c>
       <c r="H36" s="8" t="s">
-        <v>15</v>
+        <v>82</v>
       </c>
       <c r="I36" s="1">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="J36" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K36" s="1" t="s">
-        <v>50</v>
+        <v>26</v>
       </c>
     </row>
     <row r="37" customHeight="1" spans="3:11">
@@ -2438,7 +2516,7 @@
         <v>32</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="E37" s="1">
         <f t="shared" si="0"/>
@@ -2451,16 +2529,16 @@
         <v>18</v>
       </c>
       <c r="H37" s="8" t="s">
-        <v>19</v>
+        <v>84</v>
       </c>
       <c r="I37" s="1">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="J37" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K37" s="1" t="s">
-        <v>53</v>
+        <v>29</v>
       </c>
     </row>
     <row r="38" customHeight="1" spans="3:11">
@@ -2468,7 +2546,7 @@
         <v>33</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="E38" s="1">
         <f t="shared" si="0"/>
@@ -2481,16 +2559,16 @@
         <v>22</v>
       </c>
       <c r="H38" s="8" t="s">
-        <v>19</v>
+        <v>84</v>
       </c>
       <c r="I38" s="1">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="J38" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K38" s="1" t="s">
-        <v>55</v>
+        <v>31</v>
       </c>
     </row>
     <row r="39" customHeight="1" spans="3:11">
@@ -2498,7 +2576,7 @@
         <v>34</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="E39" s="1">
         <f t="shared" si="0"/>
@@ -2508,19 +2586,19 @@
         <v>5</v>
       </c>
       <c r="G39" s="8" t="s">
-        <v>14</v>
+        <v>87</v>
       </c>
       <c r="H39" s="8" t="s">
-        <v>25</v>
+        <v>88</v>
       </c>
       <c r="I39" s="1">
         <v>12</v>
       </c>
       <c r="J39" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K39" s="1" t="s">
-        <v>58</v>
+        <v>89</v>
       </c>
     </row>
     <row r="40" customHeight="1" spans="3:11">
@@ -2528,7 +2606,7 @@
         <v>35</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="E40" s="1">
         <f t="shared" si="0"/>
@@ -2538,19 +2616,19 @@
         <v>5</v>
       </c>
       <c r="G40" s="8" t="s">
-        <v>18</v>
+        <v>91</v>
       </c>
       <c r="H40" s="8" t="s">
-        <v>28</v>
+        <v>88</v>
       </c>
       <c r="I40" s="1">
         <v>10</v>
       </c>
       <c r="J40" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K40" s="1" t="s">
-        <v>61</v>
+        <v>92</v>
       </c>
     </row>
     <row r="41" customHeight="1" spans="3:11">
@@ -2558,7 +2636,7 @@
         <v>36</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="E41" s="1">
         <f t="shared" si="0"/>
@@ -2568,19 +2646,19 @@
         <v>5</v>
       </c>
       <c r="G41" s="8" t="s">
-        <v>22</v>
+        <v>94</v>
       </c>
       <c r="H41" s="8" t="s">
-        <v>28</v>
+        <v>88</v>
       </c>
       <c r="I41" s="1">
         <v>11</v>
       </c>
       <c r="J41" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K41" s="1" t="s">
-        <v>63</v>
+        <v>95</v>
       </c>
     </row>
     <row r="42" customHeight="1" spans="3:11">
@@ -2588,7 +2666,7 @@
         <v>37</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>82</v>
+        <v>96</v>
       </c>
       <c r="E42" s="1">
         <f t="shared" si="0"/>
@@ -2598,16 +2676,16 @@
         <v>5</v>
       </c>
       <c r="G42" s="8" t="s">
-        <v>14</v>
+        <v>87</v>
       </c>
       <c r="H42" s="8" t="s">
-        <v>15</v>
+        <v>97</v>
       </c>
       <c r="I42" s="1">
         <v>1</v>
       </c>
       <c r="J42" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K42" s="1" t="s">
         <v>16</v>
@@ -2618,7 +2696,7 @@
         <v>38</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>83</v>
+        <v>98</v>
       </c>
       <c r="E43" s="1">
         <f t="shared" si="0"/>
@@ -2628,16 +2706,16 @@
         <v>5</v>
       </c>
       <c r="G43" s="8" t="s">
-        <v>18</v>
+        <v>91</v>
       </c>
       <c r="H43" s="8" t="s">
-        <v>19</v>
+        <v>97</v>
       </c>
       <c r="I43" s="1">
         <v>2</v>
       </c>
       <c r="J43" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K43" s="1" t="s">
         <v>20</v>
@@ -2648,7 +2726,7 @@
         <v>39</v>
       </c>
       <c r="D44" s="5" t="s">
-        <v>84</v>
+        <v>99</v>
       </c>
       <c r="E44" s="1">
         <f t="shared" si="0"/>
@@ -2658,16 +2736,16 @@
         <v>5</v>
       </c>
       <c r="G44" s="8" t="s">
-        <v>22</v>
+        <v>94</v>
       </c>
       <c r="H44" s="8" t="s">
-        <v>19</v>
+        <v>97</v>
       </c>
       <c r="I44" s="1">
         <v>3</v>
       </c>
       <c r="J44" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K44" s="1" t="s">
         <v>23</v>
@@ -2678,7 +2756,7 @@
         <v>40</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="E45" s="1">
         <f t="shared" si="0"/>
@@ -2688,16 +2766,16 @@
         <v>5</v>
       </c>
       <c r="G45" s="8" t="s">
-        <v>14</v>
+        <v>87</v>
       </c>
       <c r="H45" s="8" t="s">
-        <v>25</v>
+        <v>101</v>
       </c>
       <c r="I45" s="1">
         <v>4</v>
       </c>
       <c r="J45" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K45" s="1" t="s">
         <v>26</v>
@@ -2708,7 +2786,7 @@
         <v>41</v>
       </c>
       <c r="D46" s="6" t="s">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="E46" s="1">
         <f t="shared" si="0"/>
@@ -2718,16 +2796,16 @@
         <v>5</v>
       </c>
       <c r="G46" s="8" t="s">
-        <v>18</v>
+        <v>91</v>
       </c>
       <c r="H46" s="8" t="s">
-        <v>28</v>
+        <v>101</v>
       </c>
       <c r="I46" s="1">
         <v>5</v>
       </c>
       <c r="J46" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K46" s="1" t="s">
         <v>29</v>
@@ -2738,7 +2816,7 @@
         <v>42</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>87</v>
+        <v>103</v>
       </c>
       <c r="E47" s="1">
         <f t="shared" si="0"/>
@@ -2748,16 +2826,16 @@
         <v>5</v>
       </c>
       <c r="G47" s="8" t="s">
-        <v>22</v>
+        <v>94</v>
       </c>
       <c r="H47" s="8" t="s">
-        <v>28</v>
+        <v>101</v>
       </c>
       <c r="I47" s="1">
         <v>6</v>
       </c>
       <c r="J47" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K47" s="1" t="s">
         <v>31</v>
@@ -2768,7 +2846,7 @@
         <v>43</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="E48" s="1">
         <f t="shared" si="0"/>
@@ -2778,16 +2856,16 @@
         <v>5</v>
       </c>
       <c r="G48" s="8" t="s">
-        <v>14</v>
+        <v>87</v>
       </c>
       <c r="H48" s="8" t="s">
-        <v>15</v>
+        <v>105</v>
       </c>
       <c r="I48" s="1">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="J48" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K48" s="1" t="s">
         <v>34</v>
@@ -2798,7 +2876,7 @@
         <v>44</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>89</v>
+        <v>106</v>
       </c>
       <c r="E49" s="1">
         <f t="shared" si="0"/>
@@ -2808,16 +2886,16 @@
         <v>5</v>
       </c>
       <c r="G49" s="8" t="s">
-        <v>18</v>
+        <v>91</v>
       </c>
       <c r="H49" s="8" t="s">
-        <v>19</v>
+        <v>105</v>
       </c>
       <c r="I49" s="1">
         <v>82</v>
       </c>
       <c r="J49" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K49" s="1" t="s">
         <v>37</v>
@@ -2828,7 +2906,7 @@
         <v>45</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>90</v>
+        <v>107</v>
       </c>
       <c r="E50" s="1">
         <f t="shared" si="0"/>
@@ -2838,16 +2916,16 @@
         <v>5</v>
       </c>
       <c r="G50" s="8" t="s">
-        <v>22</v>
+        <v>94</v>
       </c>
       <c r="H50" s="8" t="s">
-        <v>19</v>
+        <v>105</v>
       </c>
       <c r="I50" s="1">
         <v>83</v>
       </c>
       <c r="J50" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K50" s="1" t="s">
         <v>39</v>
@@ -2858,7 +2936,7 @@
         <v>46</v>
       </c>
       <c r="D51" s="6" t="s">
-        <v>91</v>
+        <v>108</v>
       </c>
       <c r="E51" s="1">
         <f t="shared" si="0"/>
@@ -2868,19 +2946,19 @@
         <v>5</v>
       </c>
       <c r="G51" s="8" t="s">
-        <v>14</v>
+        <v>87</v>
       </c>
       <c r="H51" s="8" t="s">
-        <v>25</v>
+        <v>109</v>
       </c>
       <c r="I51" s="1">
-        <v>84</v>
+        <v>1</v>
       </c>
       <c r="J51" s="1">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K51" s="1" t="s">
-        <v>42</v>
+        <v>16</v>
       </c>
     </row>
     <row r="52" customHeight="1" spans="3:11">
@@ -2888,7 +2966,7 @@
         <v>47</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>92</v>
+        <v>110</v>
       </c>
       <c r="E52" s="1">
         <f t="shared" si="0"/>
@@ -2898,19 +2976,19 @@
         <v>5</v>
       </c>
       <c r="G52" s="8" t="s">
-        <v>18</v>
+        <v>91</v>
       </c>
       <c r="H52" s="8" t="s">
-        <v>28</v>
+        <v>109</v>
       </c>
       <c r="I52" s="1">
-        <v>85</v>
+        <v>2</v>
       </c>
       <c r="J52" s="1">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K52" s="1" t="s">
-        <v>45</v>
+        <v>20</v>
       </c>
     </row>
     <row r="53" customHeight="1" spans="3:11">
@@ -2918,7 +2996,7 @@
         <v>48</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>89</v>
+        <v>106</v>
       </c>
       <c r="E53" s="1">
         <f t="shared" si="0"/>
@@ -2928,19 +3006,19 @@
         <v>5</v>
       </c>
       <c r="G53" s="8" t="s">
-        <v>22</v>
+        <v>94</v>
       </c>
       <c r="H53" s="8" t="s">
-        <v>28</v>
+        <v>109</v>
       </c>
       <c r="I53" s="1">
-        <v>86</v>
+        <v>3</v>
       </c>
       <c r="J53" s="1">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K53" s="1" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
     </row>
     <row r="54" customHeight="1" spans="3:11">
@@ -2948,7 +3026,7 @@
         <v>49</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>93</v>
+        <v>111</v>
       </c>
       <c r="E54" s="1">
         <f t="shared" si="0"/>
@@ -2958,19 +3036,19 @@
         <v>5</v>
       </c>
       <c r="G54" s="8" t="s">
-        <v>14</v>
+        <v>87</v>
       </c>
       <c r="H54" s="8" t="s">
-        <v>15</v>
+        <v>112</v>
       </c>
       <c r="I54" s="1">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="J54" s="1">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K54" s="1" t="s">
-        <v>50</v>
+        <v>26</v>
       </c>
     </row>
     <row r="55" customHeight="1" spans="3:11">
@@ -2978,7 +3056,7 @@
         <v>50</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>94</v>
+        <v>113</v>
       </c>
       <c r="E55" s="1">
         <f t="shared" si="0"/>
@@ -2988,19 +3066,19 @@
         <v>5</v>
       </c>
       <c r="G55" s="8" t="s">
-        <v>18</v>
+        <v>91</v>
       </c>
       <c r="H55" s="8" t="s">
-        <v>19</v>
+        <v>112</v>
       </c>
       <c r="I55" s="1">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="J55" s="1">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K55" s="1" t="s">
-        <v>53</v>
+        <v>29</v>
       </c>
     </row>
     <row r="56" customHeight="1" spans="3:11">
@@ -3008,7 +3086,7 @@
         <v>51</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>95</v>
+        <v>114</v>
       </c>
       <c r="E56" s="1">
         <f t="shared" si="0"/>
@@ -3018,19 +3096,19 @@
         <v>5</v>
       </c>
       <c r="G56" s="8" t="s">
-        <v>22</v>
+        <v>94</v>
       </c>
       <c r="H56" s="8" t="s">
-        <v>19</v>
+        <v>112</v>
       </c>
       <c r="I56" s="1">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="J56" s="1">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K56" s="1" t="s">
-        <v>55</v>
+        <v>31</v>
       </c>
     </row>
     <row r="57" customHeight="1" spans="3:11">
@@ -3038,7 +3116,7 @@
         <v>52</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>96</v>
+        <v>115</v>
       </c>
       <c r="E57" s="1">
         <f t="shared" si="0"/>
@@ -3048,19 +3126,19 @@
         <v>5</v>
       </c>
       <c r="G57" s="8" t="s">
-        <v>14</v>
+        <v>87</v>
       </c>
       <c r="H57" s="8" t="s">
-        <v>25</v>
+        <v>116</v>
       </c>
       <c r="I57" s="1">
-        <v>12</v>
+        <v>85</v>
       </c>
       <c r="J57" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K57" s="1" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
     </row>
     <row r="58" customHeight="1" spans="3:11">
@@ -3068,7 +3146,7 @@
         <v>53</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>97</v>
+        <v>117</v>
       </c>
       <c r="E58" s="1">
         <f t="shared" si="0"/>
@@ -3078,19 +3156,19 @@
         <v>5</v>
       </c>
       <c r="G58" s="8" t="s">
-        <v>18</v>
+        <v>91</v>
       </c>
       <c r="H58" s="8" t="s">
-        <v>28</v>
+        <v>116</v>
       </c>
       <c r="I58" s="1">
-        <v>10</v>
+        <v>81</v>
       </c>
       <c r="J58" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K58" s="1" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
     </row>
     <row r="59" customHeight="1" spans="3:11">
@@ -3098,7 +3176,7 @@
         <v>54</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>98</v>
+        <v>118</v>
       </c>
       <c r="E59" s="1">
         <f t="shared" si="0"/>
@@ -3108,19 +3186,19 @@
         <v>5</v>
       </c>
       <c r="G59" s="8" t="s">
-        <v>22</v>
+        <v>94</v>
       </c>
       <c r="H59" s="8" t="s">
-        <v>28</v>
+        <v>116</v>
       </c>
       <c r="I59" s="1">
-        <v>11</v>
+        <v>84</v>
       </c>
       <c r="J59" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K59" s="1" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
     </row>
     <row r="60" customHeight="1" spans="3:11">
@@ -3128,7 +3206,7 @@
         <v>55</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>99</v>
+        <v>119</v>
       </c>
       <c r="E60" s="1">
         <f t="shared" si="0"/>
@@ -3138,16 +3216,16 @@
         <v>5</v>
       </c>
       <c r="G60" s="8" t="s">
-        <v>14</v>
+        <v>87</v>
       </c>
       <c r="H60" s="8" t="s">
-        <v>15</v>
+        <v>120</v>
       </c>
       <c r="I60" s="1">
         <v>1</v>
       </c>
       <c r="J60" s="1">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K60" s="1" t="s">
         <v>16</v>
@@ -3158,7 +3236,7 @@
         <v>56</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>100</v>
+        <v>121</v>
       </c>
       <c r="E61" s="1">
         <f t="shared" si="0"/>
@@ -3168,16 +3246,16 @@
         <v>5</v>
       </c>
       <c r="G61" s="8" t="s">
-        <v>18</v>
+        <v>91</v>
       </c>
       <c r="H61" s="8" t="s">
-        <v>19</v>
+        <v>120</v>
       </c>
       <c r="I61" s="1">
         <v>2</v>
       </c>
       <c r="J61" s="1">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K61" s="1" t="s">
         <v>20</v>
@@ -3188,7 +3266,7 @@
         <v>57</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="E62" s="1">
         <f t="shared" si="0"/>
@@ -3198,16 +3276,16 @@
         <v>5</v>
       </c>
       <c r="G62" s="8" t="s">
-        <v>22</v>
+        <v>94</v>
       </c>
       <c r="H62" s="8" t="s">
-        <v>19</v>
+        <v>120</v>
       </c>
       <c r="I62" s="1">
         <v>3</v>
       </c>
       <c r="J62" s="1">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K62" s="1" t="s">
         <v>23</v>
@@ -3218,7 +3296,7 @@
         <v>58</v>
       </c>
       <c r="D63" s="5" t="s">
-        <v>101</v>
+        <v>122</v>
       </c>
       <c r="E63" s="1">
         <f t="shared" si="0"/>
@@ -3228,16 +3306,16 @@
         <v>5</v>
       </c>
       <c r="G63" s="8" t="s">
-        <v>14</v>
+        <v>87</v>
       </c>
       <c r="H63" s="8" t="s">
-        <v>25</v>
+        <v>123</v>
       </c>
       <c r="I63" s="1">
         <v>4</v>
       </c>
       <c r="J63" s="1">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K63" s="1" t="s">
         <v>26</v>
@@ -3248,7 +3326,7 @@
         <v>59</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>102</v>
+        <v>124</v>
       </c>
       <c r="E64" s="1">
         <f t="shared" si="0"/>
@@ -3258,16 +3336,16 @@
         <v>5</v>
       </c>
       <c r="G64" s="8" t="s">
-        <v>18</v>
+        <v>91</v>
       </c>
       <c r="H64" s="8" t="s">
-        <v>28</v>
+        <v>123</v>
       </c>
       <c r="I64" s="1">
         <v>5</v>
       </c>
       <c r="J64" s="1">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K64" s="1" t="s">
         <v>29</v>
@@ -3278,7 +3356,7 @@
         <v>60</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="E65" s="1">
         <f t="shared" si="0"/>
@@ -3288,16 +3366,16 @@
         <v>5</v>
       </c>
       <c r="G65" s="8" t="s">
-        <v>22</v>
+        <v>94</v>
       </c>
       <c r="H65" s="8" t="s">
-        <v>28</v>
+        <v>123</v>
       </c>
       <c r="I65" s="1">
         <v>6</v>
       </c>
       <c r="J65" s="1">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K65" s="1" t="s">
         <v>31</v>
@@ -3308,7 +3386,7 @@
         <v>61</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>104</v>
+        <v>126</v>
       </c>
       <c r="E66" s="1">
         <f t="shared" si="0"/>
@@ -3318,19 +3396,19 @@
         <v>5</v>
       </c>
       <c r="G66" s="8" t="s">
-        <v>14</v>
+        <v>87</v>
       </c>
       <c r="H66" s="8" t="s">
-        <v>15</v>
+        <v>127</v>
       </c>
       <c r="I66" s="1">
-        <v>81</v>
+        <v>13</v>
       </c>
       <c r="J66" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K66" s="1" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
     </row>
     <row r="67" customHeight="1" spans="3:11">
@@ -3338,7 +3416,7 @@
         <v>62</v>
       </c>
       <c r="D67" s="6" t="s">
-        <v>105</v>
+        <v>128</v>
       </c>
       <c r="E67" s="1">
         <f t="shared" si="0"/>
@@ -3348,19 +3426,19 @@
         <v>5</v>
       </c>
       <c r="G67" s="8" t="s">
-        <v>18</v>
+        <v>91</v>
       </c>
       <c r="H67" s="8" t="s">
-        <v>19</v>
+        <v>127</v>
       </c>
       <c r="I67" s="1">
-        <v>82</v>
+        <v>14</v>
       </c>
       <c r="J67" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K67" s="1" t="s">
-        <v>37</v>
+        <v>73</v>
       </c>
     </row>
     <row r="68" customHeight="1" spans="3:11">
@@ -3368,7 +3446,7 @@
         <v>63</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>106</v>
+        <v>129</v>
       </c>
       <c r="E68" s="1">
         <f t="shared" si="0"/>
@@ -3378,19 +3456,19 @@
         <v>5</v>
       </c>
       <c r="G68" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="H68" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="I68" s="1">
         <v>22</v>
       </c>
-      <c r="H68" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="I68" s="1">
-        <v>83</v>
-      </c>
       <c r="J68" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K68" s="1" t="s">
-        <v>39</v>
+        <v>75</v>
       </c>
     </row>
     <row r="69" customHeight="1" spans="3:11">
@@ -3398,7 +3476,7 @@
         <v>64</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>107</v>
+        <v>130</v>
       </c>
       <c r="E69" s="1">
         <f t="shared" si="0"/>
@@ -3408,19 +3486,19 @@
         <v>5</v>
       </c>
       <c r="G69" s="8" t="s">
-        <v>14</v>
+        <v>87</v>
       </c>
       <c r="H69" s="8" t="s">
-        <v>25</v>
+        <v>131</v>
       </c>
       <c r="I69" s="1">
-        <v>84</v>
+        <v>1</v>
       </c>
       <c r="J69" s="1">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="K69" s="1" t="s">
-        <v>42</v>
+        <v>16</v>
       </c>
     </row>
     <row r="70" customHeight="1" spans="3:11">
@@ -3428,7 +3506,7 @@
         <v>65</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>108</v>
+        <v>132</v>
       </c>
       <c r="E70" s="1">
         <f t="shared" ref="E70:E77" si="1">INT((C70-1)/6)+1101</f>
@@ -3438,19 +3516,19 @@
         <v>5</v>
       </c>
       <c r="G70" s="8" t="s">
-        <v>18</v>
+        <v>91</v>
       </c>
       <c r="H70" s="8" t="s">
-        <v>28</v>
+        <v>131</v>
       </c>
       <c r="I70" s="1">
-        <v>85</v>
+        <v>2</v>
       </c>
       <c r="J70" s="1">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="K70" s="1" t="s">
-        <v>45</v>
+        <v>20</v>
       </c>
     </row>
     <row r="71" customHeight="1" spans="3:11">
@@ -3458,7 +3536,7 @@
         <v>66</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>109</v>
+        <v>133</v>
       </c>
       <c r="E71" s="1">
         <f t="shared" si="1"/>
@@ -3468,19 +3546,19 @@
         <v>5</v>
       </c>
       <c r="G71" s="8" t="s">
-        <v>22</v>
+        <v>94</v>
       </c>
       <c r="H71" s="8" t="s">
-        <v>28</v>
+        <v>131</v>
       </c>
       <c r="I71" s="1">
-        <v>86</v>
+        <v>3</v>
       </c>
       <c r="J71" s="1">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="K71" s="1" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
     </row>
     <row r="72" customHeight="1" spans="3:11">
@@ -3488,7 +3566,7 @@
         <v>67</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>107</v>
+        <v>130</v>
       </c>
       <c r="E72" s="1">
         <f t="shared" si="1"/>
@@ -3498,19 +3576,19 @@
         <v>5</v>
       </c>
       <c r="G72" s="8" t="s">
-        <v>14</v>
+        <v>87</v>
       </c>
       <c r="H72" s="8" t="s">
-        <v>15</v>
+        <v>134</v>
       </c>
       <c r="I72" s="1">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="J72" s="1">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="K72" s="1" t="s">
-        <v>50</v>
+        <v>26</v>
       </c>
     </row>
     <row r="73" customHeight="1" spans="3:11">
@@ -3518,7 +3596,7 @@
         <v>68</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>110</v>
+        <v>135</v>
       </c>
       <c r="E73" s="1">
         <f t="shared" si="1"/>
@@ -3528,19 +3606,19 @@
         <v>5</v>
       </c>
       <c r="G73" s="8" t="s">
-        <v>18</v>
+        <v>91</v>
       </c>
       <c r="H73" s="8" t="s">
-        <v>19</v>
+        <v>134</v>
       </c>
       <c r="I73" s="1">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="J73" s="1">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="K73" s="1" t="s">
-        <v>53</v>
+        <v>29</v>
       </c>
     </row>
     <row r="74" customHeight="1" spans="3:11">
@@ -3548,7 +3626,7 @@
         <v>69</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>111</v>
+        <v>136</v>
       </c>
       <c r="E74" s="1">
         <f t="shared" si="1"/>
@@ -3558,19 +3636,19 @@
         <v>5</v>
       </c>
       <c r="G74" s="8" t="s">
-        <v>22</v>
+        <v>94</v>
       </c>
       <c r="H74" s="8" t="s">
-        <v>19</v>
+        <v>134</v>
       </c>
       <c r="I74" s="1">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="J74" s="1">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="K74" s="1" t="s">
-        <v>55</v>
+        <v>31</v>
       </c>
     </row>
     <row r="75" customHeight="1" spans="3:11">
@@ -3578,7 +3656,7 @@
         <v>70</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>112</v>
+        <v>137</v>
       </c>
       <c r="E75" s="1">
         <f t="shared" si="1"/>
@@ -3588,19 +3666,19 @@
         <v>5</v>
       </c>
       <c r="G75" s="8" t="s">
-        <v>14</v>
+        <v>87</v>
       </c>
       <c r="H75" s="8" t="s">
-        <v>25</v>
+        <v>138</v>
       </c>
       <c r="I75" s="1">
         <v>12</v>
       </c>
       <c r="J75" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K75" s="1" t="s">
-        <v>58</v>
+        <v>89</v>
       </c>
     </row>
     <row r="76" customHeight="1" spans="3:11">
@@ -3608,7 +3686,7 @@
         <v>71</v>
       </c>
       <c r="D76" s="5" t="s">
-        <v>113</v>
+        <v>139</v>
       </c>
       <c r="E76" s="1">
         <f t="shared" si="1"/>
@@ -3618,19 +3696,19 @@
         <v>5</v>
       </c>
       <c r="G76" s="8" t="s">
-        <v>18</v>
+        <v>91</v>
       </c>
       <c r="H76" s="8" t="s">
-        <v>28</v>
+        <v>138</v>
       </c>
       <c r="I76" s="1">
         <v>10</v>
       </c>
       <c r="J76" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K76" s="1" t="s">
-        <v>61</v>
+        <v>92</v>
       </c>
     </row>
     <row r="77" customHeight="1" spans="3:11">
@@ -3638,7 +3716,7 @@
         <v>72</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>114</v>
+        <v>140</v>
       </c>
       <c r="E77" s="1">
         <f t="shared" si="1"/>
@@ -3648,19 +3726,19 @@
         <v>5</v>
       </c>
       <c r="G77" s="8" t="s">
-        <v>22</v>
+        <v>94</v>
       </c>
       <c r="H77" s="8" t="s">
-        <v>28</v>
+        <v>138</v>
       </c>
       <c r="I77" s="1">
         <v>11</v>
       </c>
       <c r="J77" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K77" s="1" t="s">
-        <v>63</v>
+        <v>95</v>
       </c>
     </row>
     <row r="106" customHeight="1" spans="5:8">

--- a/Excel/PetConfig.xlsx
+++ b/Excel/PetConfig.xlsx
@@ -296,7 +296,7 @@
     <t>60000,50</t>
   </si>
   <si>
-    <t>法师宝宝</t>
+    <t>骨法宝宝</t>
   </si>
   <si>
     <t>6000,50</t>

--- a/Excel/PetConfig.xlsx
+++ b/Excel/PetConfig.xlsx
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="97">
   <si>
     <t>#</t>
   </si>
@@ -71,16 +71,10 @@
     <t>Name</t>
   </si>
   <si>
-    <t>CardGroupId</t>
-  </si>
-  <si>
     <t>CardQuality</t>
   </si>
   <si>
-    <t>CardAtrList</t>
-  </si>
-  <si>
-    <t>CardVueList</t>
+    <t>CardId</t>
   </si>
   <si>
     <t>TraitId</t>
@@ -98,57 +92,33 @@
     <t>string</t>
   </si>
   <si>
-    <t>int[]</t>
-  </si>
-  <si>
     <t>狼宝宝</t>
   </si>
   <si>
-    <t>1,1001</t>
-  </si>
-  <si>
-    <t>1000,5</t>
-  </si>
-  <si>
     <t>基础生命</t>
   </si>
   <si>
     <t>骷髅宝宝</t>
   </si>
   <si>
-    <t>2,1002</t>
-  </si>
-  <si>
-    <t>100,5</t>
-  </si>
-  <si>
     <t>基础防御</t>
   </si>
   <si>
     <t>兽人宝宝</t>
   </si>
   <si>
-    <t>3,1003</t>
-  </si>
-  <si>
     <t>基础攻击</t>
   </si>
   <si>
     <t>蜘蛛宝宝</t>
   </si>
   <si>
-    <t>2000,10</t>
-  </si>
-  <si>
     <t>基础物攻</t>
   </si>
   <si>
     <t>岩蝎宝宝</t>
   </si>
   <si>
-    <t>200,10</t>
-  </si>
-  <si>
     <t>基础魔法</t>
   </si>
   <si>
@@ -161,18 +131,12 @@
     <t>毒蛆宝宝</t>
   </si>
   <si>
-    <t>4000,15</t>
-  </si>
-  <si>
     <t>杀敌经验</t>
   </si>
   <si>
     <t>蜈蚣宝宝</t>
   </si>
   <si>
-    <t>400,15</t>
-  </si>
-  <si>
     <t>经验加成</t>
   </si>
   <si>
@@ -185,48 +149,30 @@
     <t>蛛王宝宝</t>
   </si>
   <si>
-    <t>7000,20</t>
-  </si>
-  <si>
     <t>蛇宝宝</t>
   </si>
   <si>
-    <t>700,20</t>
-  </si>
-  <si>
     <t>巨鳄宝宝</t>
   </si>
   <si>
     <t>乌鸦宝宝</t>
   </si>
   <si>
-    <t>10000,25</t>
-  </si>
-  <si>
     <t>行尸宝宝</t>
   </si>
   <si>
-    <t>1000,25</t>
-  </si>
-  <si>
     <t>尸鬼宝宝</t>
   </si>
   <si>
     <t>蝙蝠宝宝</t>
   </si>
   <si>
-    <t>20000,30</t>
-  </si>
-  <si>
     <t>杀敌金币</t>
   </si>
   <si>
     <t>尸魔宝宝</t>
   </si>
   <si>
-    <t>2000,30</t>
-  </si>
-  <si>
     <t>金币加成</t>
   </si>
   <si>
@@ -239,48 +185,30 @@
     <t>花妖宝宝</t>
   </si>
   <si>
-    <t>30000,35</t>
-  </si>
-  <si>
     <t>树精宝宝</t>
   </si>
   <si>
-    <t>3000,35</t>
-  </si>
-  <si>
     <t>鱼人宝宝</t>
   </si>
   <si>
     <t>狼人宝宝</t>
   </si>
   <si>
-    <t>40000,40</t>
-  </si>
-  <si>
     <t>蠕虫宝宝</t>
   </si>
   <si>
-    <t>4000,40</t>
-  </si>
-  <si>
     <t>角鹿宝宝</t>
   </si>
   <si>
     <t>恶犬宝宝</t>
   </si>
   <si>
-    <t>50000,45</t>
-  </si>
-  <si>
     <t>命中</t>
   </si>
   <si>
     <t>守卫宝宝</t>
   </si>
   <si>
-    <t>5000,45</t>
-  </si>
-  <si>
     <t>闪避</t>
   </si>
   <si>
@@ -293,69 +221,42 @@
     <t>幽灵宝宝</t>
   </si>
   <si>
-    <t>60000,50</t>
-  </si>
-  <si>
     <t>骨法宝宝</t>
   </si>
   <si>
-    <t>6000,50</t>
-  </si>
-  <si>
     <t>骸骨宝宝</t>
   </si>
   <si>
     <t>战猪宝宝</t>
   </si>
   <si>
-    <t>70000,55</t>
-  </si>
-  <si>
     <t>勇猪宝宝</t>
   </si>
   <si>
-    <t>7000,55</t>
-  </si>
-  <si>
     <t>力猪宝宝</t>
   </si>
   <si>
     <t>萨满宝宝</t>
   </si>
   <si>
-    <t>1001,2001</t>
-  </si>
-  <si>
-    <t>60,5</t>
-  </si>
-  <si>
     <t>移动速度</t>
   </si>
   <si>
     <t>战将宝宝</t>
   </si>
   <si>
-    <t>1002,2002</t>
-  </si>
-  <si>
     <t>技能冷却</t>
   </si>
   <si>
     <t>亲卫宝宝</t>
   </si>
   <si>
-    <t>1003,2003</t>
-  </si>
-  <si>
     <t>攻速</t>
   </si>
   <si>
     <t>花宝宝</t>
   </si>
   <si>
-    <t>70,10</t>
-  </si>
-  <si>
     <t>甲虫宝宝</t>
   </si>
   <si>
@@ -365,9 +266,6 @@
     <t>赤炎宝宝</t>
   </si>
   <si>
-    <t>80,15</t>
-  </si>
-  <si>
     <t>魔姬宝宝</t>
   </si>
   <si>
@@ -377,9 +275,6 @@
     <t>冰蝎宝宝</t>
   </si>
   <si>
-    <t>90,20</t>
-  </si>
-  <si>
     <t>寒冰宝宝</t>
   </si>
   <si>
@@ -389,18 +284,12 @@
     <t>霜骑宝宝</t>
   </si>
   <si>
-    <t>100,25</t>
-  </si>
-  <si>
     <t>巨霜宝宝</t>
   </si>
   <si>
     <t>鬼蛛宝宝</t>
   </si>
   <si>
-    <t>110,30</t>
-  </si>
-  <si>
     <t>蛇姬宝宝</t>
   </si>
   <si>
@@ -410,9 +299,6 @@
     <t>暗夜宝宝</t>
   </si>
   <si>
-    <t>120,35</t>
-  </si>
-  <si>
     <t>祭司宝宝</t>
   </si>
   <si>
@@ -422,18 +308,12 @@
     <t>人马宝宝</t>
   </si>
   <si>
-    <t>130,40</t>
-  </si>
-  <si>
     <t>巨熊宝宝</t>
   </si>
   <si>
     <t>屠戮宝宝</t>
   </si>
   <si>
-    <t>140,45</t>
-  </si>
-  <si>
     <t>牛头宝宝</t>
   </si>
   <si>
@@ -443,9 +323,6 @@
     <t>魔瞳宝宝</t>
   </si>
   <si>
-    <t>150,50</t>
-  </si>
-  <si>
     <t>收割宝宝</t>
   </si>
   <si>
@@ -455,18 +332,12 @@
     <t>恶魔宝宝</t>
   </si>
   <si>
-    <t>160,55</t>
-  </si>
-  <si>
     <t>黑骑宝宝</t>
   </si>
   <si>
     <t>巫师宝宝</t>
   </si>
   <si>
-    <t>170,60</t>
-  </si>
-  <si>
     <t>三头宝宝</t>
   </si>
   <si>
@@ -474,9 +345,6 @@
   </si>
   <si>
     <t>魇兽宝宝</t>
-  </si>
-  <si>
-    <t>175,65</t>
   </si>
   <si>
     <t>大魔宝宝</t>
@@ -1150,7 +1018,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1470,31 +1337,29 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:K107"/>
+  <dimension ref="C1:I107"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="1"/>
-    <col min="4" max="4" width="12.8333333333333" style="1" customWidth="1"/>
-    <col min="5" max="6" width="13" style="1" customWidth="1"/>
-    <col min="7" max="7" width="14.1666666666667" style="1" customWidth="1"/>
-    <col min="8" max="8" width="16.25" style="1" customWidth="1"/>
-    <col min="9" max="9" width="14.8333333333333" style="1" customWidth="1"/>
-    <col min="10" max="10" width="13" style="1" customWidth="1"/>
-    <col min="11" max="11" width="17" style="1" customWidth="1"/>
-    <col min="12" max="16384" width="9" style="1"/>
+    <col min="4" max="5" width="12.8333333333333" style="1" customWidth="1"/>
+    <col min="6" max="6" width="13" style="1" customWidth="1"/>
+    <col min="7" max="7" width="14.8333333333333" style="1" customWidth="1"/>
+    <col min="8" max="8" width="13" style="1" customWidth="1"/>
+    <col min="9" max="9" width="17" style="1" customWidth="1"/>
+    <col min="10" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" customHeight="1" spans="3:11">
-      <c r="K1" s="1" t="s">
+    <row r="1" customHeight="1" spans="3:9">
+      <c r="I1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" customHeight="1" spans="3:11">
-      <c r="K2" s="1" t="s">
+    <row r="2" customHeight="1" spans="3:9">
+      <c r="I2" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:11">
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:9">
       <c r="C3" s="2" t="s">
         <v>1</v>
       </c>
@@ -1514,18 +1379,12 @@
         <v>6</v>
       </c>
       <c r="I3" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:9">
+      <c r="C4" s="2" t="s">
         <v>7</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:11">
-      <c r="C4" s="2" t="s">
-        <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>2</v>
@@ -1543,2223 +1402,1773 @@
         <v>6</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="J4" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:9">
+      <c r="C5" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="K4" s="2" t="s">
+      <c r="D5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I5" s="2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:11">
-      <c r="C5" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="K5" s="2" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" s="1" customFormat="1" customHeight="1" spans="3:11">
+    <row r="6" s="1" customFormat="1" customHeight="1" spans="3:9">
       <c r="C6" s="1">
         <v>1</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E6" s="1">
-        <f t="shared" ref="E6:E69" si="0">INT((C6-1)/6)+1101</f>
+        <v>10</v>
+      </c>
+      <c r="E6" s="3">
+        <v>5</v>
+      </c>
+      <c r="F6" s="1">
+        <f t="shared" ref="F6:F69" si="0">INT((C6-1)/6)+1101</f>
         <v>1101</v>
       </c>
-      <c r="F6" s="1">
-        <v>5</v>
-      </c>
-      <c r="G6" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H6" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I6" s="1">
+      <c r="G6" s="1">
         <v>1</v>
       </c>
-      <c r="J6" s="1">
+      <c r="H6" s="1">
         <v>1</v>
       </c>
-      <c r="K6" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="7" s="1" customFormat="1" customHeight="1" spans="3:11">
+      <c r="I6" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" customHeight="1" spans="3:9">
       <c r="C7" s="1">
         <v>2</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E7" s="1">
+        <v>12</v>
+      </c>
+      <c r="E7" s="3">
+        <v>5</v>
+      </c>
+      <c r="F7" s="1">
         <f t="shared" si="0"/>
         <v>1101</v>
       </c>
-      <c r="F7" s="1">
-        <v>5</v>
-      </c>
-      <c r="G7" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="H7" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="I7" s="1">
+      <c r="G7" s="1">
         <v>2</v>
       </c>
-      <c r="J7" s="1">
+      <c r="H7" s="1">
         <v>1</v>
       </c>
-      <c r="K7" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:11">
+      <c r="I7" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:9">
       <c r="C8" s="1">
         <v>3</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="E8" s="1">
+        <v>14</v>
+      </c>
+      <c r="E8" s="3">
+        <v>5</v>
+      </c>
+      <c r="F8" s="1">
         <f t="shared" si="0"/>
         <v>1101</v>
       </c>
-      <c r="F8" s="1">
-        <v>5</v>
-      </c>
-      <c r="G8" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="H8" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="I8" s="1">
+      <c r="G8" s="1">
         <v>3</v>
       </c>
-      <c r="J8" s="1">
+      <c r="H8" s="1">
         <v>1</v>
       </c>
-      <c r="K8" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="9" s="1" customFormat="1" customHeight="1" spans="3:11">
+      <c r="I8" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" s="1" customFormat="1" customHeight="1" spans="3:9">
       <c r="C9" s="1">
         <v>4</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="E9" s="1">
+        <v>16</v>
+      </c>
+      <c r="E9" s="3">
+        <v>5</v>
+      </c>
+      <c r="F9" s="1">
         <f t="shared" si="0"/>
         <v>1101</v>
       </c>
-      <c r="F9" s="1">
-        <v>5</v>
-      </c>
-      <c r="G9" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H9" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="I9" s="1">
+      <c r="G9" s="1">
         <v>4</v>
       </c>
-      <c r="J9" s="1">
+      <c r="H9" s="1">
         <v>1</v>
       </c>
-      <c r="K9" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="10" s="1" customFormat="1" customHeight="1" spans="3:11">
+      <c r="I9" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" s="1" customFormat="1" customHeight="1" spans="3:9">
       <c r="C10" s="1">
         <v>5</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E10" s="1">
+        <v>18</v>
+      </c>
+      <c r="E10" s="3">
+        <v>5</v>
+      </c>
+      <c r="F10" s="1">
         <f t="shared" si="0"/>
         <v>1101</v>
       </c>
-      <c r="F10" s="1">
-        <v>5</v>
-      </c>
-      <c r="G10" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="H10" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="I10" s="1">
-        <v>5</v>
-      </c>
-      <c r="J10" s="1">
+      <c r="G10" s="1">
+        <v>5</v>
+      </c>
+      <c r="H10" s="1">
         <v>1</v>
       </c>
-      <c r="K10" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:11">
+      <c r="I10" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:9">
       <c r="C11" s="1">
         <v>6</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="E11" s="1">
+        <v>20</v>
+      </c>
+      <c r="E11" s="3">
+        <v>5</v>
+      </c>
+      <c r="F11" s="1">
         <f t="shared" si="0"/>
         <v>1101</v>
       </c>
-      <c r="F11" s="1">
-        <v>5</v>
-      </c>
-      <c r="G11" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="H11" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="I11" s="1">
+      <c r="G11" s="1">
         <v>6</v>
       </c>
-      <c r="J11" s="1">
+      <c r="H11" s="1">
         <v>1</v>
       </c>
-      <c r="K11" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="12" s="1" customFormat="1" customHeight="1" spans="3:11">
+      <c r="I11" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12" s="1" customFormat="1" customHeight="1" spans="3:9">
       <c r="C12" s="1">
         <v>7</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="E12" s="1">
+        <v>22</v>
+      </c>
+      <c r="E12" s="3">
+        <v>5</v>
+      </c>
+      <c r="F12" s="1">
         <f t="shared" si="0"/>
         <v>1102</v>
       </c>
-      <c r="F12" s="1">
-        <v>5</v>
-      </c>
-      <c r="G12" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H12" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="I12" s="1">
+      <c r="G12" s="1">
         <v>86</v>
       </c>
-      <c r="J12" s="1">
+      <c r="H12" s="1">
         <v>1</v>
       </c>
-      <c r="K12" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="13" s="1" customFormat="1" customHeight="1" spans="3:11">
+      <c r="I12" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="13" s="1" customFormat="1" customHeight="1" spans="3:9">
       <c r="C13" s="1">
         <v>8</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="E13" s="1">
+        <v>24</v>
+      </c>
+      <c r="E13" s="3">
+        <v>5</v>
+      </c>
+      <c r="F13" s="1">
         <f t="shared" si="0"/>
         <v>1102</v>
       </c>
-      <c r="F13" s="1">
-        <v>5</v>
-      </c>
-      <c r="G13" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="H13" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="I13" s="1">
+      <c r="G13" s="1">
         <v>82</v>
       </c>
-      <c r="J13" s="1">
+      <c r="H13" s="1">
         <v>1</v>
       </c>
-      <c r="K13" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="14" customHeight="1" spans="3:11">
+      <c r="I13" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="14" customHeight="1" spans="3:9">
       <c r="C14" s="1">
         <v>9</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="E14" s="1">
+        <v>26</v>
+      </c>
+      <c r="E14" s="3">
+        <v>5</v>
+      </c>
+      <c r="F14" s="1">
         <f t="shared" si="0"/>
         <v>1102</v>
       </c>
-      <c r="F14" s="1">
-        <v>5</v>
-      </c>
-      <c r="G14" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="H14" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="I14" s="1">
+      <c r="G14" s="1">
         <v>83</v>
       </c>
-      <c r="J14" s="1">
+      <c r="H14" s="1">
         <v>1</v>
       </c>
-      <c r="K14" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="15" s="1" customFormat="1" customHeight="1" spans="3:11">
+      <c r="I14" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="15" s="1" customFormat="1" customHeight="1" spans="3:9">
       <c r="C15" s="1">
         <v>10</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="E15" s="1">
+        <v>28</v>
+      </c>
+      <c r="E15" s="3">
+        <v>5</v>
+      </c>
+      <c r="F15" s="1">
         <f t="shared" si="0"/>
         <v>1102</v>
       </c>
-      <c r="F15" s="1">
-        <v>5</v>
-      </c>
-      <c r="G15" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H15" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="I15" s="1">
+      <c r="G15" s="1">
         <v>1</v>
       </c>
-      <c r="J15" s="1">
+      <c r="H15" s="1">
         <v>2</v>
       </c>
-      <c r="K15" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="16" s="1" customFormat="1" customHeight="1" spans="3:11">
+      <c r="I15" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16" s="1" customFormat="1" customHeight="1" spans="3:9">
       <c r="C16" s="1">
         <v>11</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="E16" s="1">
+        <v>29</v>
+      </c>
+      <c r="E16" s="3">
+        <v>5</v>
+      </c>
+      <c r="F16" s="1">
         <f t="shared" si="0"/>
         <v>1102</v>
       </c>
-      <c r="F16" s="1">
-        <v>5</v>
-      </c>
-      <c r="G16" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="H16" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="I16" s="1">
+      <c r="G16" s="1">
         <v>2</v>
       </c>
-      <c r="J16" s="1">
+      <c r="H16" s="1">
         <v>2</v>
       </c>
-      <c r="K16" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="17" s="1" customFormat="1" customHeight="1" spans="3:11">
+      <c r="I16" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="17" s="1" customFormat="1" customHeight="1" spans="3:9">
       <c r="C17" s="1">
         <v>12</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="E17" s="1">
+        <v>30</v>
+      </c>
+      <c r="E17" s="3">
+        <v>5</v>
+      </c>
+      <c r="F17" s="1">
         <f t="shared" si="0"/>
         <v>1102</v>
       </c>
-      <c r="F17" s="1">
-        <v>5</v>
-      </c>
-      <c r="G17" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="H17" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="I17" s="1">
+      <c r="G17" s="1">
         <v>3</v>
       </c>
-      <c r="J17" s="1">
+      <c r="H17" s="1">
         <v>2</v>
       </c>
-      <c r="K17" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="18" s="1" customFormat="1" customHeight="1" spans="3:11">
+      <c r="I17" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18" s="1" customFormat="1" customHeight="1" spans="3:9">
       <c r="C18" s="1">
         <v>13</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="E18" s="1">
+        <v>31</v>
+      </c>
+      <c r="E18" s="3">
+        <v>5</v>
+      </c>
+      <c r="F18" s="1">
         <f t="shared" si="0"/>
         <v>1103</v>
       </c>
-      <c r="F18" s="1">
-        <v>5</v>
-      </c>
-      <c r="G18" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H18" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="I18" s="1">
+      <c r="G18" s="1">
         <v>4</v>
       </c>
-      <c r="J18" s="1">
+      <c r="H18" s="1">
         <v>2</v>
       </c>
-      <c r="K18" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="19" s="1" customFormat="1" customHeight="1" spans="3:11">
+      <c r="I18" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" s="1" customFormat="1" customHeight="1" spans="3:9">
       <c r="C19" s="1">
         <v>14</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="E19" s="1">
+        <v>32</v>
+      </c>
+      <c r="E19" s="3">
+        <v>5</v>
+      </c>
+      <c r="F19" s="1">
         <f t="shared" si="0"/>
         <v>1103</v>
       </c>
-      <c r="F19" s="1">
-        <v>5</v>
-      </c>
-      <c r="G19" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="H19" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="I19" s="1">
-        <v>5</v>
-      </c>
-      <c r="J19" s="1">
+      <c r="G19" s="1">
+        <v>5</v>
+      </c>
+      <c r="H19" s="1">
         <v>2</v>
       </c>
-      <c r="K19" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="20" s="1" customFormat="1" customHeight="1" spans="3:11">
+      <c r="I19" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="20" s="1" customFormat="1" customHeight="1" spans="3:9">
       <c r="C20" s="1">
         <v>15</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="E20" s="1">
+        <v>33</v>
+      </c>
+      <c r="E20" s="3">
+        <v>5</v>
+      </c>
+      <c r="F20" s="1">
         <f t="shared" si="0"/>
         <v>1103</v>
       </c>
-      <c r="F20" s="1">
-        <v>5</v>
-      </c>
-      <c r="G20" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="H20" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="I20" s="1">
+      <c r="G20" s="1">
         <v>6</v>
       </c>
-      <c r="J20" s="1">
+      <c r="H20" s="1">
         <v>2</v>
       </c>
-      <c r="K20" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="21" s="1" customFormat="1" customHeight="1" spans="3:11">
+      <c r="I20" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="21" s="1" customFormat="1" customHeight="1" spans="3:9">
       <c r="C21" s="1">
         <v>16</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="E21" s="1">
+        <v>34</v>
+      </c>
+      <c r="E21" s="3">
+        <v>5</v>
+      </c>
+      <c r="F21" s="1">
         <f t="shared" si="0"/>
         <v>1103</v>
       </c>
-      <c r="F21" s="1">
-        <v>5</v>
-      </c>
-      <c r="G21" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H21" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="I21" s="1">
+      <c r="G21" s="1">
         <v>85</v>
       </c>
-      <c r="J21" s="1">
+      <c r="H21" s="1">
         <v>1</v>
       </c>
-      <c r="K21" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="22" s="1" customFormat="1" customHeight="1" spans="3:11">
+      <c r="I21" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="22" s="1" customFormat="1" customHeight="1" spans="3:9">
       <c r="C22" s="1">
         <v>17</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="E22" s="1">
+        <v>36</v>
+      </c>
+      <c r="E22" s="3">
+        <v>5</v>
+      </c>
+      <c r="F22" s="1">
         <f t="shared" si="0"/>
         <v>1103</v>
       </c>
-      <c r="F22" s="1">
-        <v>5</v>
-      </c>
-      <c r="G22" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="H22" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="I22" s="1">
+      <c r="G22" s="1">
         <v>81</v>
       </c>
-      <c r="J22" s="1">
+      <c r="H22" s="1">
         <v>1</v>
       </c>
-      <c r="K22" s="1" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="23" s="1" customFormat="1" customHeight="1" spans="3:11">
+      <c r="I22" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="23" s="1" customFormat="1" customHeight="1" spans="3:9">
       <c r="C23" s="1">
         <v>18</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="E23" s="1">
+        <v>38</v>
+      </c>
+      <c r="E23" s="3">
+        <v>5</v>
+      </c>
+      <c r="F23" s="1">
         <f t="shared" si="0"/>
         <v>1103</v>
       </c>
-      <c r="F23" s="1">
-        <v>5</v>
-      </c>
-      <c r="G23" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="H23" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="I23" s="1">
+      <c r="G23" s="1">
         <v>84</v>
       </c>
-      <c r="J23" s="1">
+      <c r="H23" s="1">
         <v>1</v>
       </c>
-      <c r="K23" s="1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="24" s="1" customFormat="1" customHeight="1" spans="3:11">
+      <c r="I23" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="24" s="1" customFormat="1" customHeight="1" spans="3:9">
       <c r="C24" s="1">
         <v>19</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="E24" s="1">
+        <v>40</v>
+      </c>
+      <c r="E24" s="3">
+        <v>5</v>
+      </c>
+      <c r="F24" s="1">
         <f t="shared" si="0"/>
         <v>1104</v>
       </c>
-      <c r="F24" s="1">
-        <v>5</v>
-      </c>
-      <c r="G24" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H24" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="I24" s="1">
+      <c r="G24" s="1">
         <v>1</v>
       </c>
-      <c r="J24" s="1">
+      <c r="H24" s="1">
         <v>3</v>
       </c>
-      <c r="K24" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="25" s="1" customFormat="1" customHeight="1" spans="3:11">
+      <c r="I24" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="25" s="1" customFormat="1" customHeight="1" spans="3:9">
       <c r="C25" s="1">
         <v>20</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="E25" s="1">
+        <v>41</v>
+      </c>
+      <c r="E25" s="3">
+        <v>5</v>
+      </c>
+      <c r="F25" s="1">
         <f t="shared" si="0"/>
         <v>1104</v>
       </c>
-      <c r="F25" s="1">
-        <v>5</v>
-      </c>
-      <c r="G25" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="H25" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="I25" s="1">
+      <c r="G25" s="1">
         <v>2</v>
       </c>
-      <c r="J25" s="1">
+      <c r="H25" s="1">
         <v>3</v>
       </c>
-      <c r="K25" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="26" s="1" customFormat="1" customHeight="1" spans="3:11">
+      <c r="I25" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="26" s="1" customFormat="1" customHeight="1" spans="3:9">
       <c r="C26" s="1">
         <v>21</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="E26" s="1">
+        <v>42</v>
+      </c>
+      <c r="E26" s="3">
+        <v>5</v>
+      </c>
+      <c r="F26" s="1">
         <f t="shared" si="0"/>
         <v>1104</v>
       </c>
-      <c r="F26" s="1">
-        <v>5</v>
-      </c>
-      <c r="G26" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="H26" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="I26" s="1">
+      <c r="G26" s="1">
         <v>3</v>
       </c>
-      <c r="J26" s="1">
+      <c r="H26" s="1">
         <v>3</v>
       </c>
-      <c r="K26" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="27" customHeight="1" spans="3:11">
+      <c r="I26" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="27" customHeight="1" spans="3:9">
       <c r="C27" s="1">
         <v>22</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="E27" s="1">
+        <v>43</v>
+      </c>
+      <c r="E27" s="3">
+        <v>5</v>
+      </c>
+      <c r="F27" s="1">
         <f t="shared" si="0"/>
         <v>1104</v>
       </c>
-      <c r="F27" s="1">
-        <v>5</v>
-      </c>
-      <c r="G27" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H27" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="I27" s="1">
+      <c r="G27" s="1">
         <v>4</v>
       </c>
-      <c r="J27" s="1">
+      <c r="H27" s="1">
         <v>3</v>
       </c>
-      <c r="K27" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="28" customHeight="1" spans="3:11">
+      <c r="I27" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="28" customHeight="1" spans="3:9">
       <c r="C28" s="1">
         <v>23</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="E28" s="1">
+        <v>44</v>
+      </c>
+      <c r="E28" s="3">
+        <v>5</v>
+      </c>
+      <c r="F28" s="1">
         <f t="shared" si="0"/>
         <v>1104</v>
       </c>
-      <c r="F28" s="1">
-        <v>5</v>
-      </c>
-      <c r="G28" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="H28" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="I28" s="1">
-        <v>5</v>
-      </c>
-      <c r="J28" s="1">
+      <c r="G28" s="1">
+        <v>5</v>
+      </c>
+      <c r="H28" s="1">
         <v>3</v>
       </c>
-      <c r="K28" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="29" customHeight="1" spans="3:11">
+      <c r="I28" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="29" customHeight="1" spans="3:9">
       <c r="C29" s="1">
         <v>24</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="E29" s="1">
+        <v>45</v>
+      </c>
+      <c r="E29" s="3">
+        <v>5</v>
+      </c>
+      <c r="F29" s="1">
         <f t="shared" si="0"/>
         <v>1104</v>
       </c>
-      <c r="F29" s="1">
-        <v>5</v>
-      </c>
-      <c r="G29" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="H29" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="I29" s="1">
+      <c r="G29" s="1">
         <v>6</v>
       </c>
-      <c r="J29" s="1">
+      <c r="H29" s="1">
         <v>3</v>
       </c>
-      <c r="K29" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="30" customHeight="1" spans="3:11">
+      <c r="I29" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="30" customHeight="1" spans="3:9">
       <c r="C30" s="1">
         <v>25</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="E30" s="1">
+        <v>46</v>
+      </c>
+      <c r="E30" s="3">
+        <v>5</v>
+      </c>
+      <c r="F30" s="1">
         <f t="shared" si="0"/>
         <v>1105</v>
       </c>
-      <c r="F30" s="1">
-        <v>5</v>
-      </c>
-      <c r="G30" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H30" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="I30" s="1">
+      <c r="G30" s="1">
         <v>13</v>
       </c>
-      <c r="J30" s="1">
+      <c r="H30" s="1">
         <v>1</v>
       </c>
-      <c r="K30" s="1" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="31" customHeight="1" spans="3:11">
+      <c r="I30" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="31" customHeight="1" spans="3:9">
       <c r="C31" s="1">
         <v>26</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="E31" s="1">
+        <v>48</v>
+      </c>
+      <c r="E31" s="3">
+        <v>5</v>
+      </c>
+      <c r="F31" s="1">
         <f t="shared" si="0"/>
         <v>1105</v>
       </c>
-      <c r="F31" s="1">
-        <v>5</v>
-      </c>
-      <c r="G31" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="H31" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="I31" s="1">
+      <c r="G31" s="1">
         <v>14</v>
       </c>
-      <c r="J31" s="1">
+      <c r="H31" s="1">
         <v>1</v>
       </c>
-      <c r="K31" s="1" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="32" customHeight="1" spans="3:11">
+      <c r="I31" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="32" customHeight="1" spans="3:9">
       <c r="C32" s="1">
         <v>27</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="E32" s="1">
+        <v>50</v>
+      </c>
+      <c r="E32" s="3">
+        <v>5</v>
+      </c>
+      <c r="F32" s="1">
         <f t="shared" si="0"/>
         <v>1105</v>
       </c>
-      <c r="F32" s="1">
-        <v>5</v>
-      </c>
-      <c r="G32" s="8" t="s">
+      <c r="G32" s="1">
         <v>22</v>
       </c>
-      <c r="H32" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="I32" s="1">
-        <v>22</v>
-      </c>
-      <c r="J32" s="1">
+      <c r="H32" s="1">
         <v>1</v>
       </c>
-      <c r="K32" s="1" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="33" customHeight="1" spans="3:11">
+      <c r="I32" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="33" customHeight="1" spans="3:9">
       <c r="C33" s="1">
         <v>28</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="E33" s="1">
+        <v>52</v>
+      </c>
+      <c r="E33" s="3">
+        <v>5</v>
+      </c>
+      <c r="F33" s="1">
         <f t="shared" si="0"/>
         <v>1105</v>
       </c>
-      <c r="F33" s="1">
-        <v>5</v>
-      </c>
-      <c r="G33" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H33" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="I33" s="1">
+      <c r="G33" s="1">
         <v>1</v>
       </c>
-      <c r="J33" s="1">
+      <c r="H33" s="1">
         <v>4</v>
       </c>
-      <c r="K33" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="34" customHeight="1" spans="3:11">
+      <c r="I33" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="34" customHeight="1" spans="3:9">
       <c r="C34" s="1">
         <v>29</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="E34" s="1">
+        <v>53</v>
+      </c>
+      <c r="E34" s="3">
+        <v>5</v>
+      </c>
+      <c r="F34" s="1">
         <f t="shared" si="0"/>
         <v>1105</v>
       </c>
-      <c r="F34" s="1">
-        <v>5</v>
-      </c>
-      <c r="G34" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="H34" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="I34" s="1">
+      <c r="G34" s="1">
         <v>2</v>
       </c>
-      <c r="J34" s="1">
+      <c r="H34" s="1">
         <v>4</v>
       </c>
-      <c r="K34" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="35" customHeight="1" spans="3:11">
+      <c r="I34" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="35" customHeight="1" spans="3:9">
       <c r="C35" s="1">
         <v>30</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="E35" s="1">
+        <v>54</v>
+      </c>
+      <c r="E35" s="3">
+        <v>5</v>
+      </c>
+      <c r="F35" s="1">
         <f t="shared" si="0"/>
         <v>1105</v>
       </c>
-      <c r="F35" s="1">
-        <v>5</v>
-      </c>
-      <c r="G35" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="H35" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="I35" s="1">
+      <c r="G35" s="1">
         <v>3</v>
       </c>
-      <c r="J35" s="1">
+      <c r="H35" s="1">
         <v>4</v>
       </c>
-      <c r="K35" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="36" customHeight="1" spans="3:11">
+      <c r="I35" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="36" customHeight="1" spans="3:9">
       <c r="C36" s="1">
         <v>31</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="E36" s="1">
+        <v>55</v>
+      </c>
+      <c r="E36" s="3">
+        <v>5</v>
+      </c>
+      <c r="F36" s="1">
         <f t="shared" si="0"/>
         <v>1106</v>
       </c>
-      <c r="F36" s="1">
-        <v>5</v>
-      </c>
-      <c r="G36" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H36" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="I36" s="1">
+      <c r="G36" s="1">
         <v>4</v>
       </c>
-      <c r="J36" s="1">
+      <c r="H36" s="1">
         <v>4</v>
       </c>
-      <c r="K36" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="37" customHeight="1" spans="3:11">
+      <c r="I36" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="37" customHeight="1" spans="3:9">
       <c r="C37" s="1">
         <v>32</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="E37" s="1">
+        <v>56</v>
+      </c>
+      <c r="E37" s="3">
+        <v>5</v>
+      </c>
+      <c r="F37" s="1">
         <f t="shared" si="0"/>
         <v>1106</v>
       </c>
-      <c r="F37" s="1">
-        <v>5</v>
-      </c>
-      <c r="G37" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="H37" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="I37" s="1">
-        <v>5</v>
-      </c>
-      <c r="J37" s="1">
+      <c r="G37" s="1">
+        <v>5</v>
+      </c>
+      <c r="H37" s="1">
         <v>4</v>
       </c>
-      <c r="K37" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="38" customHeight="1" spans="3:11">
+      <c r="I37" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="38" customHeight="1" spans="3:9">
       <c r="C38" s="1">
         <v>33</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="E38" s="1">
+        <v>57</v>
+      </c>
+      <c r="E38" s="3">
+        <v>5</v>
+      </c>
+      <c r="F38" s="1">
         <f t="shared" si="0"/>
         <v>1106</v>
       </c>
-      <c r="F38" s="1">
-        <v>5</v>
-      </c>
-      <c r="G38" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="H38" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="I38" s="1">
+      <c r="G38" s="1">
         <v>6</v>
       </c>
-      <c r="J38" s="1">
+      <c r="H38" s="1">
         <v>4</v>
       </c>
-      <c r="K38" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="39" customHeight="1" spans="3:11">
+      <c r="I38" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="39" customHeight="1" spans="3:9">
       <c r="C39" s="1">
         <v>34</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="E39" s="1">
+        <v>58</v>
+      </c>
+      <c r="E39" s="3">
+        <v>5</v>
+      </c>
+      <c r="F39" s="1">
         <f t="shared" si="0"/>
         <v>1106</v>
       </c>
-      <c r="F39" s="1">
-        <v>5</v>
-      </c>
-      <c r="G39" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="H39" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="I39" s="1">
+      <c r="G39" s="1">
         <v>12</v>
       </c>
-      <c r="J39" s="1">
+      <c r="H39" s="1">
         <v>1</v>
       </c>
-      <c r="K39" s="1" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="40" customHeight="1" spans="3:11">
+      <c r="I39" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="40" customHeight="1" spans="3:9">
       <c r="C40" s="1">
         <v>35</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="E40" s="1">
+        <v>60</v>
+      </c>
+      <c r="E40" s="3">
+        <v>5</v>
+      </c>
+      <c r="F40" s="1">
         <f t="shared" si="0"/>
         <v>1106</v>
       </c>
-      <c r="F40" s="1">
-        <v>5</v>
-      </c>
-      <c r="G40" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="H40" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="I40" s="1">
+      <c r="G40" s="1">
         <v>10</v>
       </c>
-      <c r="J40" s="1">
+      <c r="H40" s="1">
         <v>1</v>
       </c>
-      <c r="K40" s="1" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="41" customHeight="1" spans="3:11">
+      <c r="I40" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="41" customHeight="1" spans="3:9">
       <c r="C41" s="1">
         <v>36</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="E41" s="1">
+        <v>62</v>
+      </c>
+      <c r="E41" s="3">
+        <v>5</v>
+      </c>
+      <c r="F41" s="1">
         <f t="shared" si="0"/>
         <v>1106</v>
       </c>
-      <c r="F41" s="1">
-        <v>5</v>
-      </c>
-      <c r="G41" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="H41" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="I41" s="1">
+      <c r="G41" s="1">
         <v>11</v>
       </c>
-      <c r="J41" s="1">
+      <c r="H41" s="1">
         <v>1</v>
       </c>
-      <c r="K41" s="1" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="42" customHeight="1" spans="3:11">
+      <c r="I41" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="42" customHeight="1" spans="3:9">
       <c r="C42" s="1">
         <v>37</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="E42" s="1">
+        <v>64</v>
+      </c>
+      <c r="E42" s="3">
+        <v>5</v>
+      </c>
+      <c r="F42" s="1">
         <f t="shared" si="0"/>
         <v>1107</v>
       </c>
-      <c r="F42" s="1">
-        <v>5</v>
-      </c>
-      <c r="G42" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="H42" s="8" t="s">
-        <v>97</v>
-      </c>
-      <c r="I42" s="1">
+      <c r="G42" s="1">
         <v>1</v>
       </c>
-      <c r="J42" s="1">
-        <v>5</v>
-      </c>
-      <c r="K42" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="43" customHeight="1" spans="3:11">
+      <c r="H42" s="1">
+        <v>5</v>
+      </c>
+      <c r="I42" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="43" customHeight="1" spans="3:9">
       <c r="C43" s="1">
         <v>38</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="E43" s="1">
+        <v>65</v>
+      </c>
+      <c r="E43" s="3">
+        <v>5</v>
+      </c>
+      <c r="F43" s="1">
         <f t="shared" si="0"/>
         <v>1107</v>
       </c>
-      <c r="F43" s="1">
-        <v>5</v>
-      </c>
-      <c r="G43" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="H43" s="8" t="s">
-        <v>97</v>
-      </c>
-      <c r="I43" s="1">
+      <c r="G43" s="1">
         <v>2</v>
       </c>
-      <c r="J43" s="1">
-        <v>5</v>
-      </c>
-      <c r="K43" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="44" customHeight="1" spans="3:11">
+      <c r="H43" s="1">
+        <v>5</v>
+      </c>
+      <c r="I43" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="44" customHeight="1" spans="3:9">
       <c r="C44" s="1">
         <v>39</v>
       </c>
       <c r="D44" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="E44" s="1">
+        <v>66</v>
+      </c>
+      <c r="E44" s="3">
+        <v>5</v>
+      </c>
+      <c r="F44" s="1">
         <f t="shared" si="0"/>
         <v>1107</v>
       </c>
-      <c r="F44" s="1">
-        <v>5</v>
-      </c>
-      <c r="G44" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="H44" s="8" t="s">
-        <v>97</v>
-      </c>
-      <c r="I44" s="1">
+      <c r="G44" s="1">
         <v>3</v>
       </c>
-      <c r="J44" s="1">
-        <v>5</v>
-      </c>
-      <c r="K44" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="45" customHeight="1" spans="3:11">
+      <c r="H44" s="1">
+        <v>5</v>
+      </c>
+      <c r="I44" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="45" customHeight="1" spans="3:9">
       <c r="C45" s="1">
         <v>40</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="E45" s="1">
+        <v>67</v>
+      </c>
+      <c r="E45" s="3">
+        <v>5</v>
+      </c>
+      <c r="F45" s="1">
         <f t="shared" si="0"/>
         <v>1107</v>
       </c>
-      <c r="F45" s="1">
-        <v>5</v>
-      </c>
-      <c r="G45" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="H45" s="8" t="s">
-        <v>101</v>
-      </c>
-      <c r="I45" s="1">
+      <c r="G45" s="1">
         <v>4</v>
       </c>
-      <c r="J45" s="1">
-        <v>5</v>
-      </c>
-      <c r="K45" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="46" customHeight="1" spans="3:11">
+      <c r="H45" s="1">
+        <v>5</v>
+      </c>
+      <c r="I45" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="46" customHeight="1" spans="3:9">
       <c r="C46" s="1">
         <v>41</v>
       </c>
       <c r="D46" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="E46" s="1">
+        <v>68</v>
+      </c>
+      <c r="E46" s="3">
+        <v>5</v>
+      </c>
+      <c r="F46" s="1">
         <f t="shared" si="0"/>
         <v>1107</v>
       </c>
-      <c r="F46" s="1">
-        <v>5</v>
-      </c>
-      <c r="G46" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="H46" s="8" t="s">
-        <v>101</v>
-      </c>
-      <c r="I46" s="1">
-        <v>5</v>
-      </c>
-      <c r="J46" s="1">
-        <v>5</v>
-      </c>
-      <c r="K46" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="47" customHeight="1" spans="3:11">
+      <c r="G46" s="1">
+        <v>5</v>
+      </c>
+      <c r="H46" s="1">
+        <v>5</v>
+      </c>
+      <c r="I46" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="47" customHeight="1" spans="3:9">
       <c r="C47" s="1">
         <v>42</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="E47" s="1">
+        <v>69</v>
+      </c>
+      <c r="E47" s="3">
+        <v>5</v>
+      </c>
+      <c r="F47" s="1">
         <f t="shared" si="0"/>
         <v>1107</v>
       </c>
-      <c r="F47" s="1">
-        <v>5</v>
-      </c>
-      <c r="G47" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="H47" s="8" t="s">
-        <v>101</v>
-      </c>
-      <c r="I47" s="1">
+      <c r="G47" s="1">
         <v>6</v>
       </c>
-      <c r="J47" s="1">
-        <v>5</v>
-      </c>
-      <c r="K47" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="48" customHeight="1" spans="3:11">
+      <c r="H47" s="1">
+        <v>5</v>
+      </c>
+      <c r="I47" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="48" customHeight="1" spans="3:9">
       <c r="C48" s="1">
         <v>43</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="E48" s="1">
+        <v>70</v>
+      </c>
+      <c r="E48" s="3">
+        <v>5</v>
+      </c>
+      <c r="F48" s="1">
         <f t="shared" si="0"/>
         <v>1108</v>
       </c>
-      <c r="F48" s="1">
-        <v>5</v>
-      </c>
-      <c r="G48" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="H48" s="8" t="s">
-        <v>105</v>
-      </c>
-      <c r="I48" s="1">
+      <c r="G48" s="1">
         <v>86</v>
       </c>
-      <c r="J48" s="1">
+      <c r="H48" s="1">
         <v>2</v>
       </c>
-      <c r="K48" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="49" customHeight="1" spans="3:11">
+      <c r="I48" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="49" customHeight="1" spans="3:9">
       <c r="C49" s="1">
         <v>44</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="E49" s="1">
+        <v>71</v>
+      </c>
+      <c r="E49" s="3">
+        <v>5</v>
+      </c>
+      <c r="F49" s="1">
         <f t="shared" si="0"/>
         <v>1108</v>
       </c>
-      <c r="F49" s="1">
-        <v>5</v>
-      </c>
-      <c r="G49" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="H49" s="8" t="s">
-        <v>105</v>
-      </c>
-      <c r="I49" s="1">
+      <c r="G49" s="1">
         <v>82</v>
       </c>
-      <c r="J49" s="1">
+      <c r="H49" s="1">
         <v>2</v>
       </c>
-      <c r="K49" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="50" customHeight="1" spans="3:11">
+      <c r="I49" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="50" customHeight="1" spans="3:9">
       <c r="C50" s="1">
         <v>45</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="E50" s="1">
+        <v>72</v>
+      </c>
+      <c r="E50" s="3">
+        <v>5</v>
+      </c>
+      <c r="F50" s="1">
         <f t="shared" si="0"/>
         <v>1108</v>
       </c>
-      <c r="F50" s="1">
-        <v>5</v>
-      </c>
-      <c r="G50" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="H50" s="8" t="s">
-        <v>105</v>
-      </c>
-      <c r="I50" s="1">
+      <c r="G50" s="1">
         <v>83</v>
       </c>
-      <c r="J50" s="1">
+      <c r="H50" s="1">
         <v>2</v>
       </c>
-      <c r="K50" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="51" customHeight="1" spans="3:11">
+      <c r="I50" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="51" customHeight="1" spans="3:9">
       <c r="C51" s="1">
         <v>46</v>
       </c>
       <c r="D51" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="E51" s="1">
+        <v>73</v>
+      </c>
+      <c r="E51" s="3">
+        <v>5</v>
+      </c>
+      <c r="F51" s="1">
         <f t="shared" si="0"/>
         <v>1108</v>
       </c>
-      <c r="F51" s="1">
-        <v>5</v>
-      </c>
-      <c r="G51" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="H51" s="8" t="s">
-        <v>109</v>
-      </c>
-      <c r="I51" s="1">
+      <c r="G51" s="1">
         <v>1</v>
       </c>
-      <c r="J51" s="1">
+      <c r="H51" s="1">
         <v>6</v>
       </c>
-      <c r="K51" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="52" customHeight="1" spans="3:11">
+      <c r="I51" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="52" customHeight="1" spans="3:9">
       <c r="C52" s="1">
         <v>47</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="E52" s="1">
+        <v>74</v>
+      </c>
+      <c r="E52" s="3">
+        <v>5</v>
+      </c>
+      <c r="F52" s="1">
         <f t="shared" si="0"/>
         <v>1108</v>
       </c>
-      <c r="F52" s="1">
-        <v>5</v>
-      </c>
-      <c r="G52" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="H52" s="8" t="s">
-        <v>109</v>
-      </c>
-      <c r="I52" s="1">
+      <c r="G52" s="1">
         <v>2</v>
       </c>
-      <c r="J52" s="1">
+      <c r="H52" s="1">
         <v>6</v>
       </c>
-      <c r="K52" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="53" customHeight="1" spans="3:11">
+      <c r="I52" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="53" customHeight="1" spans="3:9">
       <c r="C53" s="1">
         <v>48</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="E53" s="1">
+        <v>71</v>
+      </c>
+      <c r="E53" s="3">
+        <v>5</v>
+      </c>
+      <c r="F53" s="1">
         <f t="shared" si="0"/>
         <v>1108</v>
       </c>
-      <c r="F53" s="1">
-        <v>5</v>
-      </c>
-      <c r="G53" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="H53" s="8" t="s">
-        <v>109</v>
-      </c>
-      <c r="I53" s="1">
+      <c r="G53" s="1">
         <v>3</v>
       </c>
-      <c r="J53" s="1">
+      <c r="H53" s="1">
         <v>6</v>
       </c>
-      <c r="K53" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="54" customHeight="1" spans="3:11">
+      <c r="I53" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="54" customHeight="1" spans="3:9">
       <c r="C54" s="1">
         <v>49</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="E54" s="1">
+        <v>75</v>
+      </c>
+      <c r="E54" s="3">
+        <v>5</v>
+      </c>
+      <c r="F54" s="1">
         <f t="shared" si="0"/>
         <v>1109</v>
       </c>
-      <c r="F54" s="1">
-        <v>5</v>
-      </c>
-      <c r="G54" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="H54" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="I54" s="1">
+      <c r="G54" s="1">
         <v>4</v>
       </c>
-      <c r="J54" s="1">
+      <c r="H54" s="1">
         <v>6</v>
       </c>
-      <c r="K54" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="55" customHeight="1" spans="3:11">
+      <c r="I54" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="55" customHeight="1" spans="3:9">
       <c r="C55" s="1">
         <v>50</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="E55" s="1">
+        <v>76</v>
+      </c>
+      <c r="E55" s="3">
+        <v>5</v>
+      </c>
+      <c r="F55" s="1">
         <f t="shared" si="0"/>
         <v>1109</v>
       </c>
-      <c r="F55" s="1">
-        <v>5</v>
-      </c>
-      <c r="G55" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="H55" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="I55" s="1">
-        <v>5</v>
-      </c>
-      <c r="J55" s="1">
+      <c r="G55" s="1">
+        <v>5</v>
+      </c>
+      <c r="H55" s="1">
         <v>6</v>
       </c>
-      <c r="K55" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="56" customHeight="1" spans="3:11">
+      <c r="I55" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="56" customHeight="1" spans="3:9">
       <c r="C56" s="1">
         <v>51</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="E56" s="1">
+        <v>77</v>
+      </c>
+      <c r="E56" s="3">
+        <v>5</v>
+      </c>
+      <c r="F56" s="1">
         <f t="shared" si="0"/>
         <v>1109</v>
       </c>
-      <c r="F56" s="1">
-        <v>5</v>
-      </c>
-      <c r="G56" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="H56" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="I56" s="1">
+      <c r="G56" s="1">
         <v>6</v>
       </c>
-      <c r="J56" s="1">
+      <c r="H56" s="1">
         <v>6</v>
       </c>
-      <c r="K56" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="57" customHeight="1" spans="3:11">
+      <c r="I56" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="57" customHeight="1" spans="3:9">
       <c r="C57" s="1">
         <v>52</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="E57" s="1">
+        <v>78</v>
+      </c>
+      <c r="E57" s="3">
+        <v>5</v>
+      </c>
+      <c r="F57" s="1">
         <f t="shared" si="0"/>
         <v>1109</v>
       </c>
-      <c r="F57" s="1">
-        <v>5</v>
-      </c>
-      <c r="G57" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="H57" s="8" t="s">
-        <v>116</v>
-      </c>
-      <c r="I57" s="1">
+      <c r="G57" s="1">
         <v>85</v>
       </c>
-      <c r="J57" s="1">
+      <c r="H57" s="1">
         <v>2</v>
       </c>
-      <c r="K57" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="58" customHeight="1" spans="3:11">
+      <c r="I57" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="58" customHeight="1" spans="3:9">
       <c r="C58" s="1">
         <v>53</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="E58" s="1">
+        <v>79</v>
+      </c>
+      <c r="E58" s="3">
+        <v>5</v>
+      </c>
+      <c r="F58" s="1">
         <f t="shared" si="0"/>
         <v>1109</v>
       </c>
-      <c r="F58" s="1">
-        <v>5</v>
-      </c>
-      <c r="G58" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="H58" s="8" t="s">
-        <v>116</v>
-      </c>
-      <c r="I58" s="1">
+      <c r="G58" s="1">
         <v>81</v>
       </c>
-      <c r="J58" s="1">
+      <c r="H58" s="1">
         <v>2</v>
       </c>
-      <c r="K58" s="1" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="59" customHeight="1" spans="3:11">
+      <c r="I58" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="59" customHeight="1" spans="3:9">
       <c r="C59" s="1">
         <v>54</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="E59" s="1">
+        <v>80</v>
+      </c>
+      <c r="E59" s="3">
+        <v>5</v>
+      </c>
+      <c r="F59" s="1">
         <f t="shared" si="0"/>
         <v>1109</v>
       </c>
-      <c r="F59" s="1">
-        <v>5</v>
-      </c>
-      <c r="G59" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="H59" s="8" t="s">
-        <v>116</v>
-      </c>
-      <c r="I59" s="1">
+      <c r="G59" s="1">
         <v>84</v>
       </c>
-      <c r="J59" s="1">
+      <c r="H59" s="1">
         <v>2</v>
       </c>
-      <c r="K59" s="1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="60" customHeight="1" spans="3:11">
+      <c r="I59" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="60" customHeight="1" spans="3:9">
       <c r="C60" s="1">
         <v>55</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="E60" s="1">
+        <v>81</v>
+      </c>
+      <c r="E60" s="3">
+        <v>5</v>
+      </c>
+      <c r="F60" s="1">
         <f t="shared" si="0"/>
         <v>1110</v>
       </c>
-      <c r="F60" s="1">
-        <v>5</v>
-      </c>
-      <c r="G60" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="H60" s="8" t="s">
-        <v>120</v>
-      </c>
-      <c r="I60" s="1">
+      <c r="G60" s="1">
         <v>1</v>
       </c>
-      <c r="J60" s="1">
+      <c r="H60" s="1">
         <v>7</v>
       </c>
-      <c r="K60" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="61" customHeight="1" spans="3:11">
+      <c r="I60" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="61" customHeight="1" spans="3:9">
       <c r="C61" s="1">
         <v>56</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="E61" s="1">
+        <v>82</v>
+      </c>
+      <c r="E61" s="3">
+        <v>5</v>
+      </c>
+      <c r="F61" s="1">
         <f t="shared" si="0"/>
         <v>1110</v>
       </c>
-      <c r="F61" s="1">
-        <v>5</v>
-      </c>
-      <c r="G61" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="H61" s="8" t="s">
-        <v>120</v>
-      </c>
-      <c r="I61" s="1">
+      <c r="G61" s="1">
         <v>2</v>
       </c>
-      <c r="J61" s="1">
+      <c r="H61" s="1">
         <v>7</v>
       </c>
-      <c r="K61" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="62" customHeight="1" spans="3:11">
+      <c r="I61" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="62" customHeight="1" spans="3:9">
       <c r="C62" s="1">
         <v>57</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="E62" s="1">
+        <v>58</v>
+      </c>
+      <c r="E62" s="3">
+        <v>5</v>
+      </c>
+      <c r="F62" s="1">
         <f t="shared" si="0"/>
         <v>1110</v>
       </c>
-      <c r="F62" s="1">
-        <v>5</v>
-      </c>
-      <c r="G62" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="H62" s="8" t="s">
-        <v>120</v>
-      </c>
-      <c r="I62" s="1">
+      <c r="G62" s="1">
         <v>3</v>
       </c>
-      <c r="J62" s="1">
+      <c r="H62" s="1">
         <v>7</v>
       </c>
-      <c r="K62" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="63" customHeight="1" spans="3:11">
+      <c r="I62" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="63" customHeight="1" spans="3:9">
       <c r="C63" s="1">
         <v>58</v>
       </c>
       <c r="D63" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="E63" s="1">
+        <v>83</v>
+      </c>
+      <c r="E63" s="3">
+        <v>5</v>
+      </c>
+      <c r="F63" s="1">
         <f t="shared" si="0"/>
         <v>1110</v>
       </c>
-      <c r="F63" s="1">
-        <v>5</v>
-      </c>
-      <c r="G63" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="H63" s="8" t="s">
-        <v>123</v>
-      </c>
-      <c r="I63" s="1">
+      <c r="G63" s="1">
         <v>4</v>
       </c>
-      <c r="J63" s="1">
+      <c r="H63" s="1">
         <v>7</v>
       </c>
-      <c r="K63" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="64" customHeight="1" spans="3:11">
+      <c r="I63" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="64" customHeight="1" spans="3:9">
       <c r="C64" s="1">
         <v>59</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="E64" s="1">
+        <v>84</v>
+      </c>
+      <c r="E64" s="3">
+        <v>5</v>
+      </c>
+      <c r="F64" s="1">
         <f t="shared" si="0"/>
         <v>1110</v>
       </c>
-      <c r="F64" s="1">
-        <v>5</v>
-      </c>
-      <c r="G64" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="H64" s="8" t="s">
-        <v>123</v>
-      </c>
-      <c r="I64" s="1">
-        <v>5</v>
-      </c>
-      <c r="J64" s="1">
+      <c r="G64" s="1">
+        <v>5</v>
+      </c>
+      <c r="H64" s="1">
         <v>7</v>
       </c>
-      <c r="K64" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="65" customHeight="1" spans="3:11">
+      <c r="I64" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="65" customHeight="1" spans="3:9">
       <c r="C65" s="1">
         <v>60</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="E65" s="1">
+        <v>85</v>
+      </c>
+      <c r="E65" s="3">
+        <v>5</v>
+      </c>
+      <c r="F65" s="1">
         <f t="shared" si="0"/>
         <v>1110</v>
       </c>
-      <c r="F65" s="1">
-        <v>5</v>
-      </c>
-      <c r="G65" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="H65" s="8" t="s">
-        <v>123</v>
-      </c>
-      <c r="I65" s="1">
+      <c r="G65" s="1">
         <v>6</v>
       </c>
-      <c r="J65" s="1">
+      <c r="H65" s="1">
         <v>7</v>
       </c>
-      <c r="K65" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="66" customHeight="1" spans="3:11">
+      <c r="I65" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="66" customHeight="1" spans="3:9">
       <c r="C66" s="1">
         <v>61</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="E66" s="1">
+        <v>86</v>
+      </c>
+      <c r="E66" s="3">
+        <v>5</v>
+      </c>
+      <c r="F66" s="1">
         <f t="shared" si="0"/>
         <v>1111</v>
       </c>
-      <c r="F66" s="1">
-        <v>5</v>
-      </c>
-      <c r="G66" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="H66" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="I66" s="1">
+      <c r="G66" s="1">
         <v>13</v>
       </c>
-      <c r="J66" s="1">
+      <c r="H66" s="1">
         <v>2</v>
       </c>
-      <c r="K66" s="1" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="67" customHeight="1" spans="3:11">
+      <c r="I66" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="67" customHeight="1" spans="3:9">
       <c r="C67" s="1">
         <v>62</v>
       </c>
       <c r="D67" s="6" t="s">
-        <v>128</v>
-      </c>
-      <c r="E67" s="1">
+        <v>87</v>
+      </c>
+      <c r="E67" s="3">
+        <v>5</v>
+      </c>
+      <c r="F67" s="1">
         <f t="shared" si="0"/>
         <v>1111</v>
       </c>
-      <c r="F67" s="1">
-        <v>5</v>
-      </c>
-      <c r="G67" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="H67" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="I67" s="1">
+      <c r="G67" s="1">
         <v>14</v>
       </c>
-      <c r="J67" s="1">
+      <c r="H67" s="1">
         <v>2</v>
       </c>
-      <c r="K67" s="1" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="68" customHeight="1" spans="3:11">
+      <c r="I67" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="68" customHeight="1" spans="3:9">
       <c r="C68" s="1">
         <v>63</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="E68" s="1">
+        <v>88</v>
+      </c>
+      <c r="E68" s="3">
+        <v>5</v>
+      </c>
+      <c r="F68" s="1">
         <f t="shared" si="0"/>
         <v>1111</v>
       </c>
-      <c r="F68" s="1">
-        <v>5</v>
-      </c>
-      <c r="G68" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="H68" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="I68" s="1">
+      <c r="G68" s="1">
         <v>22</v>
       </c>
-      <c r="J68" s="1">
+      <c r="H68" s="1">
         <v>2</v>
       </c>
-      <c r="K68" s="1" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="69" customHeight="1" spans="3:11">
+      <c r="I68" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="69" customHeight="1" spans="3:9">
       <c r="C69" s="1">
         <v>64</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="E69" s="1">
+        <v>89</v>
+      </c>
+      <c r="E69" s="3">
+        <v>5</v>
+      </c>
+      <c r="F69" s="1">
         <f t="shared" si="0"/>
         <v>1111</v>
       </c>
-      <c r="F69" s="1">
-        <v>5</v>
-      </c>
-      <c r="G69" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="H69" s="8" t="s">
-        <v>131</v>
-      </c>
-      <c r="I69" s="1">
+      <c r="G69" s="1">
         <v>1</v>
       </c>
-      <c r="J69" s="1">
+      <c r="H69" s="1">
         <v>8</v>
       </c>
-      <c r="K69" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="70" customHeight="1" spans="3:11">
+      <c r="I69" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="70" customHeight="1" spans="3:9">
       <c r="C70" s="1">
         <v>65</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="E70" s="1">
-        <f t="shared" ref="E70:E77" si="1">INT((C70-1)/6)+1101</f>
+        <v>90</v>
+      </c>
+      <c r="E70" s="3">
+        <v>5</v>
+      </c>
+      <c r="F70" s="1">
+        <f t="shared" ref="F70:F77" si="1">INT((C70-1)/6)+1101</f>
         <v>1111</v>
       </c>
-      <c r="F70" s="1">
-        <v>5</v>
-      </c>
-      <c r="G70" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="H70" s="8" t="s">
-        <v>131</v>
-      </c>
-      <c r="I70" s="1">
+      <c r="G70" s="1">
         <v>2</v>
       </c>
-      <c r="J70" s="1">
+      <c r="H70" s="1">
         <v>8</v>
       </c>
-      <c r="K70" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="71" customHeight="1" spans="3:11">
+      <c r="I70" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="71" customHeight="1" spans="3:9">
       <c r="C71" s="1">
         <v>66</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="E71" s="1">
+        <v>91</v>
+      </c>
+      <c r="E71" s="3">
+        <v>5</v>
+      </c>
+      <c r="F71" s="1">
         <f t="shared" si="1"/>
         <v>1111</v>
       </c>
-      <c r="F71" s="1">
-        <v>5</v>
-      </c>
-      <c r="G71" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="H71" s="8" t="s">
-        <v>131</v>
-      </c>
-      <c r="I71" s="1">
+      <c r="G71" s="1">
         <v>3</v>
       </c>
-      <c r="J71" s="1">
+      <c r="H71" s="1">
         <v>8</v>
       </c>
-      <c r="K71" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="72" customHeight="1" spans="3:11">
+      <c r="I71" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="72" customHeight="1" spans="3:9">
       <c r="C72" s="1">
         <v>67</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="E72" s="1">
+        <v>89</v>
+      </c>
+      <c r="E72" s="3">
+        <v>5</v>
+      </c>
+      <c r="F72" s="1">
         <f t="shared" si="1"/>
         <v>1112</v>
       </c>
-      <c r="F72" s="1">
-        <v>5</v>
-      </c>
-      <c r="G72" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="H72" s="8" t="s">
-        <v>134</v>
-      </c>
-      <c r="I72" s="1">
+      <c r="G72" s="1">
         <v>4</v>
       </c>
-      <c r="J72" s="1">
+      <c r="H72" s="1">
         <v>8</v>
       </c>
-      <c r="K72" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="73" customHeight="1" spans="3:11">
+      <c r="I72" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="73" customHeight="1" spans="3:9">
       <c r="C73" s="1">
         <v>68</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="E73" s="1">
+        <v>92</v>
+      </c>
+      <c r="E73" s="3">
+        <v>5</v>
+      </c>
+      <c r="F73" s="1">
         <f t="shared" si="1"/>
         <v>1112</v>
       </c>
-      <c r="F73" s="1">
-        <v>5</v>
-      </c>
-      <c r="G73" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="H73" s="8" t="s">
-        <v>134</v>
-      </c>
-      <c r="I73" s="1">
-        <v>5</v>
-      </c>
-      <c r="J73" s="1">
+      <c r="G73" s="1">
+        <v>5</v>
+      </c>
+      <c r="H73" s="1">
         <v>8</v>
       </c>
-      <c r="K73" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="74" customHeight="1" spans="3:11">
+      <c r="I73" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="74" customHeight="1" spans="3:9">
       <c r="C74" s="1">
         <v>69</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="E74" s="1">
+        <v>93</v>
+      </c>
+      <c r="E74" s="3">
+        <v>5</v>
+      </c>
+      <c r="F74" s="1">
         <f t="shared" si="1"/>
         <v>1112</v>
       </c>
-      <c r="F74" s="1">
-        <v>5</v>
-      </c>
-      <c r="G74" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="H74" s="8" t="s">
-        <v>134</v>
-      </c>
-      <c r="I74" s="1">
+      <c r="G74" s="1">
         <v>6</v>
       </c>
-      <c r="J74" s="1">
+      <c r="H74" s="1">
         <v>8</v>
       </c>
-      <c r="K74" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="75" customHeight="1" spans="3:11">
+      <c r="I74" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="75" customHeight="1" spans="3:9">
       <c r="C75" s="1">
         <v>70</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="E75" s="1">
+        <v>94</v>
+      </c>
+      <c r="E75" s="3">
+        <v>5</v>
+      </c>
+      <c r="F75" s="1">
         <f t="shared" si="1"/>
         <v>1112</v>
       </c>
-      <c r="F75" s="1">
-        <v>5</v>
-      </c>
-      <c r="G75" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="H75" s="8" t="s">
-        <v>138</v>
-      </c>
-      <c r="I75" s="1">
+      <c r="G75" s="1">
         <v>12</v>
       </c>
-      <c r="J75" s="1">
+      <c r="H75" s="1">
         <v>2</v>
       </c>
-      <c r="K75" s="1" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="76" customHeight="1" spans="3:11">
+      <c r="I75" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="76" customHeight="1" spans="3:9">
       <c r="C76" s="1">
         <v>71</v>
       </c>
       <c r="D76" s="5" t="s">
-        <v>139</v>
-      </c>
-      <c r="E76" s="1">
+        <v>95</v>
+      </c>
+      <c r="E76" s="3">
+        <v>5</v>
+      </c>
+      <c r="F76" s="1">
         <f t="shared" si="1"/>
         <v>1112</v>
       </c>
-      <c r="F76" s="1">
-        <v>5</v>
-      </c>
-      <c r="G76" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="H76" s="8" t="s">
-        <v>138</v>
-      </c>
-      <c r="I76" s="1">
+      <c r="G76" s="1">
         <v>10</v>
       </c>
-      <c r="J76" s="1">
+      <c r="H76" s="1">
         <v>2</v>
       </c>
-      <c r="K76" s="1" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="77" customHeight="1" spans="3:11">
+      <c r="I76" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="77" customHeight="1" spans="3:9">
       <c r="C77" s="1">
         <v>72</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="E77" s="1">
+        <v>96</v>
+      </c>
+      <c r="E77" s="3">
+        <v>5</v>
+      </c>
+      <c r="F77" s="1">
         <f t="shared" si="1"/>
         <v>1112</v>
       </c>
-      <c r="F77" s="1">
-        <v>5</v>
-      </c>
-      <c r="G77" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="H77" s="8" t="s">
-        <v>138</v>
-      </c>
-      <c r="I77" s="1">
+      <c r="G77" s="1">
         <v>11</v>
       </c>
-      <c r="J77" s="1">
+      <c r="H77" s="1">
         <v>2</v>
       </c>
-      <c r="K77" s="1" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="106" customHeight="1" spans="5:8">
-      <c r="E106" s="7"/>
+      <c r="I77" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="106" customHeight="1" spans="6:6">
       <c r="F106" s="7"/>
-      <c r="G106" s="7"/>
-      <c r="H106" s="7"/>
-    </row>
-    <row r="107" customHeight="1" spans="5:8">
-      <c r="E107" s="7"/>
+    </row>
+    <row r="107" customHeight="1" spans="6:6">
       <c r="F107" s="7"/>
-      <c r="G107" s="7"/>
-      <c r="H107" s="7"/>
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="K3:K5 C3:D5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="F3 F4 F5" errorStyle="warning">
+      <formula1>COUNTIF($A:$A,F3)&lt;2</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="E3:E5 I3:I5 C3:D5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="E3:H5" errorStyle="warning">
-      <formula1>COUNTIF($A:$A,E3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Excel/PetConfig.xlsx
+++ b/Excel/PetConfig.xlsx
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="108">
   <si>
     <t>#</t>
   </si>
@@ -77,7 +77,7 @@
     <t>CardId</t>
   </si>
   <si>
-    <t>TraitId</t>
+    <t>TraitIdList</t>
   </si>
   <si>
     <t>TraitLevel</t>
@@ -92,58 +92,91 @@
     <t>string</t>
   </si>
   <si>
+    <t>int[]</t>
+  </si>
+  <si>
     <t>狼宝宝</t>
   </si>
   <si>
+    <t>1</t>
+  </si>
+  <si>
     <t>基础生命</t>
   </si>
   <si>
+    <t>1,2,3,10</t>
+  </si>
+  <si>
     <t>骷髅宝宝</t>
   </si>
   <si>
     <t>基础防御</t>
   </si>
   <si>
+    <t>4,5,6,11</t>
+  </si>
+  <si>
     <t>兽人宝宝</t>
   </si>
   <si>
     <t>基础攻击</t>
   </si>
   <si>
+    <t>1,2,3,12</t>
+  </si>
+  <si>
     <t>蜘蛛宝宝</t>
   </si>
   <si>
     <t>基础物攻</t>
   </si>
   <si>
+    <t>4,5,6,13</t>
+  </si>
+  <si>
     <t>岩蝎宝宝</t>
   </si>
   <si>
     <t>基础魔法</t>
   </si>
   <si>
+    <t>1,2,3,14</t>
+  </si>
+  <si>
     <t>鬃狮宝宝</t>
   </si>
   <si>
     <t>基础道术</t>
   </si>
   <si>
+    <t>4,5,6,15</t>
+  </si>
+  <si>
     <t>毒蛆宝宝</t>
   </si>
   <si>
     <t>杀敌经验</t>
   </si>
   <si>
+    <t>1,2,3,21</t>
+  </si>
+  <si>
     <t>蜈蚣宝宝</t>
   </si>
   <si>
     <t>经验加成</t>
   </si>
   <si>
+    <t>4,5,6,22</t>
+  </si>
+  <si>
     <t>双头宝宝</t>
   </si>
   <si>
     <t>品质加成</t>
+  </si>
+  <si>
+    <t>81,82,83,84,85,86</t>
   </si>
   <si>
     <t>蛛王宝宝</t>
@@ -1018,6 +1051,7 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1337,7 +1371,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:I107"/>
+  <dimension ref="C1:J107"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="1"/>
@@ -1346,20 +1380,21 @@
     <col min="7" max="7" width="14.8333333333333" style="1" customWidth="1"/>
     <col min="8" max="8" width="13" style="1" customWidth="1"/>
     <col min="9" max="9" width="17" style="1" customWidth="1"/>
-    <col min="10" max="16384" width="9" style="1"/>
+    <col min="10" max="10" width="28.5833333333333" style="1" customWidth="1"/>
+    <col min="11" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" customHeight="1" spans="3:9">
+    <row r="1" customHeight="1" spans="3:10">
       <c r="I1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" customHeight="1" spans="3:9">
+    <row r="2" customHeight="1" spans="3:10">
       <c r="I2" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:9">
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:10">
       <c r="C3" s="2" t="s">
         <v>1</v>
       </c>
@@ -1381,8 +1416,11 @@
       <c r="I3" s="2" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:9">
+      <c r="J3" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:10">
       <c r="C4" s="2" t="s">
         <v>7</v>
       </c>
@@ -1404,8 +1442,11 @@
       <c r="I4" s="2" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:9">
+      <c r="J4" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:10">
       <c r="C5" s="2" t="s">
         <v>8</v>
       </c>
@@ -1419,7 +1460,7 @@
         <v>8</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>8</v>
@@ -1427,13 +1468,16 @@
       <c r="I5" s="2" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" s="1" customFormat="1" customHeight="1" spans="3:9">
+      <c r="J5" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" s="1" customFormat="1" customHeight="1" spans="3:10">
       <c r="C6" s="1">
         <v>1</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E6" s="3">
         <v>5</v>
@@ -1442,22 +1486,25 @@
         <f t="shared" ref="F6:F69" si="0">INT((C6-1)/6)+1101</f>
         <v>1101</v>
       </c>
-      <c r="G6" s="1">
-        <v>1</v>
+      <c r="G6" s="8" t="s">
+        <v>12</v>
       </c>
       <c r="H6" s="1">
         <v>1</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="7" s="1" customFormat="1" customHeight="1" spans="3:9">
+        <v>13</v>
+      </c>
+      <c r="J6" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" customHeight="1" spans="3:10">
       <c r="C7" s="1">
         <v>2</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E7" s="3">
         <v>5</v>
@@ -1473,15 +1520,18 @@
         <v>1</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:9">
+        <v>16</v>
+      </c>
+      <c r="J7" s="8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:10">
       <c r="C8" s="1">
         <v>3</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E8" s="3">
         <v>5</v>
@@ -1497,15 +1547,18 @@
         <v>1</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="9" s="1" customFormat="1" customHeight="1" spans="3:9">
+        <v>19</v>
+      </c>
+      <c r="J8" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" s="1" customFormat="1" customHeight="1" spans="3:10">
       <c r="C9" s="1">
         <v>4</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="E9" s="3">
         <v>5</v>
@@ -1521,15 +1574,18 @@
         <v>1</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="10" s="1" customFormat="1" customHeight="1" spans="3:9">
+        <v>22</v>
+      </c>
+      <c r="J9" s="8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="10" s="1" customFormat="1" customHeight="1" spans="3:10">
       <c r="C10" s="1">
         <v>5</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="E10" s="3">
         <v>5</v>
@@ -1545,15 +1601,18 @@
         <v>1</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:9">
+        <v>25</v>
+      </c>
+      <c r="J10" s="8" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:10">
       <c r="C11" s="1">
         <v>6</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="E11" s="3">
         <v>5</v>
@@ -1569,15 +1628,18 @@
         <v>1</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="12" s="1" customFormat="1" customHeight="1" spans="3:9">
+        <v>28</v>
+      </c>
+      <c r="J11" s="8" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="12" s="1" customFormat="1" customHeight="1" spans="3:10">
       <c r="C12" s="1">
         <v>7</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="E12" s="3">
         <v>5</v>
@@ -1593,15 +1655,18 @@
         <v>1</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="13" s="1" customFormat="1" customHeight="1" spans="3:9">
+        <v>31</v>
+      </c>
+      <c r="J12" s="8" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="13" s="1" customFormat="1" customHeight="1" spans="3:10">
       <c r="C13" s="1">
         <v>8</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="E13" s="3">
         <v>5</v>
@@ -1617,15 +1682,18 @@
         <v>1</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="14" customHeight="1" spans="3:9">
+        <v>34</v>
+      </c>
+      <c r="J13" s="8" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="14" customHeight="1" spans="3:10">
       <c r="C14" s="1">
         <v>9</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="E14" s="3">
         <v>5</v>
@@ -1641,15 +1709,18 @@
         <v>1</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="15" s="1" customFormat="1" customHeight="1" spans="3:9">
+        <v>37</v>
+      </c>
+      <c r="J14" s="8" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="15" s="1" customFormat="1" customHeight="1" spans="3:10">
       <c r="C15" s="1">
         <v>10</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="E15" s="3">
         <v>5</v>
@@ -1665,15 +1736,15 @@
         <v>2</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="16" s="1" customFormat="1" customHeight="1" spans="3:9">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="16" s="1" customFormat="1" customHeight="1" spans="3:10">
       <c r="C16" s="1">
         <v>11</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="E16" s="3">
         <v>5</v>
@@ -1689,15 +1760,15 @@
         <v>2</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="17" s="1" customFormat="1" customHeight="1" spans="3:9">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17" s="1" customFormat="1" customHeight="1" spans="3:10">
       <c r="C17" s="1">
         <v>12</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="E17" s="3">
         <v>5</v>
@@ -1713,15 +1784,15 @@
         <v>2</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="18" s="1" customFormat="1" customHeight="1" spans="3:9">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="18" s="1" customFormat="1" customHeight="1" spans="3:10">
       <c r="C18" s="1">
         <v>13</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="E18" s="3">
         <v>5</v>
@@ -1737,15 +1808,18 @@
         <v>2</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="19" s="1" customFormat="1" customHeight="1" spans="3:9">
+        <v>22</v>
+      </c>
+      <c r="J18" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" s="1" customFormat="1" customHeight="1" spans="3:10">
       <c r="C19" s="1">
         <v>14</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="E19" s="3">
         <v>5</v>
@@ -1761,15 +1835,15 @@
         <v>2</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="20" s="1" customFormat="1" customHeight="1" spans="3:9">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="20" s="1" customFormat="1" customHeight="1" spans="3:10">
       <c r="C20" s="1">
         <v>15</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="E20" s="3">
         <v>5</v>
@@ -1785,15 +1859,18 @@
         <v>2</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="21" s="1" customFormat="1" customHeight="1" spans="3:9">
+        <v>28</v>
+      </c>
+      <c r="J20" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="21" s="1" customFormat="1" customHeight="1" spans="3:10">
       <c r="C21" s="1">
         <v>16</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="E21" s="3">
         <v>5</v>
@@ -1809,15 +1886,18 @@
         <v>1</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="22" s="1" customFormat="1" customHeight="1" spans="3:9">
+        <v>46</v>
+      </c>
+      <c r="J21" s="1">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="22" s="1" customFormat="1" customHeight="1" spans="3:10">
       <c r="C22" s="1">
         <v>17</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="E22" s="3">
         <v>5</v>
@@ -1833,15 +1913,18 @@
         <v>1</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="23" s="1" customFormat="1" customHeight="1" spans="3:9">
+        <v>48</v>
+      </c>
+      <c r="J22" s="1">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="23" s="1" customFormat="1" customHeight="1" spans="3:10">
       <c r="C23" s="1">
         <v>18</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="E23" s="3">
         <v>5</v>
@@ -1857,15 +1940,18 @@
         <v>1</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="24" s="1" customFormat="1" customHeight="1" spans="3:9">
+        <v>50</v>
+      </c>
+      <c r="J23" s="1">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="24" s="1" customFormat="1" customHeight="1" spans="3:10">
       <c r="C24" s="1">
         <v>19</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="E24" s="3">
         <v>5</v>
@@ -1881,15 +1967,18 @@
         <v>3</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="25" s="1" customFormat="1" customHeight="1" spans="3:9">
+        <v>13</v>
+      </c>
+      <c r="J24" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" s="1" customFormat="1" customHeight="1" spans="3:10">
       <c r="C25" s="1">
         <v>20</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="E25" s="3">
         <v>5</v>
@@ -1905,15 +1994,18 @@
         <v>3</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="26" s="1" customFormat="1" customHeight="1" spans="3:9">
+        <v>16</v>
+      </c>
+      <c r="J25" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26" s="1" customFormat="1" customHeight="1" spans="3:10">
       <c r="C26" s="1">
         <v>21</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="E26" s="3">
         <v>5</v>
@@ -1929,15 +2021,18 @@
         <v>3</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="27" customHeight="1" spans="3:9">
+        <v>19</v>
+      </c>
+      <c r="J26" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" customHeight="1" spans="3:10">
       <c r="C27" s="1">
         <v>22</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="E27" s="3">
         <v>5</v>
@@ -1953,15 +2048,18 @@
         <v>3</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="28" customHeight="1" spans="3:9">
+        <v>22</v>
+      </c>
+      <c r="J27" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" customHeight="1" spans="3:10">
       <c r="C28" s="1">
         <v>23</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="E28" s="3">
         <v>5</v>
@@ -1977,15 +2075,18 @@
         <v>3</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="29" customHeight="1" spans="3:9">
+        <v>25</v>
+      </c>
+      <c r="J28" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="29" customHeight="1" spans="3:10">
       <c r="C29" s="1">
         <v>24</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="E29" s="3">
         <v>5</v>
@@ -2001,15 +2102,18 @@
         <v>3</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="30" customHeight="1" spans="3:9">
+        <v>28</v>
+      </c>
+      <c r="J29" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30" customHeight="1" spans="3:10">
       <c r="C30" s="1">
         <v>25</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="E30" s="3">
         <v>5</v>
@@ -2025,15 +2129,18 @@
         <v>1</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="31" customHeight="1" spans="3:9">
+        <v>58</v>
+      </c>
+      <c r="J30" s="1">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="31" customHeight="1" spans="3:10">
       <c r="C31" s="1">
         <v>26</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="E31" s="3">
         <v>5</v>
@@ -2049,15 +2156,18 @@
         <v>1</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="32" customHeight="1" spans="3:9">
+        <v>60</v>
+      </c>
+      <c r="J31" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="32" customHeight="1" spans="3:10">
       <c r="C32" s="1">
         <v>27</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="E32" s="3">
         <v>5</v>
@@ -2073,15 +2183,18 @@
         <v>1</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="33" customHeight="1" spans="3:9">
+        <v>62</v>
+      </c>
+      <c r="J32" s="1">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="33" customHeight="1" spans="3:10">
       <c r="C33" s="1">
         <v>28</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="E33" s="3">
         <v>5</v>
@@ -2097,15 +2210,18 @@
         <v>4</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="34" customHeight="1" spans="3:9">
+        <v>13</v>
+      </c>
+      <c r="J33" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" customHeight="1" spans="3:10">
       <c r="C34" s="1">
         <v>29</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="E34" s="3">
         <v>5</v>
@@ -2121,15 +2237,18 @@
         <v>4</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="35" customHeight="1" spans="3:9">
+        <v>16</v>
+      </c>
+      <c r="J34" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="35" customHeight="1" spans="3:10">
       <c r="C35" s="1">
         <v>30</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="E35" s="3">
         <v>5</v>
@@ -2145,15 +2264,18 @@
         <v>4</v>
       </c>
       <c r="I35" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="36" customHeight="1" spans="3:9">
+        <v>19</v>
+      </c>
+      <c r="J35" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="36" customHeight="1" spans="3:10">
       <c r="C36" s="1">
         <v>31</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="E36" s="3">
         <v>5</v>
@@ -2169,15 +2291,18 @@
         <v>4</v>
       </c>
       <c r="I36" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="37" customHeight="1" spans="3:9">
+        <v>22</v>
+      </c>
+      <c r="J36" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" customHeight="1" spans="3:10">
       <c r="C37" s="1">
         <v>32</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="E37" s="3">
         <v>5</v>
@@ -2193,15 +2318,18 @@
         <v>4</v>
       </c>
       <c r="I37" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="38" customHeight="1" spans="3:9">
+        <v>25</v>
+      </c>
+      <c r="J37" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="38" customHeight="1" spans="3:10">
       <c r="C38" s="1">
         <v>33</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="E38" s="3">
         <v>5</v>
@@ -2217,15 +2345,18 @@
         <v>4</v>
       </c>
       <c r="I38" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="39" customHeight="1" spans="3:9">
+        <v>28</v>
+      </c>
+      <c r="J38" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="39" customHeight="1" spans="3:10">
       <c r="C39" s="1">
         <v>34</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="E39" s="3">
         <v>5</v>
@@ -2241,15 +2372,18 @@
         <v>1</v>
       </c>
       <c r="I39" s="1" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="40" customHeight="1" spans="3:9">
+        <v>70</v>
+      </c>
+      <c r="J39" s="1">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="40" customHeight="1" spans="3:10">
       <c r="C40" s="1">
         <v>35</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="E40" s="3">
         <v>5</v>
@@ -2265,15 +2399,18 @@
         <v>1</v>
       </c>
       <c r="I40" s="1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="41" customHeight="1" spans="3:9">
+        <v>72</v>
+      </c>
+      <c r="J40" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="41" customHeight="1" spans="3:10">
       <c r="C41" s="1">
         <v>36</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>62</v>
+        <v>73</v>
       </c>
       <c r="E41" s="3">
         <v>5</v>
@@ -2289,15 +2426,18 @@
         <v>1</v>
       </c>
       <c r="I41" s="1" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="42" customHeight="1" spans="3:9">
+        <v>74</v>
+      </c>
+      <c r="J41" s="1">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="42" customHeight="1" spans="3:10">
       <c r="C42" s="1">
         <v>37</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="E42" s="3">
         <v>5</v>
@@ -2313,15 +2453,18 @@
         <v>5</v>
       </c>
       <c r="I42" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="43" customHeight="1" spans="3:9">
+        <v>13</v>
+      </c>
+      <c r="J42" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" customHeight="1" spans="3:10">
       <c r="C43" s="1">
         <v>38</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="E43" s="3">
         <v>5</v>
@@ -2337,15 +2480,18 @@
         <v>5</v>
       </c>
       <c r="I43" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="44" customHeight="1" spans="3:9">
+        <v>16</v>
+      </c>
+      <c r="J43" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="44" customHeight="1" spans="3:10">
       <c r="C44" s="1">
         <v>39</v>
       </c>
       <c r="D44" s="5" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="E44" s="3">
         <v>5</v>
@@ -2361,15 +2507,18 @@
         <v>5</v>
       </c>
       <c r="I44" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="45" customHeight="1" spans="3:9">
+        <v>19</v>
+      </c>
+      <c r="J44" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" customHeight="1" spans="3:10">
       <c r="C45" s="1">
         <v>40</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="E45" s="3">
         <v>5</v>
@@ -2385,15 +2534,18 @@
         <v>5</v>
       </c>
       <c r="I45" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="46" customHeight="1" spans="3:9">
+        <v>22</v>
+      </c>
+      <c r="J45" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" customHeight="1" spans="3:10">
       <c r="C46" s="1">
         <v>41</v>
       </c>
       <c r="D46" s="6" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="E46" s="3">
         <v>5</v>
@@ -2409,15 +2561,18 @@
         <v>5</v>
       </c>
       <c r="I46" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="47" customHeight="1" spans="3:9">
+        <v>25</v>
+      </c>
+      <c r="J46" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47" customHeight="1" spans="3:10">
       <c r="C47" s="1">
         <v>42</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="E47" s="3">
         <v>5</v>
@@ -2433,15 +2588,18 @@
         <v>5</v>
       </c>
       <c r="I47" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="48" customHeight="1" spans="3:9">
+        <v>28</v>
+      </c>
+      <c r="J47" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="48" customHeight="1" spans="3:10">
       <c r="C48" s="1">
         <v>43</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="E48" s="3">
         <v>5</v>
@@ -2457,15 +2615,18 @@
         <v>2</v>
       </c>
       <c r="I48" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="49" customHeight="1" spans="3:9">
+        <v>31</v>
+      </c>
+      <c r="J48" s="1">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="49" customHeight="1" spans="3:10">
       <c r="C49" s="1">
         <v>44</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="E49" s="3">
         <v>5</v>
@@ -2481,15 +2642,18 @@
         <v>2</v>
       </c>
       <c r="I49" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="50" customHeight="1" spans="3:9">
+        <v>34</v>
+      </c>
+      <c r="J49" s="1">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="50" customHeight="1" spans="3:10">
       <c r="C50" s="1">
         <v>45</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="E50" s="3">
         <v>5</v>
@@ -2505,15 +2669,18 @@
         <v>2</v>
       </c>
       <c r="I50" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="51" customHeight="1" spans="3:9">
+        <v>37</v>
+      </c>
+      <c r="J50" s="1">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="51" customHeight="1" spans="3:10">
       <c r="C51" s="1">
         <v>46</v>
       </c>
       <c r="D51" s="6" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="E51" s="3">
         <v>5</v>
@@ -2529,15 +2696,18 @@
         <v>6</v>
       </c>
       <c r="I51" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="52" customHeight="1" spans="3:9">
+        <v>13</v>
+      </c>
+      <c r="J51" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" customHeight="1" spans="3:10">
       <c r="C52" s="1">
         <v>47</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>74</v>
+        <v>85</v>
       </c>
       <c r="E52" s="3">
         <v>5</v>
@@ -2553,15 +2723,18 @@
         <v>6</v>
       </c>
       <c r="I52" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="53" customHeight="1" spans="3:9">
+        <v>16</v>
+      </c>
+      <c r="J52" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="53" customHeight="1" spans="3:10">
       <c r="C53" s="1">
         <v>48</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="E53" s="3">
         <v>5</v>
@@ -2577,15 +2750,18 @@
         <v>6</v>
       </c>
       <c r="I53" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="54" customHeight="1" spans="3:9">
+        <v>19</v>
+      </c>
+      <c r="J53" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="54" customHeight="1" spans="3:10">
       <c r="C54" s="1">
         <v>49</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="E54" s="3">
         <v>5</v>
@@ -2601,15 +2777,18 @@
         <v>6</v>
       </c>
       <c r="I54" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="55" customHeight="1" spans="3:9">
+        <v>22</v>
+      </c>
+      <c r="J54" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="55" customHeight="1" spans="3:10">
       <c r="C55" s="1">
         <v>50</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="E55" s="3">
         <v>5</v>
@@ -2625,15 +2804,18 @@
         <v>6</v>
       </c>
       <c r="I55" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="56" customHeight="1" spans="3:9">
+        <v>25</v>
+      </c>
+      <c r="J55" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="56" customHeight="1" spans="3:10">
       <c r="C56" s="1">
         <v>51</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="E56" s="3">
         <v>5</v>
@@ -2649,15 +2831,18 @@
         <v>6</v>
       </c>
       <c r="I56" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="57" customHeight="1" spans="3:9">
+        <v>28</v>
+      </c>
+      <c r="J56" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="57" customHeight="1" spans="3:10">
       <c r="C57" s="1">
         <v>52</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="E57" s="3">
         <v>5</v>
@@ -2673,15 +2858,18 @@
         <v>2</v>
       </c>
       <c r="I57" s="1" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="58" customHeight="1" spans="3:9">
+        <v>46</v>
+      </c>
+      <c r="J57" s="1">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="58" customHeight="1" spans="3:10">
       <c r="C58" s="1">
         <v>53</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="E58" s="3">
         <v>5</v>
@@ -2697,15 +2885,18 @@
         <v>2</v>
       </c>
       <c r="I58" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="59" customHeight="1" spans="3:9">
+        <v>48</v>
+      </c>
+      <c r="J58" s="1">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="59" customHeight="1" spans="3:10">
       <c r="C59" s="1">
         <v>54</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="E59" s="3">
         <v>5</v>
@@ -2721,15 +2912,18 @@
         <v>2</v>
       </c>
       <c r="I59" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="60" customHeight="1" spans="3:9">
+        <v>50</v>
+      </c>
+      <c r="J59" s="1">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="60" customHeight="1" spans="3:10">
       <c r="C60" s="1">
         <v>55</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="E60" s="3">
         <v>5</v>
@@ -2745,15 +2939,18 @@
         <v>7</v>
       </c>
       <c r="I60" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="61" customHeight="1" spans="3:9">
+        <v>13</v>
+      </c>
+      <c r="J60" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" customHeight="1" spans="3:10">
       <c r="C61" s="1">
         <v>56</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="E61" s="3">
         <v>5</v>
@@ -2769,15 +2966,18 @@
         <v>7</v>
       </c>
       <c r="I61" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="62" customHeight="1" spans="3:9">
+        <v>16</v>
+      </c>
+      <c r="J61" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="62" customHeight="1" spans="3:10">
       <c r="C62" s="1">
         <v>57</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="E62" s="3">
         <v>5</v>
@@ -2793,15 +2993,18 @@
         <v>7</v>
       </c>
       <c r="I62" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="63" customHeight="1" spans="3:9">
+        <v>19</v>
+      </c>
+      <c r="J62" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" customHeight="1" spans="3:10">
       <c r="C63" s="1">
         <v>58</v>
       </c>
       <c r="D63" s="5" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="E63" s="3">
         <v>5</v>
@@ -2817,15 +3020,18 @@
         <v>7</v>
       </c>
       <c r="I63" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="64" customHeight="1" spans="3:9">
+        <v>22</v>
+      </c>
+      <c r="J63" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="64" customHeight="1" spans="3:10">
       <c r="C64" s="1">
         <v>59</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="E64" s="3">
         <v>5</v>
@@ -2841,15 +3047,18 @@
         <v>7</v>
       </c>
       <c r="I64" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="65" customHeight="1" spans="3:9">
+        <v>25</v>
+      </c>
+      <c r="J64" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="65" customHeight="1" spans="3:10">
       <c r="C65" s="1">
         <v>60</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="E65" s="3">
         <v>5</v>
@@ -2865,15 +3074,18 @@
         <v>7</v>
       </c>
       <c r="I65" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="66" customHeight="1" spans="3:9">
+        <v>28</v>
+      </c>
+      <c r="J65" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="66" customHeight="1" spans="3:10">
       <c r="C66" s="1">
         <v>61</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="E66" s="3">
         <v>5</v>
@@ -2889,15 +3101,18 @@
         <v>2</v>
       </c>
       <c r="I66" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="67" customHeight="1" spans="3:9">
+        <v>58</v>
+      </c>
+      <c r="J66" s="1">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="67" customHeight="1" spans="3:10">
       <c r="C67" s="1">
         <v>62</v>
       </c>
       <c r="D67" s="6" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="E67" s="3">
         <v>5</v>
@@ -2913,15 +3128,18 @@
         <v>2</v>
       </c>
       <c r="I67" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="68" customHeight="1" spans="3:9">
+        <v>60</v>
+      </c>
+      <c r="J67" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="68" customHeight="1" spans="3:10">
       <c r="C68" s="1">
         <v>63</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="E68" s="3">
         <v>5</v>
@@ -2937,15 +3155,18 @@
         <v>2</v>
       </c>
       <c r="I68" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="69" customHeight="1" spans="3:9">
+        <v>62</v>
+      </c>
+      <c r="J68" s="1">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="69" customHeight="1" spans="3:10">
       <c r="C69" s="1">
         <v>64</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="E69" s="3">
         <v>5</v>
@@ -2961,15 +3182,18 @@
         <v>8</v>
       </c>
       <c r="I69" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="70" customHeight="1" spans="3:9">
+        <v>13</v>
+      </c>
+      <c r="J69" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70" customHeight="1" spans="3:10">
       <c r="C70" s="1">
         <v>65</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="E70" s="3">
         <v>5</v>
@@ -2985,15 +3209,18 @@
         <v>8</v>
       </c>
       <c r="I70" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="71" customHeight="1" spans="3:9">
+        <v>16</v>
+      </c>
+      <c r="J70" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="71" customHeight="1" spans="3:10">
       <c r="C71" s="1">
         <v>66</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="E71" s="3">
         <v>5</v>
@@ -3009,15 +3236,18 @@
         <v>8</v>
       </c>
       <c r="I71" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="72" customHeight="1" spans="3:9">
+        <v>19</v>
+      </c>
+      <c r="J71" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="72" customHeight="1" spans="3:10">
       <c r="C72" s="1">
         <v>67</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="E72" s="3">
         <v>5</v>
@@ -3033,15 +3263,18 @@
         <v>8</v>
       </c>
       <c r="I72" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="73" customHeight="1" spans="3:9">
+        <v>22</v>
+      </c>
+      <c r="J72" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73" customHeight="1" spans="3:10">
       <c r="C73" s="1">
         <v>68</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="E73" s="3">
         <v>5</v>
@@ -3057,15 +3290,18 @@
         <v>8</v>
       </c>
       <c r="I73" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="74" customHeight="1" spans="3:9">
+        <v>25</v>
+      </c>
+      <c r="J73" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="74" customHeight="1" spans="3:10">
       <c r="C74" s="1">
         <v>69</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>93</v>
+        <v>104</v>
       </c>
       <c r="E74" s="3">
         <v>5</v>
@@ -3081,15 +3317,18 @@
         <v>8</v>
       </c>
       <c r="I74" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="75" customHeight="1" spans="3:9">
+        <v>28</v>
+      </c>
+      <c r="J74" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="75" customHeight="1" spans="3:10">
       <c r="C75" s="1">
         <v>70</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>94</v>
+        <v>105</v>
       </c>
       <c r="E75" s="3">
         <v>5</v>
@@ -3105,15 +3344,18 @@
         <v>2</v>
       </c>
       <c r="I75" s="1" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="76" customHeight="1" spans="3:9">
+        <v>70</v>
+      </c>
+      <c r="J75" s="1">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="76" customHeight="1" spans="3:10">
       <c r="C76" s="1">
         <v>71</v>
       </c>
       <c r="D76" s="5" t="s">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="E76" s="3">
         <v>5</v>
@@ -3129,15 +3371,18 @@
         <v>2</v>
       </c>
       <c r="I76" s="1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="77" customHeight="1" spans="3:9">
+        <v>72</v>
+      </c>
+      <c r="J76" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="77" customHeight="1" spans="3:10">
       <c r="C77" s="1">
         <v>72</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>96</v>
+        <v>107</v>
       </c>
       <c r="E77" s="3">
         <v>5</v>
@@ -3153,7 +3398,10 @@
         <v>2</v>
       </c>
       <c r="I77" s="1" t="s">
-        <v>63</v>
+        <v>74</v>
+      </c>
+      <c r="J77" s="1">
+        <v>11</v>
       </c>
     </row>
     <row r="106" customHeight="1" spans="6:6">
@@ -3164,10 +3412,10 @@
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="F3 F4 F5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="F3:F5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,F3)&lt;2</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="E3:E5 I3:I5 C3:D5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="I3:I5 C3:E5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>
